--- a/bronzeville_assets.xlsx
+++ b/bronzeville_assets.xlsx
@@ -21,6 +21,9 @@
     <sheet name="CTA Bus Routes" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Metra Stations" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Metra Lines" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Bike Routes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Divvy Stations" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bike Racks" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +46,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +98,21 @@
         <fgColor rgb="001A5276"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000897B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004DD0E1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -140,6 +158,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -16345,6 +16372,3987 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>street</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>st_name</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>oneway_dir</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>f_street</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>t_street</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>displayrou</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>mi_ctrline</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>br_oneway</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>br_ow_dir</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>the_geom.type</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>the_geom.coordinates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MARTIN LUTHER KING JR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>E 60TH ST</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>E GARFIELD BLVD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bike Lane</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.606632445511</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>[[[-87.61596722873355, 41.79447924837816], [-87.61596240494777, 41.79430050261858], [-87.61595387958901, 41.794019324842175], [-87.61595221895054, 41.793914372880195], [-87.6159492328856, 41.7937256581611], [-87.61593750022224, 41.79327162576783], [-87.61592978257218, 41.79299366364513], [-87.6159225351212, 41.79273266440588], [-87.61590789718983, 41.79214452861778], [-87.61589672766125, 41.79171566450216], [-87.61589595174317, 41.79168566437099], [-87.61588731154538, 41.791353223202755], [-87.61588373604435, 41.79116387266975], [-87.61587938048893, 41.7909332432366], [-87.61586361475077, 41.790216173130815], [-87.61584652197911, 41.78953257521417], [-87.61584193583178, 41.78934637405001], [-87.6158306194276, 41.788887047122536], [-87.61581249137379, 41.788158243893456], [-87.61579995532938, 41.78764487448411], [-87.61579650199282, 41.78751482823511], [-87.61578787016359, 41.78718979679211], [-87.61577690448134, 41.78670003809722], [-87.61575999695505, 41.78593413949687], [-87.61575383227367, 41.78569102954054]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MORGAN DR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MORGAN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>E GARFIELD BLVD</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>E RAINEY DR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.273718846564</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[[[-87.61596722873355, 41.79447924837816], [-87.6146469845286, 41.79448424318099], [-87.61456787464198, 41.79436714347174], [-87.61450709727534, 41.79431895802028], [-87.6143985569633, 41.794255873500255], [-87.6141197215744, 41.79414946114153], [-87.61382441334366, 41.79403383425632], [-87.6134815765371, 41.79389227663244], [-87.6130801537817, 41.793723402199994], [-87.61266529980448, 41.793548871617894], [-87.61256569245539, 41.79351690629572], [-87.61228726976846, 41.793452589898784], [-87.61192237827309, 41.793381692076636], [-87.61160240422876, 41.79331461549506], [-87.61135460974891, 41.79325965395785], [-87.61113643580505, 41.79319189681021]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RAINEY DR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RAINEY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>E MORGAN DR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S PAYNE DR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.178889999619</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[[[-87.61113643580505, 41.79319189681021], [-87.61027140525307, 41.79324090422853], [-87.60989251887229, 41.79329304690278], [-87.60937437248673, 41.79342496623983], [-87.60886325840134, 41.793616204143184], [-87.60865500686141, 41.7937165630091], [-87.60857624945564, 41.79375451664176], [-87.60832625016991, 41.793901789122955], [-87.60815780062902, 41.794007341210126], [-87.60799024123432, 41.794105496864226]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MARTIN LUTHER KING JR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>E 63RD ST</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>E 60TH ST</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Marked Shared Lane</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.376882833436</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[[[-87.61575383227367, 41.78569102954054], [-87.61574993781109, 41.78553744521935], [-87.61574138360854, 41.78517657282576], [-87.61573776816034, 41.78502407786211], [-87.61573285074613, 41.78482393338706], [-87.61573153730231, 41.78476080670819], [-87.61572472739175, 41.78450016636337], [-87.61571872246783, 41.78427586575751], [-87.61571485138407, 41.78413637750075], [-87.61570778700545, 41.7838763432772], [-87.61569941071674, 41.78356793917766], [-87.61569566745142, 41.78337093071964], [-87.61569072742108, 41.7831267676854], [-87.6156851515035, 41.782883644180046], [-87.61568021674788, 41.78266857073254], [-87.6156740657309, 41.78240151307447], [-87.61567022077433, 41.78223337383118], [-87.615666220557, 41.78206578282973], [-87.61566197396462, 41.78188781729118], [-87.61565468608553, 41.78162077950507], [-87.61564598878145, 41.78130258011225], [-87.61563835812058, 41.78102346549074], [-87.61563106734714, 41.780756592410725], [-87.61562912474022, 41.78068679372381], [-87.61562591117682, 41.780571321066525], [-87.61562193693463, 41.78043690467687], [-87.61561662312582, 41.78023125459074]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STONY ISLAND AVE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>STONY ISLAND</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E 59TH ST</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>E 56TH ST</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.378464121006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[[[-87.58662892252528, 41.78789358129685], [-87.586706089987, 41.79153912486357], [-87.58663186923798, 41.79337593873825]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>63RD ST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>63RD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>S MARYLAND AVE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S STONY ISLAND AVE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bike Lane</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.939759213128</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[[[-87.6046422414081, 41.78042037203421], [-87.58645234642981, 41.78061152172805]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>55TH PL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>55TH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>S DORCHESTER AVE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>E 55TH ST</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.140520676257</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[[[-87.59168916179809, 41.795501250471744], [-87.59156420785152, 41.79550224079574], [-87.59131454042925, 41.79550235705856], [-87.59109786212012, 41.79550386629565], [-87.59085770346485, 41.79550615703121], [-87.59063312557093, 41.79550898557082], [-87.59034113508434, 41.79551248331219], [-87.59008263205658, 41.79551557934015], [-87.58986476270361, 41.79551853261422], [-87.58969927989575, 41.795519959075364], [-87.58959813856721, 41.79551348622447], [-87.58949753203959, 41.795492500363025], [-87.58941006033334, 41.795458316572784], [-87.58930035814839, 41.79539227921674], [-87.58923659094965, 41.795287816040414], [-87.58921021181861, 41.795222275968634], [-87.58920472557244, 41.79519313923364]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OAKWOOD BLVD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OAKWOOD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>S COTTAGE GROVE AVE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bike Lane</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.521985922417</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[[[-87.61695962339326, 41.82264134188429], [-87.61669629612875, 41.82264370313865], [-87.61606631519486, 41.822649350671306], [-87.61515537131041, 41.82265750964905], [-87.61417375753305, 41.822666282273154], [-87.61359604756068, 41.82267144039865], [-87.61289063246282, 41.82267242469886], [-87.6121351823511, 41.8226734740702], [-87.611723286215, 41.82267866256548], [-87.61021322833639, 41.82269767014164], [-87.60979638334024, 41.82270234788722], [-87.60820507512415, 41.82272019148444], [-87.6069221364619, 41.82272643226638], [-87.60684961994563, 41.822720681391324]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ELLSWORTH DR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ELLSWORTH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>E GARFIELD BLVD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>E 51ST ST</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.563850072419</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[[[-87.61610503358958, 41.80209463506868], [-87.61598017987416, 41.801936535122216], [-87.61571941210941, 41.80151328586742], [-87.61550944727176, 41.80119731531666], [-87.61539693942696, 41.80102858217285], [-87.61529932756855, 41.80088235809726], [-87.61506155892664, 41.80053756279236], [-87.614929442976, 41.80036126695795], [-87.6147326797903, 41.80020701596753], [-87.61447389984386, 41.800029817334064], [-87.61431845146083, 41.799919979246425], [-87.6141480647915, 41.79976531521329], [-87.61403399880841, 41.7996282102345], [-87.61398065771237, 41.799550981614956], [-87.61395599984449, 41.79950944339995], [-87.61391106290475, 41.79939892462118], [-87.61389464937568, 41.79934160352373], [-87.61388617434496, 41.799296050230076], [-87.61388737070605, 41.79922835661386], [-87.61389328726345, 41.79900113927943], [-87.61391381323126, 41.798644730896484], [-87.61392200607862, 41.79853402352384], [-87.61392355907101, 41.798501352248834], [-87.61392547720082, 41.798460992447886], [-87.61396071892041, 41.79813000580307], [-87.61400731520777, 41.79785924549823], [-87.6140570307326, 41.79763090320573], [-87.6141338608941, 41.79734899758503], [-87.61419534320311, 41.797160438942676], [-87.61428035246796, 41.79693075355048], [-87.61437410917135, 41.7966928071726], [-87.61439017940391, 41.79665131864515], [-87.61448490414, 41.79640677773468], [-87.61455078269736, 41.796175847853924], [-87.61459809192392, 41.79591974491938], [-87.61462586548868, 41.79561330073654], [-87.61463898952323, 41.7953906021651], [-87.6146621547144, 41.79508629626382], [-87.61469428955904, 41.7949442612965], [-87.61469972612767, 41.794814738076944], [-87.61469151426928, 41.79468057278534], [-87.61467818509446, 41.79459684387978], [-87.6146469845286, 41.79448424318099]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MARTIN LUTHER KING JR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>E 51ST ST</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>E 37TH ST</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.75304400525</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[[[-87.6170661605481, 41.82746577345483], [-87.61706142929766, 41.82722251576819], [-87.61703594211926, 41.82599621919331], [-87.6170346569476, 41.825924585756425], [-87.61702807683459, 41.825640732364505], [-87.61701815626563, 41.825212839267834], [-87.61701158986415, 41.824860489202024], [-87.61700504238831, 41.82446703021115], [-87.61699819000684, 41.82410092909017], [-87.61699111101917, 41.82382621643897], [-87.6169682780898, 41.82294010913907], [-87.61695962339326, 41.82264134188429], [-87.61694647296191, 41.82218741283243], [-87.61694134071122, 41.82200285608154], [-87.61691550518213, 41.82107381642339], [-87.61690011817095, 41.820520501742], [-87.6168912291518, 41.82022584659349], [-87.61687951834088, 41.819837625724176], [-87.61686451475447, 41.81931905960095], [-87.61685917407235, 41.819134444733976], [-87.61685486347649, 41.81903471854085], [-87.61685026940104, 41.81886108718419], [-87.61684584573, 41.818632543662474], [-87.61683899958928, 41.818426428036624], [-87.61682859667718, 41.81811322063313], [-87.61682317373558, 41.81791516029109], [-87.6168170711122, 41.81769914813044], [-87.61681204388093, 41.81752487028064], [-87.6168097679134, 41.8174459431259], [-87.61680154890371, 41.817143281582915], [-87.61680085310701, 41.81711867608355], [-87.61679454768834, 41.8168960333512], [-87.61678662778932, 41.816627119659934], [-87.61677714364522, 41.81630505574234], [-87.61677062740476, 41.81603396382891], [-87.61676552375634, 41.81582380290046], [-87.61675765682091, 41.81555209840315], [-87.61675059408309, 41.81531687029233], [-87.61674224579149, 41.815039015176694], [-87.61673544566895, 41.814814353391846], [-87.61672717933429, 41.814541247209775], [-87.61672053521322, 41.814281652787514], [-87.6167133124245, 41.814034457969235], [-87.61670518857355, 41.813756248551975], [-87.61669736056754, 41.8134778473913], [-87.61668988955066, 41.8131937690335], [-87.61668445767971, 41.813002180182174], [-87.61667472405641, 41.812658842819], [-87.616665225364, 41.812313114669124], [-87.61666403964655, 41.81227254737789], [-87.6166590672492, 41.812102152014056], [-87.61665296669604, 41.811892506022836], [-87.61664655510585, 41.811671359704654], [-87.61664207135496, 41.81149114274442], [-87.61663372407628, 41.811189079715234], [-87.61662461081087, 41.81085932970484], [-87.61662055015955, 41.81066750713534], [-87.61661158374402, 41.81035309368742], [-87.61660946369571, 41.81028007730828], [-87.61660532895206, 41.81013765741237], [-87.6165971626926, 41.809869902413276], [-87.61658969716275, 41.809631378067415], [-87.6165830260001, 41.80937622288194], [-87.61657750843742, 41.80916515967291], [-87.61657434552195, 41.80905399609861], [-87.61656977392795, 41.80889161626314], [-87.61656382612986, 41.80868147771314], [-87.6165595258573, 41.80852434140443], [-87.61655442132603, 41.80832082118215], [-87.61654832746574, 41.80807121930493], [-87.61654000442812, 41.8077846368839], [-87.61653454090984, 41.80755514196061], [-87.61652978730874, 41.80735545128697], [-87.61652116505952, 41.80702339471532], [-87.61650989769541, 41.806543569441665], [-87.6165048970603, 41.80633409577223], [-87.61649750571686, 41.805990301736024], [-87.61649069419391, 41.80573396875114], [-87.61648329413629, 41.80545551854538], [-87.6164821821902, 41.80541072451418], [-87.61647834932612, 41.8052344630603], [-87.61646633002383, 41.80475973793773], [-87.61645839638088, 41.80443169207701], [-87.61644878457702, 41.804030528954634], [-87.61644580038985, 41.803914590028064], [-87.61644156658187, 41.80375012783846], [-87.61643122120574, 41.803483868826675], [-87.61640545455953, 41.80318628304824], [-87.61636657748137, 41.803006515619764], [-87.6163590650835, 41.80297177546721], [-87.61625552696026, 41.80267897305564], [-87.61618167023049, 41.8024149789362], [-87.61610503358958, 41.80209463506868]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>55TH ST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>55TH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>S COTTAGE GROVE AVE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>S DORCHESTER AVE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.766203524173</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[[[-87.60620979087955, 41.79495747442708], [-87.6057344224648, 41.79495778503282], [-87.60525201125915, 41.79496326297865], [-87.60479417557326, 41.794968318532064], [-87.60416578190858, 41.79497613248727], [-87.60382968914276, 41.79497974562034], [-87.60364258908545, 41.79498175626839], [-87.6031618006071, 41.79498638580917], [-87.60258003192963, 41.79499286770068], [-87.60201296951952, 41.794999330425995], [-87.60176485131475, 41.79500208669209], [-87.60130428020985, 41.79500683720651], [-87.60083389016755, 41.795011687128714], [-87.60050008922202, 41.79501581473183], [-87.6002440069741, 41.79501912014317], [-87.59977157954289, 41.79502367900555], [-87.59944937777256, 41.79502678009304], [-87.5991151755601, 41.795030737243415], [-87.59876610668249, 41.79503599750648], [-87.59846421388181, 41.795039746997446], [-87.59809252263335, 41.79504284460396], [-87.59783639943313, 41.79504497752776], [-87.59764672479376, 41.79504746882311], [-87.59746279967632, 41.79504988499188], [-87.59729500945298, 41.795051197774896], [-87.59714467615815, 41.79505237459098], [-87.59712751034556, 41.79505261932045], [-87.59653845570257, 41.79505834324881], [-87.59587785724203, 41.79506631315715], [-87.59585440739944, 41.795062984370915], [-87.59491762743127, 41.79507687701188], [-87.59334179382368, 41.795100230834926], [-87.59230182841584, 41.795115630665705], [-87.592302990093, 41.795150774423014], [-87.59230046172085, 41.795201582121706], [-87.59228243740286, 41.795250862799094], [-87.59224146498102, 41.795340996591], [-87.59222898325629, 41.79535145199423], [-87.59207943860847, 41.79544011543386], [-87.5920123125014, 41.79546698816598], [-87.59190924617853, 41.795490664939614], [-87.59181796862944, 41.7955002290602], [-87.59168916179809, 41.795501250471744]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DREXEL BLVD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DREXEL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>E HYDE PARK BLVD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>E OAKWOOD BLVD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.44027790321</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[[[-87.6061357829986, 41.82285126887031], [-87.60609798571573, 41.82276399646166], [-87.60590091255791, 41.82238247366579], [-87.60556669332729, 41.8218485016191], [-87.60530502182334, 41.82143367779866], [-87.60503607482781, 41.82100731247258], [-87.6048651023532, 41.820736412610586], [-87.60468547053425, 41.82045272301633], [-87.60449083328942, 41.820146654278034], [-87.6044256482468, 41.820039488053965], [-87.60440298975179, 41.8199636312076], [-87.60436493891923, 41.819611683642336], [-87.60429991730739, 41.819055419679465], [-87.60429380433658, 41.81900362340333], [-87.60426189555417, 41.8187247681738], [-87.60423424833219, 41.81848098336986], [-87.60420878995686, 41.81825126419623], [-87.60417455131629, 41.817968413673675], [-87.60415552556421, 41.81781123864321], [-87.60413394449134, 41.81761153828346], [-87.60411028125793, 41.81739508449601], [-87.6040885112337, 41.8171992256062], [-87.6040700938691, 41.81703439693089], [-87.60405800489534, 41.81683774595473], [-87.60404268597567, 41.816588553468314], [-87.60403709666593, 41.81630849303128], [-87.60403120520014, 41.8160161354863], [-87.60402385839835, 41.81570661792346], [-87.6040170517352, 41.81545621443974], [-87.60400794890579, 41.81501570099713], [-87.60400263005133, 41.814758282399495], [-87.6039971166536, 41.8145069813334], [-87.60399159427311, 41.81425010973378], [-87.60398593909036, 41.81399836927459], [-87.60398044110272, 41.813765236437085], [-87.60397499985255, 41.81352699896516], [-87.60396816319397, 41.813199599950835], [-87.60396389986742, 41.8129954454885], [-87.60395896340789, 41.81276777679964], [-87.60395507075744, 41.812587068895915], [-87.60395103323813, 41.81239971908291], [-87.60394749744123, 41.81224261431615], [-87.60394634625938, 41.812192497109486], [-87.60394481883999, 41.812126322466376], [-87.60393970922209, 41.8119040592473], [-87.60393553325102, 41.81172255360749], [-87.60392887286369, 41.811376458031624], [-87.60392551762324, 41.81120206585357], [-87.6039220751111, 41.811026987049004], [-87.60391755623571, 41.81080453486339], [-87.60391271281719, 41.810565396211956], [-87.60390920747359, 41.810395859547214], [-87.60390545674095, 41.810224510714114], [-87.6039029260037, 41.810108878818895], [-87.60389805780825, 41.80989781291501], [-87.60389154426316, 41.80955704103505], [-87.60388737756344, 41.80933909368288], [-87.6038839679615, 41.80921055686321], [-87.60387961854272, 41.80904658706937], [-87.60387371153965, 41.80877837916568], [-87.60386741299754, 41.80847998089812], [-87.60386217213637, 41.80822741989517], [-87.60385829065206, 41.80802316594071], [-87.60385239269901, 41.80773868420216], [-87.60384783613233, 41.80751883906607], [-87.60384274399121, 41.807243419051346], [-87.60383646805631, 41.80693986273583], [-87.60383088501047, 41.80664640914328], [-87.6038268275711, 41.80644791716319], [-87.60381920996646, 41.8061785179137], [-87.60381478491121, 41.80591612025036], [-87.60381184231792, 41.80574166480126], [-87.60380626616268, 41.80551868439242], [-87.60380179621455, 41.80533089313059], [-87.60379613662855, 41.80512799991602], [-87.60379079943327, 41.80490019151557], [-87.6037865313686, 41.80469439808748], [-87.6037805331614, 41.80445368703591], [-87.60377677465617, 41.804267683853766], [-87.60377404877609, 41.80410075937107], [-87.60377006455334, 41.80385690535313], [-87.60376813499602, 41.80374251152941], [-87.60376478430065, 41.80361114875377], [-87.60375648729162, 41.803366141884204], [-87.60375141035728, 41.80319294589922], [-87.60374820447251, 41.803022835593254], [-87.60374626819105, 41.80289938597228], [-87.60374406398431, 41.80276709679405], [-87.603741005496, 41.802597042333126], [-87.60377786306702, 41.802278554577875]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MARTIN LUTHER KING JR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>E GARFIELD BLVD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>E 51ST ST</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bike Lane</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.525487613949</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[[[-87.61610503358958, 41.80209463506868], [-87.6161372553474, 41.80190169269912], [-87.61614074146709, 41.80158907436339], [-87.61612777562215, 41.80089368105505], [-87.61611061011892, 41.80022228554601], [-87.6161072447521, 41.80009063210527], [-87.61609367670414, 41.799567542526496], [-87.61608066594823, 41.799007655365806], [-87.61607252526402, 41.798655650381], [-87.61607043851457, 41.798547458174994], [-87.6160678890834, 41.798457127876596], [-87.61605837110685, 41.79805028367454], [-87.61604192712679, 41.79739045646684], [-87.6160235286314, 41.79670545121182], [-87.61602194699849, 41.79663990734271], [-87.61601550198797, 41.7963728214937], [-87.61599616418324, 41.79563948379497], [-87.61599287316523, 41.795514680599055], [-87.61597940877292, 41.795011981545464], [-87.6159753641248, 41.794792923748744], [-87.6159725954511, 41.7946429706259], [-87.61596722873355, 41.79447924837816]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>55TH ST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>55TH</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>S HYDE PARK BLVD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>S SHORE DR</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Marked Shared Lane</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.158892281839</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[[[-87.58394543361024, 41.795220065764205], [-87.5835817620467, 41.795223797172596], [-87.58327948192816, 41.79522915096661], [-87.58324210928754, 41.79522947236536], [-87.5829312072739, 41.795232145317705], [-87.58253279286843, 41.79523559512813], [-87.58220685560578, 41.795238416348866], [-87.5819200476465, 41.79524101361322], [-87.58182560768654, 41.79524177247036], [-87.58163397586631, 41.79524331336056], [-87.58124686189768, 41.795246514830914], [-87.58086945340737, 41.79525705071672]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>31ST ST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>31ST</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S MOE DR</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.374564177222</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[[[-87.61711743673902, 41.83841544388878], [-87.61349382112748, 41.83846417399243], [-87.61336507987872, 41.8384654324603], [-87.61170778684063, 41.8384964974145], [-87.6113260948113, 41.838513422816135], [-87.61122239818451, 41.83851802083818], [-87.61106328407865, 41.83852507577069], [-87.61079286825503, 41.83852833767229], [-87.61023646107017, 41.83853504871899], [-87.61004517815752, 41.83853385151719], [-87.60986250664294, 41.83853270823932]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>33RD ST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>33RD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>S STATE ST</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Marked Shared Lane</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.47034639757</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[[[-87.62649453439884, 41.834657620039394], [-87.6261375484813, 41.834653255468275], [-87.62598820768505, 41.834655523097894], [-87.6258713558933, 41.83465729648271], [-87.62555479911322, 41.834663112644094], [-87.62521987635559, 41.834667222892755], [-87.62505539738287, 41.834670172980104], [-87.62490108129768, 41.834672941521305], [-87.62458217233613, 41.834675666707916], [-87.62423396810284, 41.83467955437231], [-87.62419467526055, 41.83468228203092], [-87.62332410153712, 41.834694699177206], [-87.6225766889668, 41.834705354550316], [-87.62204427228347, 41.83471294207457], [-87.62183407802331, 41.834710293288616], [-87.62162465056676, 41.834707653371126], [-87.62122627094816, 41.83471231672194], [-87.62080305524594, 41.834717269393636], [-87.62061503357474, 41.834712419521736], [-87.62049200866362, 41.83470924673693], [-87.6196388712932, 41.834730650392935], [-87.61940523053126, 41.834732824088015], [-87.61923746068237, 41.8347343849626], [-87.61879845501683, 41.83473992804518], [-87.61849043146212, 41.83474381686139], [-87.61818788325031, 41.83474705287812], [-87.61738398483341, 41.83475564899769]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OAKWOOD BLVD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OAKWOOD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>S COTTAGE GROVE AVE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>E PERSHING RD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bike Lane</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.179532699715</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[[[-87.60684961994563, 41.822720681391324], [-87.60679180817826, 41.82272115395717], [-87.60677001340125, 41.82272103500519], [-87.60674821900858, 41.82272120146208], [-87.60672643224186, 41.822721651572905], [-87.60670465910856, 41.822722386276055], [-87.60668290562634, 41.822723405609615], [-87.60666118024034, 41.82272470782627], [-87.60663948895807, 41.82272629386447], [-87.60661783660379, 41.82272816285434], [-87.60659623160228, 41.822730314849224], [-87.60657467999161, 41.822732748086665], [-87.60655318900317, 41.82273546171211], [-87.60653176465463, 41.82273845576364], [-87.60651041297386, 41.822741729379096], [-87.6064891412025, 41.82274528080366], [-87.60646795535817, 41.82274911007541], [-87.60644686148913, 41.82275321453169], [-87.60642586802022, 41.8227575942258], [-87.60640497858236, 41.82276224738011], [-87.60638420162077, 41.82276717224742], [-87.6063635431735, 41.82277236706532], [-87.60634300805471, 41.82277783186432], [-87.60632260352641, 41.82278356308904], [-87.60630233682008, 41.822789559885024], [-87.60628221277028, 41.82279582048222], [-87.60626223741507, 41.82280234311821], [-87.6062424168028, 41.822809125130334], [-87.60622275817514, 41.8228161647638], [-87.60620326757022, 41.822823460256195], [-87.60618394862924, 41.82283100892967], [-87.6061357829986, 41.82285126887031], [-87.60489865036251, 41.82326907790459], [-87.60488618404133, 41.823273092730936], [-87.60487521949304, 41.823276932508655], [-87.60486278852834, 41.823281650728966], [-87.60484930661205, 41.82328723021869], [-87.60483704714119, 41.823292747232735], [-87.6048271855152, 41.82329751145608], [-87.6048184078212, 41.8233020088474], [-87.60481037940755, 41.823306348027266], [-87.60480191461397, 41.82331116882633], [-87.60479333766806, 41.82331632654415], [-87.6047855007208, 41.823321295379984], [-87.6047572327323, 41.823341526083084], [-87.60471652058943, 41.82336869605984], [-87.60470052458207, 41.823382623822745], [-87.60468485482315, 41.82339675893244], [-87.60466951859557, 41.82341109603318], [-87.60465451835765, 41.823425630638965], [-87.6046398601683, 41.82344035918691], [-87.60462554648588, 41.82345527719107], [-87.60461158337955, 41.82347038018828], [-87.60459797573527, 41.82348566190726], [-87.60458472599103, 41.823501119662524], [-87.60457183902265, 41.82351674808307], [-87.60455931849212, 41.82353254269051], [-87.6045471692855, 41.82354849721349], [-87.60453539263716, 41.823564608958954], [-87.60452399584045, 41.823580871670806], [-87.60451297774297, 41.82359728084015], [-87.60450234562784, 41.82361383111117], [-87.60449210196373, 41.8236305170976], [-87.60448224799534, 41.823647335206], [-87.60447278860879, 41.823664279165065], [-87.60446372506924, 41.823681343580795], [-87.60445506224238, 41.82369852398245], [-87.6044468013934, 41.823715814976026], [-87.6044389437976, 41.82373321026731], [-87.60443149431059, 41.82375070628574], [-87.60442445419751, 41.823768297637386], [-87.6044178259476, 41.823785977135316], [-87.6044116108056, 41.823803741186076], [-87.60440581126073, 41.82382158260278], [-87.60440042855778, 41.823839497791994], [-87.60439546517577, 41.82385748046702], [-87.60439092117632, 41.823875525226285], [-87.60438680023185, 41.823893626690996], [-87.60438310121057, 41.82391177855161], [-87.60437982657116, 41.82392997632201], [-87.60437697757878, 41.82394821460817], [-87.60437455311194, 41.82396648620023], [-87.60437255682261, 41.82398478752], [-87.60437098758929, 41.824003111357584], [-87.60436926671751, 41.82403533381279], [-87.60435230548126, 41.82416287487605]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>COTTAGE GROVE AVE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COTTAGE GROVE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>E PERSHING RD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>E 35TH ST</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bike Lane</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.535169697043</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[[[-87.61062764640718, 41.83117833227938], [-87.61056121164148, 41.8309831537708], [-87.61049735143008, 41.83088969918398], [-87.61035664310229, 41.830683783743886], [-87.61021807070779, 41.83042154772161], [-87.60976457816737, 41.82954607123712], [-87.60957313929535, 41.82921206775326], [-87.60953484063897, 41.829123898452686], [-87.60947872228488, 41.82899470323354], [-87.60920191148996, 41.828461613639654], [-87.60903435707688, 41.82813505890052], [-87.60893989467102, 41.82795095517259], [-87.60881964632634, 41.82771437489353], [-87.60875245248874, 41.82758217879819], [-87.60848246060718, 41.827057116463294], [-87.60835626491398, 41.82681471429994], [-87.6082719086208, 41.82665265487381], [-87.60807609502977, 41.82626881297509], [-87.60797191429859, 41.82606348435161], [-87.6079087205916, 41.82593893804116], [-87.60784009873232, 41.82580134557496], [-87.60760573951933, 41.82534195692333], [-87.60750781352307, 41.825147209548874], [-87.6073738248817, 41.824880744701375], [-87.60728073042753, 41.82469689396191], [-87.6071500174633, 41.824439506146774], [-87.60686734794898, 41.8239569091955]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>31ST DR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>31ST</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>S MOE DR</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>S FORT DEARBORN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.112279352219</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[[[-87.60986250664294, 41.83853270823932], [-87.6095086258396, 41.83853049214663], [-87.60918890021458, 41.83853812491465], [-87.60875811449299, 41.83854840731297], [-87.60865431875239, 41.83855088477592], [-87.60833750976242, 41.838558445341555], [-87.60824493561356, 41.83856065473611], [-87.60779764356145, 41.83857132811791], [-87.60768798164275, 41.83857394411922]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OAKWOOD BLVD</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OAKWOOD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>E PERSHING RD</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LAKESHORE DR</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.265190300727</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[[[-87.60435230548126, 41.82416287487605], [-87.60430631831143, 41.82416402356607], [-87.60428716161914, 41.824162095879494], [-87.60426796236939, 41.824160418216486], [-87.60424872656984, 41.824158991515496], [-87.6042294614419, 41.82415781582236], [-87.60421017058603, 41.824156892060216], [-87.60419086242726, 41.824156220282596], [-87.60417154057622, 41.82415580051237], [-87.60415221225436, 41.824155632795396], [-87.60413288226572, 41.82415571806249], [-87.60411355904553, 41.824156055466894], [-87.60409424500084, 41.824156645023855], [-87.60407494855669, 41.82415748678687], [-87.60405567333392, 41.82415857987863], [-87.60403642775758, 41.82415992435258], [-87.60401721664196, 41.82416152023936], [-87.60399804481145, 41.82416336666922], [-87.60397216606508, 41.82416626443172], [-87.60346372774372, 41.82428645007398], [-87.60283279718537, 41.82449961768677], [-87.60254227296632, 41.82459826474106], [-87.60246449645898, 41.82463065780316], [-87.60214041957721, 41.82476563187484], [-87.6020952755735, 41.8247849900892], [-87.6017964676506, 41.824913114836825], [-87.60160828555927, 41.824988222508935], [-87.60150680968545, 41.82502872373627], [-87.60091462496219, 41.825188150840695], [-87.60074975423764, 41.82519086558529], [-87.60046891563478, 41.82526537949098], [-87.60036960542857, 41.82529172834911], [-87.60027660609322, 41.82531640313449], [-87.59999145364394, 41.825392060591405], [-87.59984691458156, 41.8254304090753], [-87.5996240077739, 41.825489550046555], [-87.5995963400068, 41.82550927640572]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>31ST ST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>31ST</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>S MICHIGAN AVE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>S GILES AVE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.204433765585</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[[[-87.62343694336933, 41.83833704540958], [-87.62323358361407, 41.83833847406264], [-87.6219191008301, 41.838356765893344], [-87.62177979242179, 41.83835870302541], [-87.62128211303167, 41.83836481491048], [-87.62100750971918, 41.8383681865488], [-87.62063024755903, 41.83837298145963], [-87.62047048387781, 41.83837500885838], [-87.62015738391769, 41.83837922174425], [-87.61999021695806, 41.83838147080919], [-87.61947655373596, 41.838387441384285]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>35TH ST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>35TH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>S INDIANA AVE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bike Lane</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.247640012693</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[[[-87.62175790723948, 41.83105114677236], [-87.62147204346718, 41.83105439399251], [-87.62114680081156, 41.83105756560645], [-87.62071506301695, 41.83106177458682], [-87.62054500801808, 41.83106270827247], [-87.62038410991939, 41.83106359050268], [-87.61993842551381, 41.831068138560155], [-87.61959497831648, 41.83107164288365], [-87.61932790430228, 41.83107429835225], [-87.6192145415096, 41.83107542490796], [-87.61861331357758, 41.831080192721124], [-87.61840049624368, 41.8310834879503], [-87.61811354507196, 41.8310879292089], [-87.61794575632707, 41.83109052619566], [-87.61760482133919, 41.83109575717714], [-87.61730766754923, 41.83109415363711], [-87.61696083107093, 41.83109228088914]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>35TH ST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>35TH</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>S STATE ST</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>S INDIANA AVE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Marked Shared Lane</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.251982034456</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[[[-87.6266385987239, 41.83100580881331], [-87.6264732958851, 41.83101107967687], [-87.62623318245583, 41.83101873668085], [-87.62601026219642, 41.831016431371204], [-87.62591536563151, 41.83101335928809], [-87.62580089456586, 41.83100965335254], [-87.62578894519758, 41.8310097769209], [-87.62528748091881, 41.83101497359384], [-87.62497040535462, 41.83101825860181], [-87.62460523369673, 41.83102204008217], [-87.62425145860854, 41.831023753331884], [-87.62423505388152, 41.83102409322796], [-87.62325146933688, 41.831035886002816], [-87.623068985482, 41.831038072800894], [-87.62257009356864, 41.831042925980455], [-87.62249985576759, 41.831043609555515], [-87.62195505561091, 41.831048907025604], [-87.62175790723948, 41.83105114677236]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PERSHING RD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PERSHING</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>S MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>S COTTAGE GROVE AVE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.52273584865</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[[[-87.61699111101917, 41.82382621643897], [-87.61672658426848, 41.823830247623874], [-87.61611742079225, 41.823839530348515], [-87.61610351380473, 41.8238397010112], [-87.6154691158385, 41.82384748030514], [-87.61514202830347, 41.82385149048068], [-87.61435832379438, 41.82386109676443], [-87.61307015328607, 41.82387688472249], [-87.61261856025574, 41.82388291330555], [-87.61213034165046, 41.82388942863265], [-87.61127647198559, 41.82389814834697], [-87.61055372981066, 41.82390552337138], [-87.60983565600785, 41.82391284582243], [-87.60958135685671, 41.82391543849396], [-87.6083907741053, 41.82392832878097], [-87.60833202655425, 41.82392896457945], [-87.60732163043673, 41.82394102449633], [-87.60702288161544, 41.823950057947265], [-87.60691033374472, 41.82395217241693], [-87.60686734794898, 41.8239569091955]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PERSHING RD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PERSHING</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>S COTTAGE GROVE AVE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>E OAKWOOD BLVD</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.135533728291</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[[[-87.60686734794898, 41.8239569091955], [-87.60606651814183, 41.82417374136248], [-87.60576295911753, 41.82426465478336], [-87.60574292254485, 41.82427037292759], [-87.60572275653709, 41.824275828247], [-87.60570246591914, 41.82428101987172], [-87.60568205673985, 41.82428594513898], [-87.60566153743501, 41.824290603201796], [-87.60564091042225, 41.82429499317505], [-87.60562018535114, 41.824299113319164], [-87.60559936705677, 41.82430296186401], [-87.6055784615575, 41.824306538847644], [-87.60555747730946, 41.8243098416226], [-87.60553641792379, 41.8243128702117], [-87.60551529184642, 41.824315622867694], [-87.6054675496305, 41.82432080616751], [-87.60514959326278, 41.82431298815248], [-87.60506702606838, 41.82430186758017], [-87.60498473109828, 41.8242896709576], [-87.60490273359159, 41.824276402046785], [-87.60482105759388, 41.82426206370194], [-87.60473921548223, 41.8242465609951], [-87.6045999908213, 41.824210864913994], [-87.60435230548126, 41.82416287487605]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>31ST ST</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>31ST</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>S GILES AVE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.121774289186</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[[[-87.61947655373596, 41.838387441384285], [-87.61826297733084, 41.83840128373133], [-87.61746126495309, 41.838411426314124], [-87.61711743673902, 41.83841544388878]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PAYNE DR</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PAYNE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>E RAINEY DR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>E 55TH ST</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.0675160768248</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[[[-87.60737728719235, 41.79496310174033], [-87.60739572258301, 41.79490141710621], [-87.60759032740498, 41.794597181214684], [-87.60781895881487, 41.79429315897816], [-87.60788597312641, 41.79420071616683], [-87.60793532745689, 41.79414594962413], [-87.60799024123432, 41.794105496864226]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>55TH PL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>55TH</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>E 55TH ST</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S DORCHESTER AVE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.0456951713071</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[[[-87.59230182841584, 41.795115630665705], [-87.59228479651814, 41.79504607209104], [-87.59225548130618, 41.79497654411554], [-87.59219846154255, 41.79489528677071], [-87.59216267495331, 41.79487450803364], [-87.5920133591238, 41.794803290937494], [-87.59193680903836, 41.794782379617466], [-87.59185276036327, 41.794775717447465], [-87.59167067344248, 41.79477653357941]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>55TH PL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>55TH</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>S DORCHESTER AVE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>E 55TH ST</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.144696496175</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[[[-87.59167067344248, 41.79477653357941], [-87.59136866354801, 41.79477788763556], [-87.59102905319932, 41.7947802494273], [-87.5907804071988, 41.794781030192134], [-87.59057041516495, 41.79478167500291], [-87.59032230194119, 41.79478403653916], [-87.59011020296843, 41.79478605342406], [-87.58985624501801, 41.79478954209586], [-87.58964247007485, 41.794793948510694], [-87.58954419795131, 41.79480903782709], [-87.5894761210009, 41.79482602245259], [-87.5894100443973, 41.7948539709812], [-87.58930529537159, 41.794916096688844], [-87.58922782297005, 41.79504082853871], [-87.58920177375734, 41.79511475522187], [-87.58919925975736, 41.795164108872186], [-87.58920472557244, 41.79519313923364]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>55TH ST</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>55TH</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>E 55TH PL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>S LAKE PARK AVE</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.0858058887654</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[[[-87.58920472557244, 41.79519313923364], [-87.58843978013414, 41.795185708334266], [-87.58754346134559, 41.795176995453275]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>55TH ST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>55TH</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>S LAKE PARK AVE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>S HYDE PARK BLVD</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Marked Shared Lane</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.185855928634</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[[[-87.58754346134559, 41.795176995453275], [-87.58738962534618, 41.795178680573635], [-87.58723653779546, 41.79518035774402], [-87.58718928018563, 41.79518087552708], [-87.587017867405, 41.79518275390326], [-87.58694172794344, 41.7951835872402], [-87.58690389104218, 41.795184002251354], [-87.58673557437942, 41.79518584540241], [-87.58671603381707, 41.795186059636485], [-87.58661850963912, 41.79518760010154], [-87.58616460134657, 41.79519476866744], [-87.58576988324349, 41.79519906136454], [-87.58540490313923, 41.795203699386356], [-87.58511445279412, 41.795207390147176], [-87.58484326462393, 41.795207078465104], [-87.58467848640464, 41.79520974297046], [-87.58451912941597, 41.795212320129835], [-87.58431745967604, 41.79521624722297], [-87.58394543361024, 41.795220065764205]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DREXEL AVE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DREXEL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PAYNE DR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>E HYDE PARK BLVD</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.0259560495627</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[[[-87.60377786306702, 41.802278554577875], [-87.60384776240414, 41.80214837273826], [-87.60390914448635, 41.80205257522945], [-87.6039959751988, 41.801940495237204]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DREXEL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DREXEL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>E 55TH ST</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PAYNE DR</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Marked Shared Lane</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.460724495671</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[[[-87.6039959751988, 41.801940495237204], [-87.60398005001674, 41.80179839512371], [-87.60394732018125, 41.801506349931245], [-87.60394800636487, 41.801407011251754], [-87.60394177538063, 41.800830920157495], [-87.60393415361173, 41.80046182103748], [-87.60391387649038, 41.79937152781625], [-87.60389748791374, 41.798638427091994], [-87.60388128354194, 41.79789695686593], [-87.60386015715976, 41.796817882461646], [-87.60383874116336, 41.79590082721114], [-87.60382896532192, 41.795475812983724], [-87.6038116695482, 41.79541642661352], [-87.60379280282437, 41.79539201977848], [-87.60371397467722, 41.79532905985543], [-87.60367737235056, 41.795309946073175]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>55TH ST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>55TH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>S DREXEL AVE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>S ELLIS AVE</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Marked Shared Lane</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.126909173227</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[[[-87.60367737235056, 41.795309946073175], [-87.60363422547626, 41.79530530889886], [-87.6012208491939, 41.795333144426785]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>31ST ST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>31ST</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>S STATE ST</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>S MICHIGAN AVE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.162108043223</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[[[-87.62657731521406, 41.83829500304858], [-87.62604576913193, 41.838301553822], [-87.62596310195929, 41.838302687863916], [-87.62571612398844, 41.83830607252936], [-87.62535872708824, 41.838309852915415], [-87.62513747761189, 41.83831347505333], [-87.62505430825347, 41.83831483673369], [-87.62467528615595, 41.83831955124879], [-87.62429216946478, 41.838326215497126], [-87.62415443007986, 41.83832770511869], [-87.62365544777839, 41.83833551099617], [-87.62343694336933, 41.83833704540958]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>INDIANA AVE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>INDIANA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>E GARFIELD BLVD</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>E GARFIELD BLVD</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Buffered Bike Lane</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.0223385754247</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[[[-87.6208315835994, 41.79439138276337], [-87.62084038953641, 41.794714985686]]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INDIANA AVE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>INDIANA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>E GARFIELD BLVD</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>E 31ST ST</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Protected Bike Lane</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3.01258704379</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>MultiLineString</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[[[-87.62084038953641, 41.794714985686], [-87.62085281129865, 41.79522725844895], [-87.62088553211312, 41.7965073441015], [-87.62088644695537, 41.796543915816564], [-87.62092397658711, 41.79804400791659], [-87.62092040298522, 41.798191215958205], [-87.62091727595173, 41.79836556520069], [-87.62093883738828, 41.79854657799714], [-87.62096199438447, 41.799573795377476], [-87.62102112204656, 41.80201894759424], [-87.62106698675902, 41.803839766506655], [-87.62111335537706, 41.805661868259016], [-87.62115857655205, 41.807483871376355], [-87.62120718434561, 41.809303307294854], [-87.62125466765067, 41.811117100360924], [-87.62130448726721, 41.812932670214146], [-87.6213099124466, 41.81312469369885], [-87.62135313717764, 41.8147437457875], [-87.62140171476847, 41.81655610062988], [-87.62145181711834, 41.81835822286233], [-87.62150080290813, 41.82016180246785], [-87.6215515887697, 41.822008224063545], [-87.62159626319296, 41.82376737598187], [-87.62163641531164, 41.82559026112434], [-87.6216549409634, 41.82649974416645], [-87.62167588050762, 41.82740303141706], [-87.62172698340358, 41.8296165245134], [-87.62175790723948, 41.83105114677236], [-87.62179495991735, 41.832893680280165], [-87.62183407802331, 41.834710293288616], [-87.62187278204642, 41.8365029035063], [-87.62192230530282, 41.838280826193916], [-87.6219191008301, 41.838356765893344]]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="39" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>station_name</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>short_name</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>total_docks</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>docks_in_service</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>location.type</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>location.coordinates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>a3a7a4fc-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MLK Jr Dr &amp; 47th St</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHI00399</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>41.809851</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-87.616279</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>[-87.616279, 41.809851]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>a3a75d8a-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>State St &amp; 35th St</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHI00343</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>41.831036314</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-87.6267975569</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>[-87.626797556877, 41.831036314016]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>a3ad3d08-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Prairie Ave &amp; 43rd St</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CHI00545</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>41.816658893</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-87.6194124619</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>[-87.6194124619, 41.81665889302]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a3a9984a-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Indiana Ave &amp; 31st St</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CHI00436</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>41.838842</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-87.621857</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>[-87.621857, 41.838842]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>a3a634dd-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>State St &amp; 33rd St</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHI00223</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>41.834734</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-87.625813</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>[-87.625813, 41.834734]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>a3ad5764-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Calumet Ave &amp; 51st St</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHI00429</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>41.8022946509</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-87.6180535802</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>[-87.6180535802, 41.80229465088]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>a3a640d1-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fort Dearborn Dr &amp; 31st St</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CHI00222</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>41.838556</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-87.608218</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>[-87.608218, 41.838556]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a3ad2d57-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>State St &amp; Pershing Rd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CHI00491</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>41.823015238</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-87.6265680185</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>[-87.6265680185, 41.82301523798]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1963673207600511026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wabash Ave &amp; 49th St</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CHI01987</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>41.80581</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-87.6245</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>[-87.6245, 41.80581]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>b8c74f86-2873-4818-88ac-81d9ae374add</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fort Dearborn Dr &amp; 31st St*</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHI02026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>41.838676329</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-87.6088321209</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>[-87.608832120895, 41.838676328971]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>a3ac30c5-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cottage Grove Ave &amp; 51st St</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHI00502</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>41.803038</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-87.606615</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>[-87.606615, 41.803038]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>a3a97a01-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cottage Grove Ave &amp; Oakwood Blvd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHI00400</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>41.822985</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-87.6071</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>[-87.6071, 41.822985]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>a3a781a6-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>State St &amp; 29th St</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHI00231</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>41.8417</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-87.62693</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>[-87.62693, 41.8417]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>a3a743ff-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MLK Jr Dr &amp; Pershing Rd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CHI02040</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>41.8246</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-87.61678</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>[-87.61678, 41.8246]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>a3a859c4-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MLK Jr Dr &amp; 29th St</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CHI00386</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>41.842052</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-87.617</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>[-87.617, 41.842052]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1963650659022207484</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>State St &amp; 45th St</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CHI02004</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>41.81313</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-87.62585</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>[-87.62585, 41.81313]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>a3ad2843-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lake Park Ave &amp; 35th St</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CHI02032</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>41.8312742355</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-87.6087991946</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>[-87.6087991946, 41.83127423549]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>a3a96fd5-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rhodes Ave &amp; 32nd St</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CHI00328</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>41.836208</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-87.613533</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>[-87.613533, 41.836208]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>a3a7aa0e-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Indiana Ave &amp; 40th St</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CHI00256</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>41.82168</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-87.6216</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>[-87.6216, 41.82168]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>a3aae870-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cottage Grove Ave &amp; 49th St</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CHI00488</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>41.806273</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-87.606643</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>[-87.606643, 41.806273]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>a3aae35a-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Calumet Ave &amp; 35th St</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CHI00355</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>41.831379</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-87.618034</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>[-87.618034, 41.831379]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>a3a639f5-a135-11e9-9cda-0a87ae2ba916</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Calumet Ave &amp; 33rd St</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CHI00224</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>41.83472</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-87.61797</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>[-87.61797, 41.83472]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>racktype</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>stands</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>41.83345</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-87.62767</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>41.8344018</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-87.6277985</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41.8350676</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-87.626074</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>41.8354834</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-87.6252826</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>stands</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>41.8376861</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-87.6274522</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>41.8386122</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-87.6278464</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>41.8388786</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-87.6252598</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>stands</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>41.8351532</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-87.6253917</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>41.8436429</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-87.6179034</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>stands</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>41.8315193</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-87.6045969</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>41.8382594</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-87.6062423</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>41.8021714</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-87.6258327</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>stands</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>41.825588</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-87.624741</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>stands</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>41.8310116</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-87.62038</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>stands</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>41.8310276</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-87.6185682</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bike Rack</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rack</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>41.8314</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-87.627864</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/bronzeville_assets.xlsx
+++ b/bronzeville_assets.xlsx
@@ -12590,7 +12590,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cottage Grove &amp; 50th Street</t>
+          <t>Canal Street railroad bridge</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -16682,12 +16682,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STONY ISLAND AVE</t>
+          <t>55TH ST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>STONY ISLAND</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -16697,12 +16697,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E 59TH ST</t>
+          <t>E 55TH PL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>E 56TH ST</t>
+          <t>S LAKE PARK AVE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.378464121006</t>
+          <t>0.0858058887654</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -16732,19 +16732,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[[[-87.58662892252528, 41.78789358129685], [-87.586706089987, 41.79153912486357], [-87.58663186923798, 41.79337593873825]]]</t>
+          <t>[[[-87.58920472557244, 41.79519313923364], [-87.58843978013414, 41.795185708334266], [-87.58754346134559, 41.795176995453275]]]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>63RD ST</t>
+          <t>55TH ST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63RD</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -16754,22 +16754,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S MARYLAND AVE</t>
+          <t>S LAKE PARK AVE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S STONY ISLAND AVE</t>
+          <t>S HYDE PARK BLVD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Marked Shared Lane</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.939759213128</t>
+          <t>0.185855928634</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -16789,29 +16789,29 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[[[-87.6046422414081, 41.78042037203421], [-87.58645234642981, 41.78061152172805]]]</t>
+          <t>[[[-87.58754346134559, 41.795176995453275], [-87.58738962534618, 41.795178680573635], [-87.58723653779546, 41.79518035774402], [-87.58718928018563, 41.79518087552708], [-87.587017867405, 41.79518275390326], [-87.58694172794344, 41.7951835872402], [-87.58690389104218, 41.795184002251354], [-87.58673557437942, 41.79518584540241], [-87.58671603381707, 41.795186059636485], [-87.58661850963912, 41.79518760010154], [-87.58616460134657, 41.79519476866744], [-87.58576988324349, 41.79519906136454], [-87.58540490313923, 41.795203699386356], [-87.58511445279412, 41.795207390147176], [-87.58484326462393, 41.795207078465104], [-87.58467848640464, 41.79520974297046], [-87.58451912941597, 41.795212320129835], [-87.58431745967604, 41.79521624722297], [-87.58394543361024, 41.795220065764205]]]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>55TH PL</t>
+          <t>PAYNE DR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>PAYNE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S DORCHESTER AVE</t>
+          <t>E RAINEY DR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -16821,22 +16821,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.140520676257</t>
+          <t>0.0675160768248</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1W</t>
+          <t>2W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -16846,54 +16846,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[[[-87.59168916179809, 41.795501250471744], [-87.59156420785152, 41.79550224079574], [-87.59131454042925, 41.79550235705856], [-87.59109786212012, 41.79550386629565], [-87.59085770346485, 41.79550615703121], [-87.59063312557093, 41.79550898557082], [-87.59034113508434, 41.79551248331219], [-87.59008263205658, 41.79551557934015], [-87.58986476270361, 41.79551853261422], [-87.58969927989575, 41.795519959075364], [-87.58959813856721, 41.79551348622447], [-87.58949753203959, 41.795492500363025], [-87.58941006033334, 41.795458316572784], [-87.58930035814839, 41.79539227921674], [-87.58923659094965, 41.795287816040414], [-87.58921021181861, 41.795222275968634], [-87.58920472557244, 41.79519313923364]]]</t>
+          <t>[[[-87.60737728719235, 41.79496310174033], [-87.60739572258301, 41.79490141710621], [-87.60759032740498, 41.794597181214684], [-87.60781895881487, 41.79429315897816], [-87.60788597312641, 41.79420071616683], [-87.60793532745689, 41.79414594962413], [-87.60799024123432, 41.794105496864226]]]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OAKWOOD BLVD</t>
+          <t>55TH PL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OAKWOOD</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>E 55TH ST</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S COTTAGE GROVE AVE</t>
+          <t>S DORCHESTER AVE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.521985922417</t>
+          <t>0.0456951713071</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2W</t>
+          <t>1W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -16903,54 +16903,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[[[-87.61695962339326, 41.82264134188429], [-87.61669629612875, 41.82264370313865], [-87.61606631519486, 41.822649350671306], [-87.61515537131041, 41.82265750964905], [-87.61417375753305, 41.822666282273154], [-87.61359604756068, 41.82267144039865], [-87.61289063246282, 41.82267242469886], [-87.6121351823511, 41.8226734740702], [-87.611723286215, 41.82267866256548], [-87.61021322833639, 41.82269767014164], [-87.60979638334024, 41.82270234788722], [-87.60820507512415, 41.82272019148444], [-87.6069221364619, 41.82272643226638], [-87.60684961994563, 41.822720681391324]]]</t>
+          <t>[[[-87.59230182841584, 41.795115630665705], [-87.59228479651814, 41.79504607209104], [-87.59225548130618, 41.79497654411554], [-87.59219846154255, 41.79489528677071], [-87.59216267495331, 41.79487450803364], [-87.5920133591238, 41.794803290937494], [-87.59193680903836, 41.794782379617466], [-87.59185276036327, 41.794775717447465], [-87.59167067344248, 41.79477653357941]]]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ELLSWORTH DR</t>
+          <t>55TH PL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ELLSWORTH</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>E GARFIELD BLVD</t>
+          <t>S DORCHESTER AVE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>E 51ST ST</t>
+          <t>E 55TH ST</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.563850072419</t>
+          <t>0.144696496175</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2W</t>
+          <t>1W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -16960,19 +16960,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[[[-87.61610503358958, 41.80209463506868], [-87.61598017987416, 41.801936535122216], [-87.61571941210941, 41.80151328586742], [-87.61550944727176, 41.80119731531666], [-87.61539693942696, 41.80102858217285], [-87.61529932756855, 41.80088235809726], [-87.61506155892664, 41.80053756279236], [-87.614929442976, 41.80036126695795], [-87.6147326797903, 41.80020701596753], [-87.61447389984386, 41.800029817334064], [-87.61431845146083, 41.799919979246425], [-87.6141480647915, 41.79976531521329], [-87.61403399880841, 41.7996282102345], [-87.61398065771237, 41.799550981614956], [-87.61395599984449, 41.79950944339995], [-87.61391106290475, 41.79939892462118], [-87.61389464937568, 41.79934160352373], [-87.61388617434496, 41.799296050230076], [-87.61388737070605, 41.79922835661386], [-87.61389328726345, 41.79900113927943], [-87.61391381323126, 41.798644730896484], [-87.61392200607862, 41.79853402352384], [-87.61392355907101, 41.798501352248834], [-87.61392547720082, 41.798460992447886], [-87.61396071892041, 41.79813000580307], [-87.61400731520777, 41.79785924549823], [-87.6140570307326, 41.79763090320573], [-87.6141338608941, 41.79734899758503], [-87.61419534320311, 41.797160438942676], [-87.61428035246796, 41.79693075355048], [-87.61437410917135, 41.7966928071726], [-87.61439017940391, 41.79665131864515], [-87.61448490414, 41.79640677773468], [-87.61455078269736, 41.796175847853924], [-87.61459809192392, 41.79591974491938], [-87.61462586548868, 41.79561330073654], [-87.61463898952323, 41.7953906021651], [-87.6146621547144, 41.79508629626382], [-87.61469428955904, 41.7949442612965], [-87.61469972612767, 41.794814738076944], [-87.61469151426928, 41.79468057278534], [-87.61467818509446, 41.79459684387978], [-87.6146469845286, 41.79448424318099]]]</t>
+          <t>[[[-87.59167067344248, 41.79477653357941], [-87.59136866354801, 41.79477788763556], [-87.59102905319932, 41.7947802494273], [-87.5907804071988, 41.794781030192134], [-87.59057041516495, 41.79478167500291], [-87.59032230194119, 41.79478403653916], [-87.59011020296843, 41.79478605342406], [-87.58985624501801, 41.79478954209586], [-87.58964247007485, 41.794793948510694], [-87.58954419795131, 41.79480903782709], [-87.5894761210009, 41.79482602245259], [-87.5894100443973, 41.7948539709812], [-87.58930529537159, 41.794916096688844], [-87.58922782297005, 41.79504082853871], [-87.58920177375734, 41.79511475522187], [-87.58919925975736, 41.795164108872186], [-87.58920472557244, 41.79519313923364]]]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MARTIN LUTHER KING JR DR</t>
+          <t>55TH ST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MARTIN LUTHER KING JR</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -16982,22 +16982,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>E 51ST ST</t>
+          <t>S HYDE PARK BLVD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>E 37TH ST</t>
+          <t>S SHORE DR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Marked Shared Lane</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.75304400525</t>
+          <t>0.158892281839</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -17017,19 +17017,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[[[-87.6170661605481, 41.82746577345483], [-87.61706142929766, 41.82722251576819], [-87.61703594211926, 41.82599621919331], [-87.6170346569476, 41.825924585756425], [-87.61702807683459, 41.825640732364505], [-87.61701815626563, 41.825212839267834], [-87.61701158986415, 41.824860489202024], [-87.61700504238831, 41.82446703021115], [-87.61699819000684, 41.82410092909017], [-87.61699111101917, 41.82382621643897], [-87.6169682780898, 41.82294010913907], [-87.61695962339326, 41.82264134188429], [-87.61694647296191, 41.82218741283243], [-87.61694134071122, 41.82200285608154], [-87.61691550518213, 41.82107381642339], [-87.61690011817095, 41.820520501742], [-87.6168912291518, 41.82022584659349], [-87.61687951834088, 41.819837625724176], [-87.61686451475447, 41.81931905960095], [-87.61685917407235, 41.819134444733976], [-87.61685486347649, 41.81903471854085], [-87.61685026940104, 41.81886108718419], [-87.61684584573, 41.818632543662474], [-87.61683899958928, 41.818426428036624], [-87.61682859667718, 41.81811322063313], [-87.61682317373558, 41.81791516029109], [-87.6168170711122, 41.81769914813044], [-87.61681204388093, 41.81752487028064], [-87.6168097679134, 41.8174459431259], [-87.61680154890371, 41.817143281582915], [-87.61680085310701, 41.81711867608355], [-87.61679454768834, 41.8168960333512], [-87.61678662778932, 41.816627119659934], [-87.61677714364522, 41.81630505574234], [-87.61677062740476, 41.81603396382891], [-87.61676552375634, 41.81582380290046], [-87.61675765682091, 41.81555209840315], [-87.61675059408309, 41.81531687029233], [-87.61674224579149, 41.815039015176694], [-87.61673544566895, 41.814814353391846], [-87.61672717933429, 41.814541247209775], [-87.61672053521322, 41.814281652787514], [-87.6167133124245, 41.814034457969235], [-87.61670518857355, 41.813756248551975], [-87.61669736056754, 41.8134778473913], [-87.61668988955066, 41.8131937690335], [-87.61668445767971, 41.813002180182174], [-87.61667472405641, 41.812658842819], [-87.616665225364, 41.812313114669124], [-87.61666403964655, 41.81227254737789], [-87.6166590672492, 41.812102152014056], [-87.61665296669604, 41.811892506022836], [-87.61664655510585, 41.811671359704654], [-87.61664207135496, 41.81149114274442], [-87.61663372407628, 41.811189079715234], [-87.61662461081087, 41.81085932970484], [-87.61662055015955, 41.81066750713534], [-87.61661158374402, 41.81035309368742], [-87.61660946369571, 41.81028007730828], [-87.61660532895206, 41.81013765741237], [-87.6165971626926, 41.809869902413276], [-87.61658969716275, 41.809631378067415], [-87.6165830260001, 41.80937622288194], [-87.61657750843742, 41.80916515967291], [-87.61657434552195, 41.80905399609861], [-87.61656977392795, 41.80889161626314], [-87.61656382612986, 41.80868147771314], [-87.6165595258573, 41.80852434140443], [-87.61655442132603, 41.80832082118215], [-87.61654832746574, 41.80807121930493], [-87.61654000442812, 41.8077846368839], [-87.61653454090984, 41.80755514196061], [-87.61652978730874, 41.80735545128697], [-87.61652116505952, 41.80702339471532], [-87.61650989769541, 41.806543569441665], [-87.6165048970603, 41.80633409577223], [-87.61649750571686, 41.805990301736024], [-87.61649069419391, 41.80573396875114], [-87.61648329413629, 41.80545551854538], [-87.6164821821902, 41.80541072451418], [-87.61647834932612, 41.8052344630603], [-87.61646633002383, 41.80475973793773], [-87.61645839638088, 41.80443169207701], [-87.61644878457702, 41.804030528954634], [-87.61644580038985, 41.803914590028064], [-87.61644156658187, 41.80375012783846], [-87.61643122120574, 41.803483868826675], [-87.61640545455953, 41.80318628304824], [-87.61636657748137, 41.803006515619764], [-87.6163590650835, 41.80297177546721], [-87.61625552696026, 41.80267897305564], [-87.61618167023049, 41.8024149789362], [-87.61610503358958, 41.80209463506868]]]</t>
+          <t>[[[-87.58394543361024, 41.795220065764205], [-87.5835817620467, 41.795223797172596], [-87.58327948192816, 41.79522915096661], [-87.58324210928754, 41.79522947236536], [-87.5829312072739, 41.795232145317705], [-87.58253279286843, 41.79523559512813], [-87.58220685560578, 41.795238416348866], [-87.5819200476465, 41.79524101361322], [-87.58182560768654, 41.79524177247036], [-87.58163397586631, 41.79524331336056], [-87.58124686189768, 41.795246514830914], [-87.58086945340737, 41.79525705071672]]]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>55TH ST</t>
+          <t>STONY ISLAND AVE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>STONY ISLAND</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -17039,22 +17039,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>S COTTAGE GROVE AVE</t>
+          <t>E 59TH ST</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S DORCHESTER AVE</t>
+          <t>E 56TH ST</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.766203524173</t>
+          <t>0.378464121006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -17074,19 +17074,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[[[-87.60620979087955, 41.79495747442708], [-87.6057344224648, 41.79495778503282], [-87.60525201125915, 41.79496326297865], [-87.60479417557326, 41.794968318532064], [-87.60416578190858, 41.79497613248727], [-87.60382968914276, 41.79497974562034], [-87.60364258908545, 41.79498175626839], [-87.6031618006071, 41.79498638580917], [-87.60258003192963, 41.79499286770068], [-87.60201296951952, 41.794999330425995], [-87.60176485131475, 41.79500208669209], [-87.60130428020985, 41.79500683720651], [-87.60083389016755, 41.795011687128714], [-87.60050008922202, 41.79501581473183], [-87.6002440069741, 41.79501912014317], [-87.59977157954289, 41.79502367900555], [-87.59944937777256, 41.79502678009304], [-87.5991151755601, 41.795030737243415], [-87.59876610668249, 41.79503599750648], [-87.59846421388181, 41.795039746997446], [-87.59809252263335, 41.79504284460396], [-87.59783639943313, 41.79504497752776], [-87.59764672479376, 41.79504746882311], [-87.59746279967632, 41.79504988499188], [-87.59729500945298, 41.795051197774896], [-87.59714467615815, 41.79505237459098], [-87.59712751034556, 41.79505261932045], [-87.59653845570257, 41.79505834324881], [-87.59587785724203, 41.79506631315715], [-87.59585440739944, 41.795062984370915], [-87.59491762743127, 41.79507687701188], [-87.59334179382368, 41.795100230834926], [-87.59230182841584, 41.795115630665705], [-87.592302990093, 41.795150774423014], [-87.59230046172085, 41.795201582121706], [-87.59228243740286, 41.795250862799094], [-87.59224146498102, 41.795340996591], [-87.59222898325629, 41.79535145199423], [-87.59207943860847, 41.79544011543386], [-87.5920123125014, 41.79546698816598], [-87.59190924617853, 41.795490664939614], [-87.59181796862944, 41.7955002290602], [-87.59168916179809, 41.795501250471744]]]</t>
+          <t>[[[-87.58662892252528, 41.78789358129685], [-87.586706089987, 41.79153912486357], [-87.58663186923798, 41.79337593873825]]]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DREXEL BLVD</t>
+          <t>63RD ST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DREXEL</t>
+          <t>63RD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -17096,22 +17096,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>E HYDE PARK BLVD</t>
+          <t>S MARYLAND AVE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>E OAKWOOD BLVD</t>
+          <t>S STONY ISLAND AVE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.44027790321</t>
+          <t>0.939759213128</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -17131,54 +17131,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[[[-87.6061357829986, 41.82285126887031], [-87.60609798571573, 41.82276399646166], [-87.60590091255791, 41.82238247366579], [-87.60556669332729, 41.8218485016191], [-87.60530502182334, 41.82143367779866], [-87.60503607482781, 41.82100731247258], [-87.6048651023532, 41.820736412610586], [-87.60468547053425, 41.82045272301633], [-87.60449083328942, 41.820146654278034], [-87.6044256482468, 41.820039488053965], [-87.60440298975179, 41.8199636312076], [-87.60436493891923, 41.819611683642336], [-87.60429991730739, 41.819055419679465], [-87.60429380433658, 41.81900362340333], [-87.60426189555417, 41.8187247681738], [-87.60423424833219, 41.81848098336986], [-87.60420878995686, 41.81825126419623], [-87.60417455131629, 41.817968413673675], [-87.60415552556421, 41.81781123864321], [-87.60413394449134, 41.81761153828346], [-87.60411028125793, 41.81739508449601], [-87.6040885112337, 41.8171992256062], [-87.6040700938691, 41.81703439693089], [-87.60405800489534, 41.81683774595473], [-87.60404268597567, 41.816588553468314], [-87.60403709666593, 41.81630849303128], [-87.60403120520014, 41.8160161354863], [-87.60402385839835, 41.81570661792346], [-87.6040170517352, 41.81545621443974], [-87.60400794890579, 41.81501570099713], [-87.60400263005133, 41.814758282399495], [-87.6039971166536, 41.8145069813334], [-87.60399159427311, 41.81425010973378], [-87.60398593909036, 41.81399836927459], [-87.60398044110272, 41.813765236437085], [-87.60397499985255, 41.81352699896516], [-87.60396816319397, 41.813199599950835], [-87.60396389986742, 41.8129954454885], [-87.60395896340789, 41.81276777679964], [-87.60395507075744, 41.812587068895915], [-87.60395103323813, 41.81239971908291], [-87.60394749744123, 41.81224261431615], [-87.60394634625938, 41.812192497109486], [-87.60394481883999, 41.812126322466376], [-87.60393970922209, 41.8119040592473], [-87.60393553325102, 41.81172255360749], [-87.60392887286369, 41.811376458031624], [-87.60392551762324, 41.81120206585357], [-87.6039220751111, 41.811026987049004], [-87.60391755623571, 41.81080453486339], [-87.60391271281719, 41.810565396211956], [-87.60390920747359, 41.810395859547214], [-87.60390545674095, 41.810224510714114], [-87.6039029260037, 41.810108878818895], [-87.60389805780825, 41.80989781291501], [-87.60389154426316, 41.80955704103505], [-87.60388737756344, 41.80933909368288], [-87.6038839679615, 41.80921055686321], [-87.60387961854272, 41.80904658706937], [-87.60387371153965, 41.80877837916568], [-87.60386741299754, 41.80847998089812], [-87.60386217213637, 41.80822741989517], [-87.60385829065206, 41.80802316594071], [-87.60385239269901, 41.80773868420216], [-87.60384783613233, 41.80751883906607], [-87.60384274399121, 41.807243419051346], [-87.60383646805631, 41.80693986273583], [-87.60383088501047, 41.80664640914328], [-87.6038268275711, 41.80644791716319], [-87.60381920996646, 41.8061785179137], [-87.60381478491121, 41.80591612025036], [-87.60381184231792, 41.80574166480126], [-87.60380626616268, 41.80551868439242], [-87.60380179621455, 41.80533089313059], [-87.60379613662855, 41.80512799991602], [-87.60379079943327, 41.80490019151557], [-87.6037865313686, 41.80469439808748], [-87.6037805331614, 41.80445368703591], [-87.60377677465617, 41.804267683853766], [-87.60377404877609, 41.80410075937107], [-87.60377006455334, 41.80385690535313], [-87.60376813499602, 41.80374251152941], [-87.60376478430065, 41.80361114875377], [-87.60375648729162, 41.803366141884204], [-87.60375141035728, 41.80319294589922], [-87.60374820447251, 41.803022835593254], [-87.60374626819105, 41.80289938597228], [-87.60374406398431, 41.80276709679405], [-87.603741005496, 41.802597042333126], [-87.60377786306702, 41.802278554577875]]]</t>
+          <t>[[[-87.6046422414081, 41.78042037203421], [-87.58645234642981, 41.78061152172805]]]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MARTIN LUTHER KING JR DR</t>
+          <t>55TH PL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MARTIN LUTHER KING JR</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>E GARFIELD BLVD</t>
+          <t>S DORCHESTER AVE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>E 51ST ST</t>
+          <t>E 55TH ST</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.525487613949</t>
+          <t>0.140520676257</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2W</t>
+          <t>1W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -17188,19 +17188,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[[[-87.61610503358958, 41.80209463506868], [-87.6161372553474, 41.80190169269912], [-87.61614074146709, 41.80158907436339], [-87.61612777562215, 41.80089368105505], [-87.61611061011892, 41.80022228554601], [-87.6161072447521, 41.80009063210527], [-87.61609367670414, 41.799567542526496], [-87.61608066594823, 41.799007655365806], [-87.61607252526402, 41.798655650381], [-87.61607043851457, 41.798547458174994], [-87.6160678890834, 41.798457127876596], [-87.61605837110685, 41.79805028367454], [-87.61604192712679, 41.79739045646684], [-87.6160235286314, 41.79670545121182], [-87.61602194699849, 41.79663990734271], [-87.61601550198797, 41.7963728214937], [-87.61599616418324, 41.79563948379497], [-87.61599287316523, 41.795514680599055], [-87.61597940877292, 41.795011981545464], [-87.6159753641248, 41.794792923748744], [-87.6159725954511, 41.7946429706259], [-87.61596722873355, 41.79447924837816]]]</t>
+          <t>[[[-87.59168916179809, 41.795501250471744], [-87.59156420785152, 41.79550224079574], [-87.59131454042925, 41.79550235705856], [-87.59109786212012, 41.79550386629565], [-87.59085770346485, 41.79550615703121], [-87.59063312557093, 41.79550898557082], [-87.59034113508434, 41.79551248331219], [-87.59008263205658, 41.79551557934015], [-87.58986476270361, 41.79551853261422], [-87.58969927989575, 41.795519959075364], [-87.58959813856721, 41.79551348622447], [-87.58949753203959, 41.795492500363025], [-87.58941006033334, 41.795458316572784], [-87.58930035814839, 41.79539227921674], [-87.58923659094965, 41.795287816040414], [-87.58921021181861, 41.795222275968634], [-87.58920472557244, 41.79519313923364]]]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>55TH ST</t>
+          <t>OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>OAKWOOD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -17210,22 +17210,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S HYDE PARK BLVD</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S SHORE DR</t>
+          <t>S COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marked Shared Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.158892281839</t>
+          <t>0.521985922417</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -17245,19 +17245,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[[[-87.58394543361024, 41.795220065764205], [-87.5835817620467, 41.795223797172596], [-87.58327948192816, 41.79522915096661], [-87.58324210928754, 41.79522947236536], [-87.5829312072739, 41.795232145317705], [-87.58253279286843, 41.79523559512813], [-87.58220685560578, 41.795238416348866], [-87.5819200476465, 41.79524101361322], [-87.58182560768654, 41.79524177247036], [-87.58163397586631, 41.79524331336056], [-87.58124686189768, 41.795246514830914], [-87.58086945340737, 41.79525705071672]]]</t>
+          <t>[[[-87.61695962339326, 41.82264134188429], [-87.61669629612875, 41.82264370313865], [-87.61606631519486, 41.822649350671306], [-87.61515537131041, 41.82265750964905], [-87.61417375753305, 41.822666282273154], [-87.61359604756068, 41.82267144039865], [-87.61289063246282, 41.82267242469886], [-87.6121351823511, 41.8226734740702], [-87.611723286215, 41.82267866256548], [-87.61021322833639, 41.82269767014164], [-87.60979638334024, 41.82270234788722], [-87.60820507512415, 41.82272019148444], [-87.6069221364619, 41.82272643226638], [-87.60684961994563, 41.822720681391324]]]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>31ST ST</t>
+          <t>ELLSWORTH DR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31ST</t>
+          <t>ELLSWORTH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -17267,12 +17267,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>E GARFIELD BLVD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S MOE DR</t>
+          <t>E 51ST ST</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.374564177222</t>
+          <t>0.563850072419</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -17302,19 +17302,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[[[-87.61711743673902, 41.83841544388878], [-87.61349382112748, 41.83846417399243], [-87.61336507987872, 41.8384654324603], [-87.61170778684063, 41.8384964974145], [-87.6113260948113, 41.838513422816135], [-87.61122239818451, 41.83851802083818], [-87.61106328407865, 41.83852507577069], [-87.61079286825503, 41.83852833767229], [-87.61023646107017, 41.83853504871899], [-87.61004517815752, 41.83853385151719], [-87.60986250664294, 41.83853270823932]]]</t>
+          <t>[[[-87.61610503358958, 41.80209463506868], [-87.61598017987416, 41.801936535122216], [-87.61571941210941, 41.80151328586742], [-87.61550944727176, 41.80119731531666], [-87.61539693942696, 41.80102858217285], [-87.61529932756855, 41.80088235809726], [-87.61506155892664, 41.80053756279236], [-87.614929442976, 41.80036126695795], [-87.6147326797903, 41.80020701596753], [-87.61447389984386, 41.800029817334064], [-87.61431845146083, 41.799919979246425], [-87.6141480647915, 41.79976531521329], [-87.61403399880841, 41.7996282102345], [-87.61398065771237, 41.799550981614956], [-87.61395599984449, 41.79950944339995], [-87.61391106290475, 41.79939892462118], [-87.61389464937568, 41.79934160352373], [-87.61388617434496, 41.799296050230076], [-87.61388737070605, 41.79922835661386], [-87.61389328726345, 41.79900113927943], [-87.61391381323126, 41.798644730896484], [-87.61392200607862, 41.79853402352384], [-87.61392355907101, 41.798501352248834], [-87.61392547720082, 41.798460992447886], [-87.61396071892041, 41.79813000580307], [-87.61400731520777, 41.79785924549823], [-87.6140570307326, 41.79763090320573], [-87.6141338608941, 41.79734899758503], [-87.61419534320311, 41.797160438942676], [-87.61428035246796, 41.79693075355048], [-87.61437410917135, 41.7966928071726], [-87.61439017940391, 41.79665131864515], [-87.61448490414, 41.79640677773468], [-87.61455078269736, 41.796175847853924], [-87.61459809192392, 41.79591974491938], [-87.61462586548868, 41.79561330073654], [-87.61463898952323, 41.7953906021651], [-87.6146621547144, 41.79508629626382], [-87.61469428955904, 41.7949442612965], [-87.61469972612767, 41.794814738076944], [-87.61469151426928, 41.79468057278534], [-87.61467818509446, 41.79459684387978], [-87.6146469845286, 41.79448424318099]]]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>33RD ST</t>
+          <t>MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33RD</t>
+          <t>MARTIN LUTHER KING JR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -17324,22 +17324,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S STATE ST</t>
+          <t>E 51ST ST</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>E 37TH ST</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marked Shared Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.47034639757</t>
+          <t>1.75304400525</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17359,19 +17359,19 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[[[-87.62649453439884, 41.834657620039394], [-87.6261375484813, 41.834653255468275], [-87.62598820768505, 41.834655523097894], [-87.6258713558933, 41.83465729648271], [-87.62555479911322, 41.834663112644094], [-87.62521987635559, 41.834667222892755], [-87.62505539738287, 41.834670172980104], [-87.62490108129768, 41.834672941521305], [-87.62458217233613, 41.834675666707916], [-87.62423396810284, 41.83467955437231], [-87.62419467526055, 41.83468228203092], [-87.62332410153712, 41.834694699177206], [-87.6225766889668, 41.834705354550316], [-87.62204427228347, 41.83471294207457], [-87.62183407802331, 41.834710293288616], [-87.62162465056676, 41.834707653371126], [-87.62122627094816, 41.83471231672194], [-87.62080305524594, 41.834717269393636], [-87.62061503357474, 41.834712419521736], [-87.62049200866362, 41.83470924673693], [-87.6196388712932, 41.834730650392935], [-87.61940523053126, 41.834732824088015], [-87.61923746068237, 41.8347343849626], [-87.61879845501683, 41.83473992804518], [-87.61849043146212, 41.83474381686139], [-87.61818788325031, 41.83474705287812], [-87.61738398483341, 41.83475564899769]]]</t>
+          <t>[[[-87.6170661605481, 41.82746577345483], [-87.61706142929766, 41.82722251576819], [-87.61703594211926, 41.82599621919331], [-87.6170346569476, 41.825924585756425], [-87.61702807683459, 41.825640732364505], [-87.61701815626563, 41.825212839267834], [-87.61701158986415, 41.824860489202024], [-87.61700504238831, 41.82446703021115], [-87.61699819000684, 41.82410092909017], [-87.61699111101917, 41.82382621643897], [-87.6169682780898, 41.82294010913907], [-87.61695962339326, 41.82264134188429], [-87.61694647296191, 41.82218741283243], [-87.61694134071122, 41.82200285608154], [-87.61691550518213, 41.82107381642339], [-87.61690011817095, 41.820520501742], [-87.6168912291518, 41.82022584659349], [-87.61687951834088, 41.819837625724176], [-87.61686451475447, 41.81931905960095], [-87.61685917407235, 41.819134444733976], [-87.61685486347649, 41.81903471854085], [-87.61685026940104, 41.81886108718419], [-87.61684584573, 41.818632543662474], [-87.61683899958928, 41.818426428036624], [-87.61682859667718, 41.81811322063313], [-87.61682317373558, 41.81791516029109], [-87.6168170711122, 41.81769914813044], [-87.61681204388093, 41.81752487028064], [-87.6168097679134, 41.8174459431259], [-87.61680154890371, 41.817143281582915], [-87.61680085310701, 41.81711867608355], [-87.61679454768834, 41.8168960333512], [-87.61678662778932, 41.816627119659934], [-87.61677714364522, 41.81630505574234], [-87.61677062740476, 41.81603396382891], [-87.61676552375634, 41.81582380290046], [-87.61675765682091, 41.81555209840315], [-87.61675059408309, 41.81531687029233], [-87.61674224579149, 41.815039015176694], [-87.61673544566895, 41.814814353391846], [-87.61672717933429, 41.814541247209775], [-87.61672053521322, 41.814281652787514], [-87.6167133124245, 41.814034457969235], [-87.61670518857355, 41.813756248551975], [-87.61669736056754, 41.8134778473913], [-87.61668988955066, 41.8131937690335], [-87.61668445767971, 41.813002180182174], [-87.61667472405641, 41.812658842819], [-87.616665225364, 41.812313114669124], [-87.61666403964655, 41.81227254737789], [-87.6166590672492, 41.812102152014056], [-87.61665296669604, 41.811892506022836], [-87.61664655510585, 41.811671359704654], [-87.61664207135496, 41.81149114274442], [-87.61663372407628, 41.811189079715234], [-87.61662461081087, 41.81085932970484], [-87.61662055015955, 41.81066750713534], [-87.61661158374402, 41.81035309368742], [-87.61660946369571, 41.81028007730828], [-87.61660532895206, 41.81013765741237], [-87.6165971626926, 41.809869902413276], [-87.61658969716275, 41.809631378067415], [-87.6165830260001, 41.80937622288194], [-87.61657750843742, 41.80916515967291], [-87.61657434552195, 41.80905399609861], [-87.61656977392795, 41.80889161626314], [-87.61656382612986, 41.80868147771314], [-87.6165595258573, 41.80852434140443], [-87.61655442132603, 41.80832082118215], [-87.61654832746574, 41.80807121930493], [-87.61654000442812, 41.8077846368839], [-87.61653454090984, 41.80755514196061], [-87.61652978730874, 41.80735545128697], [-87.61652116505952, 41.80702339471532], [-87.61650989769541, 41.806543569441665], [-87.6165048970603, 41.80633409577223], [-87.61649750571686, 41.805990301736024], [-87.61649069419391, 41.80573396875114], [-87.61648329413629, 41.80545551854538], [-87.6164821821902, 41.80541072451418], [-87.61647834932612, 41.8052344630603], [-87.61646633002383, 41.80475973793773], [-87.61645839638088, 41.80443169207701], [-87.61644878457702, 41.804030528954634], [-87.61644580038985, 41.803914590028064], [-87.61644156658187, 41.80375012783846], [-87.61643122120574, 41.803483868826675], [-87.61640545455953, 41.80318628304824], [-87.61636657748137, 41.803006515619764], [-87.6163590650835, 41.80297177546721], [-87.61625552696026, 41.80267897305564], [-87.61618167023049, 41.8024149789362], [-87.61610503358958, 41.80209463506868]]]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OAKWOOD BLVD</t>
+          <t>55TH ST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OAKWOOD</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -17386,17 +17386,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>E PERSHING RD</t>
+          <t>S DORCHESTER AVE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.179532699715</t>
+          <t>0.766203524173</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17416,19 +17416,19 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[[[-87.60684961994563, 41.822720681391324], [-87.60679180817826, 41.82272115395717], [-87.60677001340125, 41.82272103500519], [-87.60674821900858, 41.82272120146208], [-87.60672643224186, 41.822721651572905], [-87.60670465910856, 41.822722386276055], [-87.60668290562634, 41.822723405609615], [-87.60666118024034, 41.82272470782627], [-87.60663948895807, 41.82272629386447], [-87.60661783660379, 41.82272816285434], [-87.60659623160228, 41.822730314849224], [-87.60657467999161, 41.822732748086665], [-87.60655318900317, 41.82273546171211], [-87.60653176465463, 41.82273845576364], [-87.60651041297386, 41.822741729379096], [-87.6064891412025, 41.82274528080366], [-87.60646795535817, 41.82274911007541], [-87.60644686148913, 41.82275321453169], [-87.60642586802022, 41.8227575942258], [-87.60640497858236, 41.82276224738011], [-87.60638420162077, 41.82276717224742], [-87.6063635431735, 41.82277236706532], [-87.60634300805471, 41.82277783186432], [-87.60632260352641, 41.82278356308904], [-87.60630233682008, 41.822789559885024], [-87.60628221277028, 41.82279582048222], [-87.60626223741507, 41.82280234311821], [-87.6062424168028, 41.822809125130334], [-87.60622275817514, 41.8228161647638], [-87.60620326757022, 41.822823460256195], [-87.60618394862924, 41.82283100892967], [-87.6061357829986, 41.82285126887031], [-87.60489865036251, 41.82326907790459], [-87.60488618404133, 41.823273092730936], [-87.60487521949304, 41.823276932508655], [-87.60486278852834, 41.823281650728966], [-87.60484930661205, 41.82328723021869], [-87.60483704714119, 41.823292747232735], [-87.6048271855152, 41.82329751145608], [-87.6048184078212, 41.8233020088474], [-87.60481037940755, 41.823306348027266], [-87.60480191461397, 41.82331116882633], [-87.60479333766806, 41.82331632654415], [-87.6047855007208, 41.823321295379984], [-87.6047572327323, 41.823341526083084], [-87.60471652058943, 41.82336869605984], [-87.60470052458207, 41.823382623822745], [-87.60468485482315, 41.82339675893244], [-87.60466951859557, 41.82341109603318], [-87.60465451835765, 41.823425630638965], [-87.6046398601683, 41.82344035918691], [-87.60462554648588, 41.82345527719107], [-87.60461158337955, 41.82347038018828], [-87.60459797573527, 41.82348566190726], [-87.60458472599103, 41.823501119662524], [-87.60457183902265, 41.82351674808307], [-87.60455931849212, 41.82353254269051], [-87.6045471692855, 41.82354849721349], [-87.60453539263716, 41.823564608958954], [-87.60452399584045, 41.823580871670806], [-87.60451297774297, 41.82359728084015], [-87.60450234562784, 41.82361383111117], [-87.60449210196373, 41.8236305170976], [-87.60448224799534, 41.823647335206], [-87.60447278860879, 41.823664279165065], [-87.60446372506924, 41.823681343580795], [-87.60445506224238, 41.82369852398245], [-87.6044468013934, 41.823715814976026], [-87.6044389437976, 41.82373321026731], [-87.60443149431059, 41.82375070628574], [-87.60442445419751, 41.823768297637386], [-87.6044178259476, 41.823785977135316], [-87.6044116108056, 41.823803741186076], [-87.60440581126073, 41.82382158260278], [-87.60440042855778, 41.823839497791994], [-87.60439546517577, 41.82385748046702], [-87.60439092117632, 41.823875525226285], [-87.60438680023185, 41.823893626690996], [-87.60438310121057, 41.82391177855161], [-87.60437982657116, 41.82392997632201], [-87.60437697757878, 41.82394821460817], [-87.60437455311194, 41.82396648620023], [-87.60437255682261, 41.82398478752], [-87.60437098758929, 41.824003111357584], [-87.60436926671751, 41.82403533381279], [-87.60435230548126, 41.82416287487605]]]</t>
+          <t>[[[-87.60620979087955, 41.79495747442708], [-87.6057344224648, 41.79495778503282], [-87.60525201125915, 41.79496326297865], [-87.60479417557326, 41.794968318532064], [-87.60416578190858, 41.79497613248727], [-87.60382968914276, 41.79497974562034], [-87.60364258908545, 41.79498175626839], [-87.6031618006071, 41.79498638580917], [-87.60258003192963, 41.79499286770068], [-87.60201296951952, 41.794999330425995], [-87.60176485131475, 41.79500208669209], [-87.60130428020985, 41.79500683720651], [-87.60083389016755, 41.795011687128714], [-87.60050008922202, 41.79501581473183], [-87.6002440069741, 41.79501912014317], [-87.59977157954289, 41.79502367900555], [-87.59944937777256, 41.79502678009304], [-87.5991151755601, 41.795030737243415], [-87.59876610668249, 41.79503599750648], [-87.59846421388181, 41.795039746997446], [-87.59809252263335, 41.79504284460396], [-87.59783639943313, 41.79504497752776], [-87.59764672479376, 41.79504746882311], [-87.59746279967632, 41.79504988499188], [-87.59729500945298, 41.795051197774896], [-87.59714467615815, 41.79505237459098], [-87.59712751034556, 41.79505261932045], [-87.59653845570257, 41.79505834324881], [-87.59587785724203, 41.79506631315715], [-87.59585440739944, 41.795062984370915], [-87.59491762743127, 41.79507687701188], [-87.59334179382368, 41.795100230834926], [-87.59230182841584, 41.795115630665705], [-87.592302990093, 41.795150774423014], [-87.59230046172085, 41.795201582121706], [-87.59228243740286, 41.795250862799094], [-87.59224146498102, 41.795340996591], [-87.59222898325629, 41.79535145199423], [-87.59207943860847, 41.79544011543386], [-87.5920123125014, 41.79546698816598], [-87.59190924617853, 41.795490664939614], [-87.59181796862944, 41.7955002290602], [-87.59168916179809, 41.795501250471744]]]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COTTAGE GROVE AVE</t>
+          <t>DREXEL BLVD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COTTAGE GROVE</t>
+          <t>DREXEL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -17438,22 +17438,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>E PERSHING RD</t>
+          <t>E HYDE PARK BLVD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>E 35TH ST</t>
+          <t>E OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.535169697043</t>
+          <t>1.44027790321</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -17473,19 +17473,19 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[[[-87.61062764640718, 41.83117833227938], [-87.61056121164148, 41.8309831537708], [-87.61049735143008, 41.83088969918398], [-87.61035664310229, 41.830683783743886], [-87.61021807070779, 41.83042154772161], [-87.60976457816737, 41.82954607123712], [-87.60957313929535, 41.82921206775326], [-87.60953484063897, 41.829123898452686], [-87.60947872228488, 41.82899470323354], [-87.60920191148996, 41.828461613639654], [-87.60903435707688, 41.82813505890052], [-87.60893989467102, 41.82795095517259], [-87.60881964632634, 41.82771437489353], [-87.60875245248874, 41.82758217879819], [-87.60848246060718, 41.827057116463294], [-87.60835626491398, 41.82681471429994], [-87.6082719086208, 41.82665265487381], [-87.60807609502977, 41.82626881297509], [-87.60797191429859, 41.82606348435161], [-87.6079087205916, 41.82593893804116], [-87.60784009873232, 41.82580134557496], [-87.60760573951933, 41.82534195692333], [-87.60750781352307, 41.825147209548874], [-87.6073738248817, 41.824880744701375], [-87.60728073042753, 41.82469689396191], [-87.6071500174633, 41.824439506146774], [-87.60686734794898, 41.8239569091955]]]</t>
+          <t>[[[-87.6061357829986, 41.82285126887031], [-87.60609798571573, 41.82276399646166], [-87.60590091255791, 41.82238247366579], [-87.60556669332729, 41.8218485016191], [-87.60530502182334, 41.82143367779866], [-87.60503607482781, 41.82100731247258], [-87.6048651023532, 41.820736412610586], [-87.60468547053425, 41.82045272301633], [-87.60449083328942, 41.820146654278034], [-87.6044256482468, 41.820039488053965], [-87.60440298975179, 41.8199636312076], [-87.60436493891923, 41.819611683642336], [-87.60429991730739, 41.819055419679465], [-87.60429380433658, 41.81900362340333], [-87.60426189555417, 41.8187247681738], [-87.60423424833219, 41.81848098336986], [-87.60420878995686, 41.81825126419623], [-87.60417455131629, 41.817968413673675], [-87.60415552556421, 41.81781123864321], [-87.60413394449134, 41.81761153828346], [-87.60411028125793, 41.81739508449601], [-87.6040885112337, 41.8171992256062], [-87.6040700938691, 41.81703439693089], [-87.60405800489534, 41.81683774595473], [-87.60404268597567, 41.816588553468314], [-87.60403709666593, 41.81630849303128], [-87.60403120520014, 41.8160161354863], [-87.60402385839835, 41.81570661792346], [-87.6040170517352, 41.81545621443974], [-87.60400794890579, 41.81501570099713], [-87.60400263005133, 41.814758282399495], [-87.6039971166536, 41.8145069813334], [-87.60399159427311, 41.81425010973378], [-87.60398593909036, 41.81399836927459], [-87.60398044110272, 41.813765236437085], [-87.60397499985255, 41.81352699896516], [-87.60396816319397, 41.813199599950835], [-87.60396389986742, 41.8129954454885], [-87.60395896340789, 41.81276777679964], [-87.60395507075744, 41.812587068895915], [-87.60395103323813, 41.81239971908291], [-87.60394749744123, 41.81224261431615], [-87.60394634625938, 41.812192497109486], [-87.60394481883999, 41.812126322466376], [-87.60393970922209, 41.8119040592473], [-87.60393553325102, 41.81172255360749], [-87.60392887286369, 41.811376458031624], [-87.60392551762324, 41.81120206585357], [-87.6039220751111, 41.811026987049004], [-87.60391755623571, 41.81080453486339], [-87.60391271281719, 41.810565396211956], [-87.60390920747359, 41.810395859547214], [-87.60390545674095, 41.810224510714114], [-87.6039029260037, 41.810108878818895], [-87.60389805780825, 41.80989781291501], [-87.60389154426316, 41.80955704103505], [-87.60388737756344, 41.80933909368288], [-87.6038839679615, 41.80921055686321], [-87.60387961854272, 41.80904658706937], [-87.60387371153965, 41.80877837916568], [-87.60386741299754, 41.80847998089812], [-87.60386217213637, 41.80822741989517], [-87.60385829065206, 41.80802316594071], [-87.60385239269901, 41.80773868420216], [-87.60384783613233, 41.80751883906607], [-87.60384274399121, 41.807243419051346], [-87.60383646805631, 41.80693986273583], [-87.60383088501047, 41.80664640914328], [-87.6038268275711, 41.80644791716319], [-87.60381920996646, 41.8061785179137], [-87.60381478491121, 41.80591612025036], [-87.60381184231792, 41.80574166480126], [-87.60380626616268, 41.80551868439242], [-87.60380179621455, 41.80533089313059], [-87.60379613662855, 41.80512799991602], [-87.60379079943327, 41.80490019151557], [-87.6037865313686, 41.80469439808748], [-87.6037805331614, 41.80445368703591], [-87.60377677465617, 41.804267683853766], [-87.60377404877609, 41.80410075937107], [-87.60377006455334, 41.80385690535313], [-87.60376813499602, 41.80374251152941], [-87.60376478430065, 41.80361114875377], [-87.60375648729162, 41.803366141884204], [-87.60375141035728, 41.80319294589922], [-87.60374820447251, 41.803022835593254], [-87.60374626819105, 41.80289938597228], [-87.60374406398431, 41.80276709679405], [-87.603741005496, 41.802597042333126], [-87.60377786306702, 41.802278554577875]]]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31ST DR</t>
+          <t>MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31ST</t>
+          <t>MARTIN LUTHER KING JR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -17495,22 +17495,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>S MOE DR</t>
+          <t>E GARFIELD BLVD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S FORT DEARBORN</t>
+          <t>E 51ST ST</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.112279352219</t>
+          <t>0.525487613949</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -17530,19 +17530,19 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[[[-87.60986250664294, 41.83853270823932], [-87.6095086258396, 41.83853049214663], [-87.60918890021458, 41.83853812491465], [-87.60875811449299, 41.83854840731297], [-87.60865431875239, 41.83855088477592], [-87.60833750976242, 41.838558445341555], [-87.60824493561356, 41.83856065473611], [-87.60779764356145, 41.83857132811791], [-87.60768798164275, 41.83857394411922]]]</t>
+          <t>[[[-87.61610503358958, 41.80209463506868], [-87.6161372553474, 41.80190169269912], [-87.61614074146709, 41.80158907436339], [-87.61612777562215, 41.80089368105505], [-87.61611061011892, 41.80022228554601], [-87.6161072447521, 41.80009063210527], [-87.61609367670414, 41.799567542526496], [-87.61608066594823, 41.799007655365806], [-87.61607252526402, 41.798655650381], [-87.61607043851457, 41.798547458174994], [-87.6160678890834, 41.798457127876596], [-87.61605837110685, 41.79805028367454], [-87.61604192712679, 41.79739045646684], [-87.6160235286314, 41.79670545121182], [-87.61602194699849, 41.79663990734271], [-87.61601550198797, 41.7963728214937], [-87.61599616418324, 41.79563948379497], [-87.61599287316523, 41.795514680599055], [-87.61597940877292, 41.795011981545464], [-87.6159753641248, 41.794792923748744], [-87.6159725954511, 41.7946429706259], [-87.61596722873355, 41.79447924837816]]]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OAKWOOD BLVD</t>
+          <t>31ST ST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OAKWOOD</t>
+          <t>31ST</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -17552,22 +17552,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>E PERSHING RD</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LAKESHORE DR</t>
+          <t>S MOE DR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.265190300727</t>
+          <t>0.374564177222</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -17587,19 +17587,19 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>[[[-87.60435230548126, 41.82416287487605], [-87.60430631831143, 41.82416402356607], [-87.60428716161914, 41.824162095879494], [-87.60426796236939, 41.824160418216486], [-87.60424872656984, 41.824158991515496], [-87.6042294614419, 41.82415781582236], [-87.60421017058603, 41.824156892060216], [-87.60419086242726, 41.824156220282596], [-87.60417154057622, 41.82415580051237], [-87.60415221225436, 41.824155632795396], [-87.60413288226572, 41.82415571806249], [-87.60411355904553, 41.824156055466894], [-87.60409424500084, 41.824156645023855], [-87.60407494855669, 41.82415748678687], [-87.60405567333392, 41.82415857987863], [-87.60403642775758, 41.82415992435258], [-87.60401721664196, 41.82416152023936], [-87.60399804481145, 41.82416336666922], [-87.60397216606508, 41.82416626443172], [-87.60346372774372, 41.82428645007398], [-87.60283279718537, 41.82449961768677], [-87.60254227296632, 41.82459826474106], [-87.60246449645898, 41.82463065780316], [-87.60214041957721, 41.82476563187484], [-87.6020952755735, 41.8247849900892], [-87.6017964676506, 41.824913114836825], [-87.60160828555927, 41.824988222508935], [-87.60150680968545, 41.82502872373627], [-87.60091462496219, 41.825188150840695], [-87.60074975423764, 41.82519086558529], [-87.60046891563478, 41.82526537949098], [-87.60036960542857, 41.82529172834911], [-87.60027660609322, 41.82531640313449], [-87.59999145364394, 41.825392060591405], [-87.59984691458156, 41.8254304090753], [-87.5996240077739, 41.825489550046555], [-87.5995963400068, 41.82550927640572]]]</t>
+          <t>[[[-87.61711743673902, 41.83841544388878], [-87.61349382112748, 41.83846417399243], [-87.61336507987872, 41.8384654324603], [-87.61170778684063, 41.8384964974145], [-87.6113260948113, 41.838513422816135], [-87.61122239818451, 41.83851802083818], [-87.61106328407865, 41.83852507577069], [-87.61079286825503, 41.83852833767229], [-87.61023646107017, 41.83853504871899], [-87.61004517815752, 41.83853385151719], [-87.60986250664294, 41.83853270823932]]]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>31ST ST</t>
+          <t>33RD ST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31ST</t>
+          <t>33RD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -17609,22 +17609,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>S MICHIGAN AVE</t>
+          <t>S STATE ST</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S GILES AVE</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Marked Shared Lane</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.204433765585</t>
+          <t>0.47034639757</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -17644,19 +17644,19 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[[[-87.62343694336933, 41.83833704540958], [-87.62323358361407, 41.83833847406264], [-87.6219191008301, 41.838356765893344], [-87.62177979242179, 41.83835870302541], [-87.62128211303167, 41.83836481491048], [-87.62100750971918, 41.8383681865488], [-87.62063024755903, 41.83837298145963], [-87.62047048387781, 41.83837500885838], [-87.62015738391769, 41.83837922174425], [-87.61999021695806, 41.83838147080919], [-87.61947655373596, 41.838387441384285]]]</t>
+          <t>[[[-87.62649453439884, 41.834657620039394], [-87.6261375484813, 41.834653255468275], [-87.62598820768505, 41.834655523097894], [-87.6258713558933, 41.83465729648271], [-87.62555479911322, 41.834663112644094], [-87.62521987635559, 41.834667222892755], [-87.62505539738287, 41.834670172980104], [-87.62490108129768, 41.834672941521305], [-87.62458217233613, 41.834675666707916], [-87.62423396810284, 41.83467955437231], [-87.62419467526055, 41.83468228203092], [-87.62332410153712, 41.834694699177206], [-87.6225766889668, 41.834705354550316], [-87.62204427228347, 41.83471294207457], [-87.62183407802331, 41.834710293288616], [-87.62162465056676, 41.834707653371126], [-87.62122627094816, 41.83471231672194], [-87.62080305524594, 41.834717269393636], [-87.62061503357474, 41.834712419521736], [-87.62049200866362, 41.83470924673693], [-87.6196388712932, 41.834730650392935], [-87.61940523053126, 41.834732824088015], [-87.61923746068237, 41.8347343849626], [-87.61879845501683, 41.83473992804518], [-87.61849043146212, 41.83474381686139], [-87.61818788325031, 41.83474705287812], [-87.61738398483341, 41.83475564899769]]]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>35TH ST</t>
+          <t>OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>35TH</t>
+          <t>OAKWOOD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -17666,12 +17666,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>S INDIANA AVE</t>
+          <t>S COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>E PERSHING RD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.247640012693</t>
+          <t>0.179532699715</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -17701,19 +17701,19 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[[[-87.62175790723948, 41.83105114677236], [-87.62147204346718, 41.83105439399251], [-87.62114680081156, 41.83105756560645], [-87.62071506301695, 41.83106177458682], [-87.62054500801808, 41.83106270827247], [-87.62038410991939, 41.83106359050268], [-87.61993842551381, 41.831068138560155], [-87.61959497831648, 41.83107164288365], [-87.61932790430228, 41.83107429835225], [-87.6192145415096, 41.83107542490796], [-87.61861331357758, 41.831080192721124], [-87.61840049624368, 41.8310834879503], [-87.61811354507196, 41.8310879292089], [-87.61794575632707, 41.83109052619566], [-87.61760482133919, 41.83109575717714], [-87.61730766754923, 41.83109415363711], [-87.61696083107093, 41.83109228088914]]]</t>
+          <t>[[[-87.60684961994563, 41.822720681391324], [-87.60679180817826, 41.82272115395717], [-87.60677001340125, 41.82272103500519], [-87.60674821900858, 41.82272120146208], [-87.60672643224186, 41.822721651572905], [-87.60670465910856, 41.822722386276055], [-87.60668290562634, 41.822723405609615], [-87.60666118024034, 41.82272470782627], [-87.60663948895807, 41.82272629386447], [-87.60661783660379, 41.82272816285434], [-87.60659623160228, 41.822730314849224], [-87.60657467999161, 41.822732748086665], [-87.60655318900317, 41.82273546171211], [-87.60653176465463, 41.82273845576364], [-87.60651041297386, 41.822741729379096], [-87.6064891412025, 41.82274528080366], [-87.60646795535817, 41.82274911007541], [-87.60644686148913, 41.82275321453169], [-87.60642586802022, 41.8227575942258], [-87.60640497858236, 41.82276224738011], [-87.60638420162077, 41.82276717224742], [-87.6063635431735, 41.82277236706532], [-87.60634300805471, 41.82277783186432], [-87.60632260352641, 41.82278356308904], [-87.60630233682008, 41.822789559885024], [-87.60628221277028, 41.82279582048222], [-87.60626223741507, 41.82280234311821], [-87.6062424168028, 41.822809125130334], [-87.60622275817514, 41.8228161647638], [-87.60620326757022, 41.822823460256195], [-87.60618394862924, 41.82283100892967], [-87.6061357829986, 41.82285126887031], [-87.60489865036251, 41.82326907790459], [-87.60488618404133, 41.823273092730936], [-87.60487521949304, 41.823276932508655], [-87.60486278852834, 41.823281650728966], [-87.60484930661205, 41.82328723021869], [-87.60483704714119, 41.823292747232735], [-87.6048271855152, 41.82329751145608], [-87.6048184078212, 41.8233020088474], [-87.60481037940755, 41.823306348027266], [-87.60480191461397, 41.82331116882633], [-87.60479333766806, 41.82331632654415], [-87.6047855007208, 41.823321295379984], [-87.6047572327323, 41.823341526083084], [-87.60471652058943, 41.82336869605984], [-87.60470052458207, 41.823382623822745], [-87.60468485482315, 41.82339675893244], [-87.60466951859557, 41.82341109603318], [-87.60465451835765, 41.823425630638965], [-87.6046398601683, 41.82344035918691], [-87.60462554648588, 41.82345527719107], [-87.60461158337955, 41.82347038018828], [-87.60459797573527, 41.82348566190726], [-87.60458472599103, 41.823501119662524], [-87.60457183902265, 41.82351674808307], [-87.60455931849212, 41.82353254269051], [-87.6045471692855, 41.82354849721349], [-87.60453539263716, 41.823564608958954], [-87.60452399584045, 41.823580871670806], [-87.60451297774297, 41.82359728084015], [-87.60450234562784, 41.82361383111117], [-87.60449210196373, 41.8236305170976], [-87.60448224799534, 41.823647335206], [-87.60447278860879, 41.823664279165065], [-87.60446372506924, 41.823681343580795], [-87.60445506224238, 41.82369852398245], [-87.6044468013934, 41.823715814976026], [-87.6044389437976, 41.82373321026731], [-87.60443149431059, 41.82375070628574], [-87.60442445419751, 41.823768297637386], [-87.6044178259476, 41.823785977135316], [-87.6044116108056, 41.823803741186076], [-87.60440581126073, 41.82382158260278], [-87.60440042855778, 41.823839497791994], [-87.60439546517577, 41.82385748046702], [-87.60439092117632, 41.823875525226285], [-87.60438680023185, 41.823893626690996], [-87.60438310121057, 41.82391177855161], [-87.60437982657116, 41.82392997632201], [-87.60437697757878, 41.82394821460817], [-87.60437455311194, 41.82396648620023], [-87.60437255682261, 41.82398478752], [-87.60437098758929, 41.824003111357584], [-87.60436926671751, 41.82403533381279], [-87.60435230548126, 41.82416287487605]]]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>35TH ST</t>
+          <t>COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>35TH</t>
+          <t>COTTAGE GROVE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -17723,22 +17723,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>S STATE ST</t>
+          <t>E PERSHING RD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S INDIANA AVE</t>
+          <t>E 35TH ST</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Marked Shared Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.251982034456</t>
+          <t>0.535169697043</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -17758,19 +17758,19 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[[[-87.6266385987239, 41.83100580881331], [-87.6264732958851, 41.83101107967687], [-87.62623318245583, 41.83101873668085], [-87.62601026219642, 41.831016431371204], [-87.62591536563151, 41.83101335928809], [-87.62580089456586, 41.83100965335254], [-87.62578894519758, 41.8310097769209], [-87.62528748091881, 41.83101497359384], [-87.62497040535462, 41.83101825860181], [-87.62460523369673, 41.83102204008217], [-87.62425145860854, 41.831023753331884], [-87.62423505388152, 41.83102409322796], [-87.62325146933688, 41.831035886002816], [-87.623068985482, 41.831038072800894], [-87.62257009356864, 41.831042925980455], [-87.62249985576759, 41.831043609555515], [-87.62195505561091, 41.831048907025604], [-87.62175790723948, 41.83105114677236]]]</t>
+          <t>[[[-87.61062764640718, 41.83117833227938], [-87.61056121164148, 41.8309831537708], [-87.61049735143008, 41.83088969918398], [-87.61035664310229, 41.830683783743886], [-87.61021807070779, 41.83042154772161], [-87.60976457816737, 41.82954607123712], [-87.60957313929535, 41.82921206775326], [-87.60953484063897, 41.829123898452686], [-87.60947872228488, 41.82899470323354], [-87.60920191148996, 41.828461613639654], [-87.60903435707688, 41.82813505890052], [-87.60893989467102, 41.82795095517259], [-87.60881964632634, 41.82771437489353], [-87.60875245248874, 41.82758217879819], [-87.60848246060718, 41.827057116463294], [-87.60835626491398, 41.82681471429994], [-87.6082719086208, 41.82665265487381], [-87.60807609502977, 41.82626881297509], [-87.60797191429859, 41.82606348435161], [-87.6079087205916, 41.82593893804116], [-87.60784009873232, 41.82580134557496], [-87.60760573951933, 41.82534195692333], [-87.60750781352307, 41.825147209548874], [-87.6073738248817, 41.824880744701375], [-87.60728073042753, 41.82469689396191], [-87.6071500174633, 41.824439506146774], [-87.60686734794898, 41.8239569091955]]]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PERSHING RD</t>
+          <t>31ST DR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PERSHING</t>
+          <t>31ST</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -17780,22 +17780,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>S MARTIN LUTHER KING JR DR</t>
+          <t>S MOE DR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S COTTAGE GROVE AVE</t>
+          <t>S FORT DEARBORN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.52273584865</t>
+          <t>0.112279352219</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -17815,19 +17815,19 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>[[[-87.61699111101917, 41.82382621643897], [-87.61672658426848, 41.823830247623874], [-87.61611742079225, 41.823839530348515], [-87.61610351380473, 41.8238397010112], [-87.6154691158385, 41.82384748030514], [-87.61514202830347, 41.82385149048068], [-87.61435832379438, 41.82386109676443], [-87.61307015328607, 41.82387688472249], [-87.61261856025574, 41.82388291330555], [-87.61213034165046, 41.82388942863265], [-87.61127647198559, 41.82389814834697], [-87.61055372981066, 41.82390552337138], [-87.60983565600785, 41.82391284582243], [-87.60958135685671, 41.82391543849396], [-87.6083907741053, 41.82392832878097], [-87.60833202655425, 41.82392896457945], [-87.60732163043673, 41.82394102449633], [-87.60702288161544, 41.823950057947265], [-87.60691033374472, 41.82395217241693], [-87.60686734794898, 41.8239569091955]]]</t>
+          <t>[[[-87.60986250664294, 41.83853270823932], [-87.6095086258396, 41.83853049214663], [-87.60918890021458, 41.83853812491465], [-87.60875811449299, 41.83854840731297], [-87.60865431875239, 41.83855088477592], [-87.60833750976242, 41.838558445341555], [-87.60824493561356, 41.83856065473611], [-87.60779764356145, 41.83857132811791], [-87.60768798164275, 41.83857394411922]]]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PERSHING RD</t>
+          <t>OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PERSHING</t>
+          <t>OAKWOOD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -17837,12 +17837,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>S COTTAGE GROVE AVE</t>
+          <t>E PERSHING RD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>E OAKWOOD BLVD</t>
+          <t>LAKESHORE DR</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.135533728291</t>
+          <t>0.265190300727</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[[[-87.60686734794898, 41.8239569091955], [-87.60606651814183, 41.82417374136248], [-87.60576295911753, 41.82426465478336], [-87.60574292254485, 41.82427037292759], [-87.60572275653709, 41.824275828247], [-87.60570246591914, 41.82428101987172], [-87.60568205673985, 41.82428594513898], [-87.60566153743501, 41.824290603201796], [-87.60564091042225, 41.82429499317505], [-87.60562018535114, 41.824299113319164], [-87.60559936705677, 41.82430296186401], [-87.6055784615575, 41.824306538847644], [-87.60555747730946, 41.8243098416226], [-87.60553641792379, 41.8243128702117], [-87.60551529184642, 41.824315622867694], [-87.6054675496305, 41.82432080616751], [-87.60514959326278, 41.82431298815248], [-87.60506702606838, 41.82430186758017], [-87.60498473109828, 41.8242896709576], [-87.60490273359159, 41.824276402046785], [-87.60482105759388, 41.82426206370194], [-87.60473921548223, 41.8242465609951], [-87.6045999908213, 41.824210864913994], [-87.60435230548126, 41.82416287487605]]]</t>
+          <t>[[[-87.60435230548126, 41.82416287487605], [-87.60430631831143, 41.82416402356607], [-87.60428716161914, 41.824162095879494], [-87.60426796236939, 41.824160418216486], [-87.60424872656984, 41.824158991515496], [-87.6042294614419, 41.82415781582236], [-87.60421017058603, 41.824156892060216], [-87.60419086242726, 41.824156220282596], [-87.60417154057622, 41.82415580051237], [-87.60415221225436, 41.824155632795396], [-87.60413288226572, 41.82415571806249], [-87.60411355904553, 41.824156055466894], [-87.60409424500084, 41.824156645023855], [-87.60407494855669, 41.82415748678687], [-87.60405567333392, 41.82415857987863], [-87.60403642775758, 41.82415992435258], [-87.60401721664196, 41.82416152023936], [-87.60399804481145, 41.82416336666922], [-87.60397216606508, 41.82416626443172], [-87.60346372774372, 41.82428645007398], [-87.60283279718537, 41.82449961768677], [-87.60254227296632, 41.82459826474106], [-87.60246449645898, 41.82463065780316], [-87.60214041957721, 41.82476563187484], [-87.6020952755735, 41.8247849900892], [-87.6017964676506, 41.824913114836825], [-87.60160828555927, 41.824988222508935], [-87.60150680968545, 41.82502872373627], [-87.60091462496219, 41.825188150840695], [-87.60074975423764, 41.82519086558529], [-87.60046891563478, 41.82526537949098], [-87.60036960542857, 41.82529172834911], [-87.60027660609322, 41.82531640313449], [-87.59999145364394, 41.825392060591405], [-87.59984691458156, 41.8254304090753], [-87.5996240077739, 41.825489550046555], [-87.5995963400068, 41.82550927640572]]]</t>
         </is>
       </c>
     </row>
@@ -17894,14 +17894,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>S MICHIGAN AVE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>S GILES AVE</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Protected Bike Lane</t>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.121774289186</t>
+          <t>0.204433765585</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -17929,19 +17929,19 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[[[-87.61947655373596, 41.838387441384285], [-87.61826297733084, 41.83840128373133], [-87.61746126495309, 41.838411426314124], [-87.61711743673902, 41.83841544388878]]]</t>
+          <t>[[[-87.62343694336933, 41.83833704540958], [-87.62323358361407, 41.83833847406264], [-87.6219191008301, 41.838356765893344], [-87.62177979242179, 41.83835870302541], [-87.62128211303167, 41.83836481491048], [-87.62100750971918, 41.8383681865488], [-87.62063024755903, 41.83837298145963], [-87.62047048387781, 41.83837500885838], [-87.62015738391769, 41.83837922174425], [-87.61999021695806, 41.83838147080919], [-87.61947655373596, 41.838387441384285]]]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAYNE DR</t>
+          <t>35TH ST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PAYNE</t>
+          <t>35TH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -17951,22 +17951,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>E RAINEY DR</t>
+          <t>S INDIANA AVE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>E 55TH ST</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0675160768248</t>
+          <t>0.247640012693</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -17986,54 +17986,54 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[[[-87.60737728719235, 41.79496310174033], [-87.60739572258301, 41.79490141710621], [-87.60759032740498, 41.794597181214684], [-87.60781895881487, 41.79429315897816], [-87.60788597312641, 41.79420071616683], [-87.60793532745689, 41.79414594962413], [-87.60799024123432, 41.794105496864226]]]</t>
+          <t>[[[-87.62175790723948, 41.83105114677236], [-87.62147204346718, 41.83105439399251], [-87.62114680081156, 41.83105756560645], [-87.62071506301695, 41.83106177458682], [-87.62054500801808, 41.83106270827247], [-87.62038410991939, 41.83106359050268], [-87.61993842551381, 41.831068138560155], [-87.61959497831648, 41.83107164288365], [-87.61932790430228, 41.83107429835225], [-87.6192145415096, 41.83107542490796], [-87.61861331357758, 41.831080192721124], [-87.61840049624368, 41.8310834879503], [-87.61811354507196, 41.8310879292089], [-87.61794575632707, 41.83109052619566], [-87.61760482133919, 41.83109575717714], [-87.61730766754923, 41.83109415363711], [-87.61696083107093, 41.83109228088914]]]</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>55TH PL</t>
+          <t>35TH ST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>35TH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>E 55TH ST</t>
+          <t>S STATE ST</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S DORCHESTER AVE</t>
+          <t>S INDIANA AVE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Marked Shared Lane</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0456951713071</t>
+          <t>0.251982034456</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1W</t>
+          <t>2W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -18043,34 +18043,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[[[-87.59230182841584, 41.795115630665705], [-87.59228479651814, 41.79504607209104], [-87.59225548130618, 41.79497654411554], [-87.59219846154255, 41.79489528677071], [-87.59216267495331, 41.79487450803364], [-87.5920133591238, 41.794803290937494], [-87.59193680903836, 41.794782379617466], [-87.59185276036327, 41.794775717447465], [-87.59167067344248, 41.79477653357941]]]</t>
+          <t>[[[-87.6266385987239, 41.83100580881331], [-87.6264732958851, 41.83101107967687], [-87.62623318245583, 41.83101873668085], [-87.62601026219642, 41.831016431371204], [-87.62591536563151, 41.83101335928809], [-87.62580089456586, 41.83100965335254], [-87.62578894519758, 41.8310097769209], [-87.62528748091881, 41.83101497359384], [-87.62497040535462, 41.83101825860181], [-87.62460523369673, 41.83102204008217], [-87.62425145860854, 41.831023753331884], [-87.62423505388152, 41.83102409322796], [-87.62325146933688, 41.831035886002816], [-87.623068985482, 41.831038072800894], [-87.62257009356864, 41.831042925980455], [-87.62249985576759, 41.831043609555515], [-87.62195505561091, 41.831048907025604], [-87.62175790723948, 41.83105114677236]]]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>55TH PL</t>
+          <t>PERSHING RD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>PERSHING</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>S DORCHESTER AVE</t>
+          <t>S MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>E 55TH ST</t>
+          <t>S COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -18080,17 +18080,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.144696496175</t>
+          <t>0.52273584865</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1W</t>
+          <t>2W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -18100,19 +18100,19 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[[[-87.59167067344248, 41.79477653357941], [-87.59136866354801, 41.79477788763556], [-87.59102905319932, 41.7947802494273], [-87.5907804071988, 41.794781030192134], [-87.59057041516495, 41.79478167500291], [-87.59032230194119, 41.79478403653916], [-87.59011020296843, 41.79478605342406], [-87.58985624501801, 41.79478954209586], [-87.58964247007485, 41.794793948510694], [-87.58954419795131, 41.79480903782709], [-87.5894761210009, 41.79482602245259], [-87.5894100443973, 41.7948539709812], [-87.58930529537159, 41.794916096688844], [-87.58922782297005, 41.79504082853871], [-87.58920177375734, 41.79511475522187], [-87.58919925975736, 41.795164108872186], [-87.58920472557244, 41.79519313923364]]]</t>
+          <t>[[[-87.61699111101917, 41.82382621643897], [-87.61672658426848, 41.823830247623874], [-87.61611742079225, 41.823839530348515], [-87.61610351380473, 41.8238397010112], [-87.6154691158385, 41.82384748030514], [-87.61514202830347, 41.82385149048068], [-87.61435832379438, 41.82386109676443], [-87.61307015328607, 41.82387688472249], [-87.61261856025574, 41.82388291330555], [-87.61213034165046, 41.82388942863265], [-87.61127647198559, 41.82389814834697], [-87.61055372981066, 41.82390552337138], [-87.60983565600785, 41.82391284582243], [-87.60958135685671, 41.82391543849396], [-87.6083907741053, 41.82392832878097], [-87.60833202655425, 41.82392896457945], [-87.60732163043673, 41.82394102449633], [-87.60702288161544, 41.823950057947265], [-87.60691033374472, 41.82395217241693], [-87.60686734794898, 41.8239569091955]]]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>55TH ST</t>
+          <t>PERSHING RD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>PERSHING</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -18122,12 +18122,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E 55TH PL</t>
+          <t>S COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S LAKE PARK AVE</t>
+          <t>E OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0858058887654</t>
+          <t>0.135533728291</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -18157,19 +18157,19 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[[[-87.58920472557244, 41.79519313923364], [-87.58843978013414, 41.795185708334266], [-87.58754346134559, 41.795176995453275]]]</t>
+          <t>[[[-87.60686734794898, 41.8239569091955], [-87.60606651814183, 41.82417374136248], [-87.60576295911753, 41.82426465478336], [-87.60574292254485, 41.82427037292759], [-87.60572275653709, 41.824275828247], [-87.60570246591914, 41.82428101987172], [-87.60568205673985, 41.82428594513898], [-87.60566153743501, 41.824290603201796], [-87.60564091042225, 41.82429499317505], [-87.60562018535114, 41.824299113319164], [-87.60559936705677, 41.82430296186401], [-87.6055784615575, 41.824306538847644], [-87.60555747730946, 41.8243098416226], [-87.60553641792379, 41.8243128702117], [-87.60551529184642, 41.824315622867694], [-87.6054675496305, 41.82432080616751], [-87.60514959326278, 41.82431298815248], [-87.60506702606838, 41.82430186758017], [-87.60498473109828, 41.8242896709576], [-87.60490273359159, 41.824276402046785], [-87.60482105759388, 41.82426206370194], [-87.60473921548223, 41.8242465609951], [-87.6045999908213, 41.824210864913994], [-87.60435230548126, 41.82416287487605]]]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>55TH ST</t>
+          <t>31ST ST</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>31ST</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -18179,22 +18179,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>S LAKE PARK AVE</t>
+          <t>S GILES AVE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S HYDE PARK BLVD</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Marked Shared Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.185855928634</t>
+          <t>0.121774289186</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[[[-87.58754346134559, 41.795176995453275], [-87.58738962534618, 41.795178680573635], [-87.58723653779546, 41.79518035774402], [-87.58718928018563, 41.79518087552708], [-87.587017867405, 41.79518275390326], [-87.58694172794344, 41.7951835872402], [-87.58690389104218, 41.795184002251354], [-87.58673557437942, 41.79518584540241], [-87.58671603381707, 41.795186059636485], [-87.58661850963912, 41.79518760010154], [-87.58616460134657, 41.79519476866744], [-87.58576988324349, 41.79519906136454], [-87.58540490313923, 41.795203699386356], [-87.58511445279412, 41.795207390147176], [-87.58484326462393, 41.795207078465104], [-87.58467848640464, 41.79520974297046], [-87.58451912941597, 41.795212320129835], [-87.58431745967604, 41.79521624722297], [-87.58394543361024, 41.795220065764205]]]</t>
+          <t>[[[-87.61947655373596, 41.838387441384285], [-87.61826297733084, 41.83840128373133], [-87.61746126495309, 41.838411426314124], [-87.61711743673902, 41.83841544388878]]]</t>
         </is>
       </c>
     </row>

--- a/bronzeville_assets.xlsx
+++ b/bronzeville_assets.xlsx
@@ -16682,12 +16682,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>55TH ST</t>
+          <t>STONY ISLAND AVE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>STONY ISLAND</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -16697,12 +16697,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E 55TH PL</t>
+          <t>E 59TH ST</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S LAKE PARK AVE</t>
+          <t>E 56TH ST</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0858058887654</t>
+          <t>0.378464121006</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -16732,19 +16732,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[[[-87.58920472557244, 41.79519313923364], [-87.58843978013414, 41.795185708334266], [-87.58754346134559, 41.795176995453275]]]</t>
+          <t>[[[-87.58662892252528, 41.78789358129685], [-87.586706089987, 41.79153912486357], [-87.58663186923798, 41.79337593873825]]]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>55TH ST</t>
+          <t>63RD ST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>63RD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -16754,22 +16754,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S LAKE PARK AVE</t>
+          <t>S MARYLAND AVE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S HYDE PARK BLVD</t>
+          <t>S STONY ISLAND AVE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marked Shared Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.185855928634</t>
+          <t>0.939759213128</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -16789,29 +16789,29 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[[[-87.58754346134559, 41.795176995453275], [-87.58738962534618, 41.795178680573635], [-87.58723653779546, 41.79518035774402], [-87.58718928018563, 41.79518087552708], [-87.587017867405, 41.79518275390326], [-87.58694172794344, 41.7951835872402], [-87.58690389104218, 41.795184002251354], [-87.58673557437942, 41.79518584540241], [-87.58671603381707, 41.795186059636485], [-87.58661850963912, 41.79518760010154], [-87.58616460134657, 41.79519476866744], [-87.58576988324349, 41.79519906136454], [-87.58540490313923, 41.795203699386356], [-87.58511445279412, 41.795207390147176], [-87.58484326462393, 41.795207078465104], [-87.58467848640464, 41.79520974297046], [-87.58451912941597, 41.795212320129835], [-87.58431745967604, 41.79521624722297], [-87.58394543361024, 41.795220065764205]]]</t>
+          <t>[[[-87.6046422414081, 41.78042037203421], [-87.58645234642981, 41.78061152172805]]]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAYNE DR</t>
+          <t>55TH PL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PAYNE</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>E RAINEY DR</t>
+          <t>S DORCHESTER AVE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -16821,22 +16821,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0675160768248</t>
+          <t>0.140520676257</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2W</t>
+          <t>1W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -16846,54 +16846,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[[[-87.60737728719235, 41.79496310174033], [-87.60739572258301, 41.79490141710621], [-87.60759032740498, 41.794597181214684], [-87.60781895881487, 41.79429315897816], [-87.60788597312641, 41.79420071616683], [-87.60793532745689, 41.79414594962413], [-87.60799024123432, 41.794105496864226]]]</t>
+          <t>[[[-87.59168916179809, 41.795501250471744], [-87.59156420785152, 41.79550224079574], [-87.59131454042925, 41.79550235705856], [-87.59109786212012, 41.79550386629565], [-87.59085770346485, 41.79550615703121], [-87.59063312557093, 41.79550898557082], [-87.59034113508434, 41.79551248331219], [-87.59008263205658, 41.79551557934015], [-87.58986476270361, 41.79551853261422], [-87.58969927989575, 41.795519959075364], [-87.58959813856721, 41.79551348622447], [-87.58949753203959, 41.795492500363025], [-87.58941006033334, 41.795458316572784], [-87.58930035814839, 41.79539227921674], [-87.58923659094965, 41.795287816040414], [-87.58921021181861, 41.795222275968634], [-87.58920472557244, 41.79519313923364]]]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>55TH PL</t>
+          <t>OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>OAKWOOD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E 55TH ST</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S DORCHESTER AVE</t>
+          <t>S COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0456951713071</t>
+          <t>0.521985922417</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1W</t>
+          <t>2W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -16903,54 +16903,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[[[-87.59230182841584, 41.795115630665705], [-87.59228479651814, 41.79504607209104], [-87.59225548130618, 41.79497654411554], [-87.59219846154255, 41.79489528677071], [-87.59216267495331, 41.79487450803364], [-87.5920133591238, 41.794803290937494], [-87.59193680903836, 41.794782379617466], [-87.59185276036327, 41.794775717447465], [-87.59167067344248, 41.79477653357941]]]</t>
+          <t>[[[-87.61695962339326, 41.82264134188429], [-87.61669629612875, 41.82264370313865], [-87.61606631519486, 41.822649350671306], [-87.61515537131041, 41.82265750964905], [-87.61417375753305, 41.822666282273154], [-87.61359604756068, 41.82267144039865], [-87.61289063246282, 41.82267242469886], [-87.6121351823511, 41.8226734740702], [-87.611723286215, 41.82267866256548], [-87.61021322833639, 41.82269767014164], [-87.60979638334024, 41.82270234788722], [-87.60820507512415, 41.82272019148444], [-87.6069221364619, 41.82272643226638], [-87.60684961994563, 41.822720681391324]]]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>55TH PL</t>
+          <t>ELLSWORTH DR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>ELLSWORTH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>S DORCHESTER AVE</t>
+          <t>E GARFIELD BLVD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>E 55TH ST</t>
+          <t>E 51ST ST</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.144696496175</t>
+          <t>0.563850072419</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1W</t>
+          <t>2W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -16960,19 +16960,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[[[-87.59167067344248, 41.79477653357941], [-87.59136866354801, 41.79477788763556], [-87.59102905319932, 41.7947802494273], [-87.5907804071988, 41.794781030192134], [-87.59057041516495, 41.79478167500291], [-87.59032230194119, 41.79478403653916], [-87.59011020296843, 41.79478605342406], [-87.58985624501801, 41.79478954209586], [-87.58964247007485, 41.794793948510694], [-87.58954419795131, 41.79480903782709], [-87.5894761210009, 41.79482602245259], [-87.5894100443973, 41.7948539709812], [-87.58930529537159, 41.794916096688844], [-87.58922782297005, 41.79504082853871], [-87.58920177375734, 41.79511475522187], [-87.58919925975736, 41.795164108872186], [-87.58920472557244, 41.79519313923364]]]</t>
+          <t>[[[-87.61610503358958, 41.80209463506868], [-87.61598017987416, 41.801936535122216], [-87.61571941210941, 41.80151328586742], [-87.61550944727176, 41.80119731531666], [-87.61539693942696, 41.80102858217285], [-87.61529932756855, 41.80088235809726], [-87.61506155892664, 41.80053756279236], [-87.614929442976, 41.80036126695795], [-87.6147326797903, 41.80020701596753], [-87.61447389984386, 41.800029817334064], [-87.61431845146083, 41.799919979246425], [-87.6141480647915, 41.79976531521329], [-87.61403399880841, 41.7996282102345], [-87.61398065771237, 41.799550981614956], [-87.61395599984449, 41.79950944339995], [-87.61391106290475, 41.79939892462118], [-87.61389464937568, 41.79934160352373], [-87.61388617434496, 41.799296050230076], [-87.61388737070605, 41.79922835661386], [-87.61389328726345, 41.79900113927943], [-87.61391381323126, 41.798644730896484], [-87.61392200607862, 41.79853402352384], [-87.61392355907101, 41.798501352248834], [-87.61392547720082, 41.798460992447886], [-87.61396071892041, 41.79813000580307], [-87.61400731520777, 41.79785924549823], [-87.6140570307326, 41.79763090320573], [-87.6141338608941, 41.79734899758503], [-87.61419534320311, 41.797160438942676], [-87.61428035246796, 41.79693075355048], [-87.61437410917135, 41.7966928071726], [-87.61439017940391, 41.79665131864515], [-87.61448490414, 41.79640677773468], [-87.61455078269736, 41.796175847853924], [-87.61459809192392, 41.79591974491938], [-87.61462586548868, 41.79561330073654], [-87.61463898952323, 41.7953906021651], [-87.6146621547144, 41.79508629626382], [-87.61469428955904, 41.7949442612965], [-87.61469972612767, 41.794814738076944], [-87.61469151426928, 41.79468057278534], [-87.61467818509446, 41.79459684387978], [-87.6146469845286, 41.79448424318099]]]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>55TH ST</t>
+          <t>MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>MARTIN LUTHER KING JR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -16982,22 +16982,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S HYDE PARK BLVD</t>
+          <t>E 51ST ST</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S SHORE DR</t>
+          <t>E 37TH ST</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marked Shared Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.158892281839</t>
+          <t>1.75304400525</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -17017,19 +17017,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[[[-87.58394543361024, 41.795220065764205], [-87.5835817620467, 41.795223797172596], [-87.58327948192816, 41.79522915096661], [-87.58324210928754, 41.79522947236536], [-87.5829312072739, 41.795232145317705], [-87.58253279286843, 41.79523559512813], [-87.58220685560578, 41.795238416348866], [-87.5819200476465, 41.79524101361322], [-87.58182560768654, 41.79524177247036], [-87.58163397586631, 41.79524331336056], [-87.58124686189768, 41.795246514830914], [-87.58086945340737, 41.79525705071672]]]</t>
+          <t>[[[-87.6170661605481, 41.82746577345483], [-87.61706142929766, 41.82722251576819], [-87.61703594211926, 41.82599621919331], [-87.6170346569476, 41.825924585756425], [-87.61702807683459, 41.825640732364505], [-87.61701815626563, 41.825212839267834], [-87.61701158986415, 41.824860489202024], [-87.61700504238831, 41.82446703021115], [-87.61699819000684, 41.82410092909017], [-87.61699111101917, 41.82382621643897], [-87.6169682780898, 41.82294010913907], [-87.61695962339326, 41.82264134188429], [-87.61694647296191, 41.82218741283243], [-87.61694134071122, 41.82200285608154], [-87.61691550518213, 41.82107381642339], [-87.61690011817095, 41.820520501742], [-87.6168912291518, 41.82022584659349], [-87.61687951834088, 41.819837625724176], [-87.61686451475447, 41.81931905960095], [-87.61685917407235, 41.819134444733976], [-87.61685486347649, 41.81903471854085], [-87.61685026940104, 41.81886108718419], [-87.61684584573, 41.818632543662474], [-87.61683899958928, 41.818426428036624], [-87.61682859667718, 41.81811322063313], [-87.61682317373558, 41.81791516029109], [-87.6168170711122, 41.81769914813044], [-87.61681204388093, 41.81752487028064], [-87.6168097679134, 41.8174459431259], [-87.61680154890371, 41.817143281582915], [-87.61680085310701, 41.81711867608355], [-87.61679454768834, 41.8168960333512], [-87.61678662778932, 41.816627119659934], [-87.61677714364522, 41.81630505574234], [-87.61677062740476, 41.81603396382891], [-87.61676552375634, 41.81582380290046], [-87.61675765682091, 41.81555209840315], [-87.61675059408309, 41.81531687029233], [-87.61674224579149, 41.815039015176694], [-87.61673544566895, 41.814814353391846], [-87.61672717933429, 41.814541247209775], [-87.61672053521322, 41.814281652787514], [-87.6167133124245, 41.814034457969235], [-87.61670518857355, 41.813756248551975], [-87.61669736056754, 41.8134778473913], [-87.61668988955066, 41.8131937690335], [-87.61668445767971, 41.813002180182174], [-87.61667472405641, 41.812658842819], [-87.616665225364, 41.812313114669124], [-87.61666403964655, 41.81227254737789], [-87.6166590672492, 41.812102152014056], [-87.61665296669604, 41.811892506022836], [-87.61664655510585, 41.811671359704654], [-87.61664207135496, 41.81149114274442], [-87.61663372407628, 41.811189079715234], [-87.61662461081087, 41.81085932970484], [-87.61662055015955, 41.81066750713534], [-87.61661158374402, 41.81035309368742], [-87.61660946369571, 41.81028007730828], [-87.61660532895206, 41.81013765741237], [-87.6165971626926, 41.809869902413276], [-87.61658969716275, 41.809631378067415], [-87.6165830260001, 41.80937622288194], [-87.61657750843742, 41.80916515967291], [-87.61657434552195, 41.80905399609861], [-87.61656977392795, 41.80889161626314], [-87.61656382612986, 41.80868147771314], [-87.6165595258573, 41.80852434140443], [-87.61655442132603, 41.80832082118215], [-87.61654832746574, 41.80807121930493], [-87.61654000442812, 41.8077846368839], [-87.61653454090984, 41.80755514196061], [-87.61652978730874, 41.80735545128697], [-87.61652116505952, 41.80702339471532], [-87.61650989769541, 41.806543569441665], [-87.6165048970603, 41.80633409577223], [-87.61649750571686, 41.805990301736024], [-87.61649069419391, 41.80573396875114], [-87.61648329413629, 41.80545551854538], [-87.6164821821902, 41.80541072451418], [-87.61647834932612, 41.8052344630603], [-87.61646633002383, 41.80475973793773], [-87.61645839638088, 41.80443169207701], [-87.61644878457702, 41.804030528954634], [-87.61644580038985, 41.803914590028064], [-87.61644156658187, 41.80375012783846], [-87.61643122120574, 41.803483868826675], [-87.61640545455953, 41.80318628304824], [-87.61636657748137, 41.803006515619764], [-87.6163590650835, 41.80297177546721], [-87.61625552696026, 41.80267897305564], [-87.61618167023049, 41.8024149789362], [-87.61610503358958, 41.80209463506868]]]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STONY ISLAND AVE</t>
+          <t>55TH ST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STONY ISLAND</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -17039,22 +17039,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>E 59TH ST</t>
+          <t>S COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>E 56TH ST</t>
+          <t>S DORCHESTER AVE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.378464121006</t>
+          <t>0.766203524173</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -17074,19 +17074,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[[[-87.58662892252528, 41.78789358129685], [-87.586706089987, 41.79153912486357], [-87.58663186923798, 41.79337593873825]]]</t>
+          <t>[[[-87.60620979087955, 41.79495747442708], [-87.6057344224648, 41.79495778503282], [-87.60525201125915, 41.79496326297865], [-87.60479417557326, 41.794968318532064], [-87.60416578190858, 41.79497613248727], [-87.60382968914276, 41.79497974562034], [-87.60364258908545, 41.79498175626839], [-87.6031618006071, 41.79498638580917], [-87.60258003192963, 41.79499286770068], [-87.60201296951952, 41.794999330425995], [-87.60176485131475, 41.79500208669209], [-87.60130428020985, 41.79500683720651], [-87.60083389016755, 41.795011687128714], [-87.60050008922202, 41.79501581473183], [-87.6002440069741, 41.79501912014317], [-87.59977157954289, 41.79502367900555], [-87.59944937777256, 41.79502678009304], [-87.5991151755601, 41.795030737243415], [-87.59876610668249, 41.79503599750648], [-87.59846421388181, 41.795039746997446], [-87.59809252263335, 41.79504284460396], [-87.59783639943313, 41.79504497752776], [-87.59764672479376, 41.79504746882311], [-87.59746279967632, 41.79504988499188], [-87.59729500945298, 41.795051197774896], [-87.59714467615815, 41.79505237459098], [-87.59712751034556, 41.79505261932045], [-87.59653845570257, 41.79505834324881], [-87.59587785724203, 41.79506631315715], [-87.59585440739944, 41.795062984370915], [-87.59491762743127, 41.79507687701188], [-87.59334179382368, 41.795100230834926], [-87.59230182841584, 41.795115630665705], [-87.592302990093, 41.795150774423014], [-87.59230046172085, 41.795201582121706], [-87.59228243740286, 41.795250862799094], [-87.59224146498102, 41.795340996591], [-87.59222898325629, 41.79535145199423], [-87.59207943860847, 41.79544011543386], [-87.5920123125014, 41.79546698816598], [-87.59190924617853, 41.795490664939614], [-87.59181796862944, 41.7955002290602], [-87.59168916179809, 41.795501250471744]]]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>63RD ST</t>
+          <t>DREXEL BLVD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>63RD</t>
+          <t>DREXEL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -17096,22 +17096,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S MARYLAND AVE</t>
+          <t>E HYDE PARK BLVD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S STONY ISLAND AVE</t>
+          <t>E OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.939759213128</t>
+          <t>1.44027790321</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -17131,54 +17131,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[[[-87.6046422414081, 41.78042037203421], [-87.58645234642981, 41.78061152172805]]]</t>
+          <t>[[[-87.6061357829986, 41.82285126887031], [-87.60609798571573, 41.82276399646166], [-87.60590091255791, 41.82238247366579], [-87.60556669332729, 41.8218485016191], [-87.60530502182334, 41.82143367779866], [-87.60503607482781, 41.82100731247258], [-87.6048651023532, 41.820736412610586], [-87.60468547053425, 41.82045272301633], [-87.60449083328942, 41.820146654278034], [-87.6044256482468, 41.820039488053965], [-87.60440298975179, 41.8199636312076], [-87.60436493891923, 41.819611683642336], [-87.60429991730739, 41.819055419679465], [-87.60429380433658, 41.81900362340333], [-87.60426189555417, 41.8187247681738], [-87.60423424833219, 41.81848098336986], [-87.60420878995686, 41.81825126419623], [-87.60417455131629, 41.817968413673675], [-87.60415552556421, 41.81781123864321], [-87.60413394449134, 41.81761153828346], [-87.60411028125793, 41.81739508449601], [-87.6040885112337, 41.8171992256062], [-87.6040700938691, 41.81703439693089], [-87.60405800489534, 41.81683774595473], [-87.60404268597567, 41.816588553468314], [-87.60403709666593, 41.81630849303128], [-87.60403120520014, 41.8160161354863], [-87.60402385839835, 41.81570661792346], [-87.6040170517352, 41.81545621443974], [-87.60400794890579, 41.81501570099713], [-87.60400263005133, 41.814758282399495], [-87.6039971166536, 41.8145069813334], [-87.60399159427311, 41.81425010973378], [-87.60398593909036, 41.81399836927459], [-87.60398044110272, 41.813765236437085], [-87.60397499985255, 41.81352699896516], [-87.60396816319397, 41.813199599950835], [-87.60396389986742, 41.8129954454885], [-87.60395896340789, 41.81276777679964], [-87.60395507075744, 41.812587068895915], [-87.60395103323813, 41.81239971908291], [-87.60394749744123, 41.81224261431615], [-87.60394634625938, 41.812192497109486], [-87.60394481883999, 41.812126322466376], [-87.60393970922209, 41.8119040592473], [-87.60393553325102, 41.81172255360749], [-87.60392887286369, 41.811376458031624], [-87.60392551762324, 41.81120206585357], [-87.6039220751111, 41.811026987049004], [-87.60391755623571, 41.81080453486339], [-87.60391271281719, 41.810565396211956], [-87.60390920747359, 41.810395859547214], [-87.60390545674095, 41.810224510714114], [-87.6039029260037, 41.810108878818895], [-87.60389805780825, 41.80989781291501], [-87.60389154426316, 41.80955704103505], [-87.60388737756344, 41.80933909368288], [-87.6038839679615, 41.80921055686321], [-87.60387961854272, 41.80904658706937], [-87.60387371153965, 41.80877837916568], [-87.60386741299754, 41.80847998089812], [-87.60386217213637, 41.80822741989517], [-87.60385829065206, 41.80802316594071], [-87.60385239269901, 41.80773868420216], [-87.60384783613233, 41.80751883906607], [-87.60384274399121, 41.807243419051346], [-87.60383646805631, 41.80693986273583], [-87.60383088501047, 41.80664640914328], [-87.6038268275711, 41.80644791716319], [-87.60381920996646, 41.8061785179137], [-87.60381478491121, 41.80591612025036], [-87.60381184231792, 41.80574166480126], [-87.60380626616268, 41.80551868439242], [-87.60380179621455, 41.80533089313059], [-87.60379613662855, 41.80512799991602], [-87.60379079943327, 41.80490019151557], [-87.6037865313686, 41.80469439808748], [-87.6037805331614, 41.80445368703591], [-87.60377677465617, 41.804267683853766], [-87.60377404877609, 41.80410075937107], [-87.60377006455334, 41.80385690535313], [-87.60376813499602, 41.80374251152941], [-87.60376478430065, 41.80361114875377], [-87.60375648729162, 41.803366141884204], [-87.60375141035728, 41.80319294589922], [-87.60374820447251, 41.803022835593254], [-87.60374626819105, 41.80289938597228], [-87.60374406398431, 41.80276709679405], [-87.603741005496, 41.802597042333126], [-87.60377786306702, 41.802278554577875]]]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>55TH PL</t>
+          <t>MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>MARTIN LUTHER KING JR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S DORCHESTER AVE</t>
+          <t>E GARFIELD BLVD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>E 55TH ST</t>
+          <t>E 51ST ST</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.140520676257</t>
+          <t>0.525487613949</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1W</t>
+          <t>2W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -17188,19 +17188,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[[[-87.59168916179809, 41.795501250471744], [-87.59156420785152, 41.79550224079574], [-87.59131454042925, 41.79550235705856], [-87.59109786212012, 41.79550386629565], [-87.59085770346485, 41.79550615703121], [-87.59063312557093, 41.79550898557082], [-87.59034113508434, 41.79551248331219], [-87.59008263205658, 41.79551557934015], [-87.58986476270361, 41.79551853261422], [-87.58969927989575, 41.795519959075364], [-87.58959813856721, 41.79551348622447], [-87.58949753203959, 41.795492500363025], [-87.58941006033334, 41.795458316572784], [-87.58930035814839, 41.79539227921674], [-87.58923659094965, 41.795287816040414], [-87.58921021181861, 41.795222275968634], [-87.58920472557244, 41.79519313923364]]]</t>
+          <t>[[[-87.61610503358958, 41.80209463506868], [-87.6161372553474, 41.80190169269912], [-87.61614074146709, 41.80158907436339], [-87.61612777562215, 41.80089368105505], [-87.61611061011892, 41.80022228554601], [-87.6161072447521, 41.80009063210527], [-87.61609367670414, 41.799567542526496], [-87.61608066594823, 41.799007655365806], [-87.61607252526402, 41.798655650381], [-87.61607043851457, 41.798547458174994], [-87.6160678890834, 41.798457127876596], [-87.61605837110685, 41.79805028367454], [-87.61604192712679, 41.79739045646684], [-87.6160235286314, 41.79670545121182], [-87.61602194699849, 41.79663990734271], [-87.61601550198797, 41.7963728214937], [-87.61599616418324, 41.79563948379497], [-87.61599287316523, 41.795514680599055], [-87.61597940877292, 41.795011981545464], [-87.6159753641248, 41.794792923748744], [-87.6159725954511, 41.7946429706259], [-87.61596722873355, 41.79447924837816]]]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OAKWOOD BLVD</t>
+          <t>55TH ST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OAKWOOD</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -17210,22 +17210,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>S HYDE PARK BLVD</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S COTTAGE GROVE AVE</t>
+          <t>S SHORE DR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Marked Shared Lane</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.521985922417</t>
+          <t>0.158892281839</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -17245,19 +17245,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[[[-87.61695962339326, 41.82264134188429], [-87.61669629612875, 41.82264370313865], [-87.61606631519486, 41.822649350671306], [-87.61515537131041, 41.82265750964905], [-87.61417375753305, 41.822666282273154], [-87.61359604756068, 41.82267144039865], [-87.61289063246282, 41.82267242469886], [-87.6121351823511, 41.8226734740702], [-87.611723286215, 41.82267866256548], [-87.61021322833639, 41.82269767014164], [-87.60979638334024, 41.82270234788722], [-87.60820507512415, 41.82272019148444], [-87.6069221364619, 41.82272643226638], [-87.60684961994563, 41.822720681391324]]]</t>
+          <t>[[[-87.58394543361024, 41.795220065764205], [-87.5835817620467, 41.795223797172596], [-87.58327948192816, 41.79522915096661], [-87.58324210928754, 41.79522947236536], [-87.5829312072739, 41.795232145317705], [-87.58253279286843, 41.79523559512813], [-87.58220685560578, 41.795238416348866], [-87.5819200476465, 41.79524101361322], [-87.58182560768654, 41.79524177247036], [-87.58163397586631, 41.79524331336056], [-87.58124686189768, 41.795246514830914], [-87.58086945340737, 41.79525705071672]]]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ELLSWORTH DR</t>
+          <t>31ST ST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ELLSWORTH</t>
+          <t>31ST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -17267,12 +17267,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>E GARFIELD BLVD</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>E 51ST ST</t>
+          <t>S MOE DR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.563850072419</t>
+          <t>0.374564177222</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -17302,19 +17302,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[[[-87.61610503358958, 41.80209463506868], [-87.61598017987416, 41.801936535122216], [-87.61571941210941, 41.80151328586742], [-87.61550944727176, 41.80119731531666], [-87.61539693942696, 41.80102858217285], [-87.61529932756855, 41.80088235809726], [-87.61506155892664, 41.80053756279236], [-87.614929442976, 41.80036126695795], [-87.6147326797903, 41.80020701596753], [-87.61447389984386, 41.800029817334064], [-87.61431845146083, 41.799919979246425], [-87.6141480647915, 41.79976531521329], [-87.61403399880841, 41.7996282102345], [-87.61398065771237, 41.799550981614956], [-87.61395599984449, 41.79950944339995], [-87.61391106290475, 41.79939892462118], [-87.61389464937568, 41.79934160352373], [-87.61388617434496, 41.799296050230076], [-87.61388737070605, 41.79922835661386], [-87.61389328726345, 41.79900113927943], [-87.61391381323126, 41.798644730896484], [-87.61392200607862, 41.79853402352384], [-87.61392355907101, 41.798501352248834], [-87.61392547720082, 41.798460992447886], [-87.61396071892041, 41.79813000580307], [-87.61400731520777, 41.79785924549823], [-87.6140570307326, 41.79763090320573], [-87.6141338608941, 41.79734899758503], [-87.61419534320311, 41.797160438942676], [-87.61428035246796, 41.79693075355048], [-87.61437410917135, 41.7966928071726], [-87.61439017940391, 41.79665131864515], [-87.61448490414, 41.79640677773468], [-87.61455078269736, 41.796175847853924], [-87.61459809192392, 41.79591974491938], [-87.61462586548868, 41.79561330073654], [-87.61463898952323, 41.7953906021651], [-87.6146621547144, 41.79508629626382], [-87.61469428955904, 41.7949442612965], [-87.61469972612767, 41.794814738076944], [-87.61469151426928, 41.79468057278534], [-87.61467818509446, 41.79459684387978], [-87.6146469845286, 41.79448424318099]]]</t>
+          <t>[[[-87.61711743673902, 41.83841544388878], [-87.61349382112748, 41.83846417399243], [-87.61336507987872, 41.8384654324603], [-87.61170778684063, 41.8384964974145], [-87.6113260948113, 41.838513422816135], [-87.61122239818451, 41.83851802083818], [-87.61106328407865, 41.83852507577069], [-87.61079286825503, 41.83852833767229], [-87.61023646107017, 41.83853504871899], [-87.61004517815752, 41.83853385151719], [-87.60986250664294, 41.83853270823932]]]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MARTIN LUTHER KING JR DR</t>
+          <t>33RD ST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MARTIN LUTHER KING JR</t>
+          <t>33RD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -17324,22 +17324,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>E 51ST ST</t>
+          <t>S STATE ST</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>E 37TH ST</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Marked Shared Lane</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.75304400525</t>
+          <t>0.47034639757</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17359,19 +17359,19 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[[[-87.6170661605481, 41.82746577345483], [-87.61706142929766, 41.82722251576819], [-87.61703594211926, 41.82599621919331], [-87.6170346569476, 41.825924585756425], [-87.61702807683459, 41.825640732364505], [-87.61701815626563, 41.825212839267834], [-87.61701158986415, 41.824860489202024], [-87.61700504238831, 41.82446703021115], [-87.61699819000684, 41.82410092909017], [-87.61699111101917, 41.82382621643897], [-87.6169682780898, 41.82294010913907], [-87.61695962339326, 41.82264134188429], [-87.61694647296191, 41.82218741283243], [-87.61694134071122, 41.82200285608154], [-87.61691550518213, 41.82107381642339], [-87.61690011817095, 41.820520501742], [-87.6168912291518, 41.82022584659349], [-87.61687951834088, 41.819837625724176], [-87.61686451475447, 41.81931905960095], [-87.61685917407235, 41.819134444733976], [-87.61685486347649, 41.81903471854085], [-87.61685026940104, 41.81886108718419], [-87.61684584573, 41.818632543662474], [-87.61683899958928, 41.818426428036624], [-87.61682859667718, 41.81811322063313], [-87.61682317373558, 41.81791516029109], [-87.6168170711122, 41.81769914813044], [-87.61681204388093, 41.81752487028064], [-87.6168097679134, 41.8174459431259], [-87.61680154890371, 41.817143281582915], [-87.61680085310701, 41.81711867608355], [-87.61679454768834, 41.8168960333512], [-87.61678662778932, 41.816627119659934], [-87.61677714364522, 41.81630505574234], [-87.61677062740476, 41.81603396382891], [-87.61676552375634, 41.81582380290046], [-87.61675765682091, 41.81555209840315], [-87.61675059408309, 41.81531687029233], [-87.61674224579149, 41.815039015176694], [-87.61673544566895, 41.814814353391846], [-87.61672717933429, 41.814541247209775], [-87.61672053521322, 41.814281652787514], [-87.6167133124245, 41.814034457969235], [-87.61670518857355, 41.813756248551975], [-87.61669736056754, 41.8134778473913], [-87.61668988955066, 41.8131937690335], [-87.61668445767971, 41.813002180182174], [-87.61667472405641, 41.812658842819], [-87.616665225364, 41.812313114669124], [-87.61666403964655, 41.81227254737789], [-87.6166590672492, 41.812102152014056], [-87.61665296669604, 41.811892506022836], [-87.61664655510585, 41.811671359704654], [-87.61664207135496, 41.81149114274442], [-87.61663372407628, 41.811189079715234], [-87.61662461081087, 41.81085932970484], [-87.61662055015955, 41.81066750713534], [-87.61661158374402, 41.81035309368742], [-87.61660946369571, 41.81028007730828], [-87.61660532895206, 41.81013765741237], [-87.6165971626926, 41.809869902413276], [-87.61658969716275, 41.809631378067415], [-87.6165830260001, 41.80937622288194], [-87.61657750843742, 41.80916515967291], [-87.61657434552195, 41.80905399609861], [-87.61656977392795, 41.80889161626314], [-87.61656382612986, 41.80868147771314], [-87.6165595258573, 41.80852434140443], [-87.61655442132603, 41.80832082118215], [-87.61654832746574, 41.80807121930493], [-87.61654000442812, 41.8077846368839], [-87.61653454090984, 41.80755514196061], [-87.61652978730874, 41.80735545128697], [-87.61652116505952, 41.80702339471532], [-87.61650989769541, 41.806543569441665], [-87.6165048970603, 41.80633409577223], [-87.61649750571686, 41.805990301736024], [-87.61649069419391, 41.80573396875114], [-87.61648329413629, 41.80545551854538], [-87.6164821821902, 41.80541072451418], [-87.61647834932612, 41.8052344630603], [-87.61646633002383, 41.80475973793773], [-87.61645839638088, 41.80443169207701], [-87.61644878457702, 41.804030528954634], [-87.61644580038985, 41.803914590028064], [-87.61644156658187, 41.80375012783846], [-87.61643122120574, 41.803483868826675], [-87.61640545455953, 41.80318628304824], [-87.61636657748137, 41.803006515619764], [-87.6163590650835, 41.80297177546721], [-87.61625552696026, 41.80267897305564], [-87.61618167023049, 41.8024149789362], [-87.61610503358958, 41.80209463506868]]]</t>
+          <t>[[[-87.62649453439884, 41.834657620039394], [-87.6261375484813, 41.834653255468275], [-87.62598820768505, 41.834655523097894], [-87.6258713558933, 41.83465729648271], [-87.62555479911322, 41.834663112644094], [-87.62521987635559, 41.834667222892755], [-87.62505539738287, 41.834670172980104], [-87.62490108129768, 41.834672941521305], [-87.62458217233613, 41.834675666707916], [-87.62423396810284, 41.83467955437231], [-87.62419467526055, 41.83468228203092], [-87.62332410153712, 41.834694699177206], [-87.6225766889668, 41.834705354550316], [-87.62204427228347, 41.83471294207457], [-87.62183407802331, 41.834710293288616], [-87.62162465056676, 41.834707653371126], [-87.62122627094816, 41.83471231672194], [-87.62080305524594, 41.834717269393636], [-87.62061503357474, 41.834712419521736], [-87.62049200866362, 41.83470924673693], [-87.6196388712932, 41.834730650392935], [-87.61940523053126, 41.834732824088015], [-87.61923746068237, 41.8347343849626], [-87.61879845501683, 41.83473992804518], [-87.61849043146212, 41.83474381686139], [-87.61818788325031, 41.83474705287812], [-87.61738398483341, 41.83475564899769]]]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>55TH ST</t>
+          <t>OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>55TH</t>
+          <t>OAKWOOD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -17386,17 +17386,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S DORCHESTER AVE</t>
+          <t>E PERSHING RD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.766203524173</t>
+          <t>0.179532699715</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17416,19 +17416,19 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[[[-87.60620979087955, 41.79495747442708], [-87.6057344224648, 41.79495778503282], [-87.60525201125915, 41.79496326297865], [-87.60479417557326, 41.794968318532064], [-87.60416578190858, 41.79497613248727], [-87.60382968914276, 41.79497974562034], [-87.60364258908545, 41.79498175626839], [-87.6031618006071, 41.79498638580917], [-87.60258003192963, 41.79499286770068], [-87.60201296951952, 41.794999330425995], [-87.60176485131475, 41.79500208669209], [-87.60130428020985, 41.79500683720651], [-87.60083389016755, 41.795011687128714], [-87.60050008922202, 41.79501581473183], [-87.6002440069741, 41.79501912014317], [-87.59977157954289, 41.79502367900555], [-87.59944937777256, 41.79502678009304], [-87.5991151755601, 41.795030737243415], [-87.59876610668249, 41.79503599750648], [-87.59846421388181, 41.795039746997446], [-87.59809252263335, 41.79504284460396], [-87.59783639943313, 41.79504497752776], [-87.59764672479376, 41.79504746882311], [-87.59746279967632, 41.79504988499188], [-87.59729500945298, 41.795051197774896], [-87.59714467615815, 41.79505237459098], [-87.59712751034556, 41.79505261932045], [-87.59653845570257, 41.79505834324881], [-87.59587785724203, 41.79506631315715], [-87.59585440739944, 41.795062984370915], [-87.59491762743127, 41.79507687701188], [-87.59334179382368, 41.795100230834926], [-87.59230182841584, 41.795115630665705], [-87.592302990093, 41.795150774423014], [-87.59230046172085, 41.795201582121706], [-87.59228243740286, 41.795250862799094], [-87.59224146498102, 41.795340996591], [-87.59222898325629, 41.79535145199423], [-87.59207943860847, 41.79544011543386], [-87.5920123125014, 41.79546698816598], [-87.59190924617853, 41.795490664939614], [-87.59181796862944, 41.7955002290602], [-87.59168916179809, 41.795501250471744]]]</t>
+          <t>[[[-87.60684961994563, 41.822720681391324], [-87.60679180817826, 41.82272115395717], [-87.60677001340125, 41.82272103500519], [-87.60674821900858, 41.82272120146208], [-87.60672643224186, 41.822721651572905], [-87.60670465910856, 41.822722386276055], [-87.60668290562634, 41.822723405609615], [-87.60666118024034, 41.82272470782627], [-87.60663948895807, 41.82272629386447], [-87.60661783660379, 41.82272816285434], [-87.60659623160228, 41.822730314849224], [-87.60657467999161, 41.822732748086665], [-87.60655318900317, 41.82273546171211], [-87.60653176465463, 41.82273845576364], [-87.60651041297386, 41.822741729379096], [-87.6064891412025, 41.82274528080366], [-87.60646795535817, 41.82274911007541], [-87.60644686148913, 41.82275321453169], [-87.60642586802022, 41.8227575942258], [-87.60640497858236, 41.82276224738011], [-87.60638420162077, 41.82276717224742], [-87.6063635431735, 41.82277236706532], [-87.60634300805471, 41.82277783186432], [-87.60632260352641, 41.82278356308904], [-87.60630233682008, 41.822789559885024], [-87.60628221277028, 41.82279582048222], [-87.60626223741507, 41.82280234311821], [-87.6062424168028, 41.822809125130334], [-87.60622275817514, 41.8228161647638], [-87.60620326757022, 41.822823460256195], [-87.60618394862924, 41.82283100892967], [-87.6061357829986, 41.82285126887031], [-87.60489865036251, 41.82326907790459], [-87.60488618404133, 41.823273092730936], [-87.60487521949304, 41.823276932508655], [-87.60486278852834, 41.823281650728966], [-87.60484930661205, 41.82328723021869], [-87.60483704714119, 41.823292747232735], [-87.6048271855152, 41.82329751145608], [-87.6048184078212, 41.8233020088474], [-87.60481037940755, 41.823306348027266], [-87.60480191461397, 41.82331116882633], [-87.60479333766806, 41.82331632654415], [-87.6047855007208, 41.823321295379984], [-87.6047572327323, 41.823341526083084], [-87.60471652058943, 41.82336869605984], [-87.60470052458207, 41.823382623822745], [-87.60468485482315, 41.82339675893244], [-87.60466951859557, 41.82341109603318], [-87.60465451835765, 41.823425630638965], [-87.6046398601683, 41.82344035918691], [-87.60462554648588, 41.82345527719107], [-87.60461158337955, 41.82347038018828], [-87.60459797573527, 41.82348566190726], [-87.60458472599103, 41.823501119662524], [-87.60457183902265, 41.82351674808307], [-87.60455931849212, 41.82353254269051], [-87.6045471692855, 41.82354849721349], [-87.60453539263716, 41.823564608958954], [-87.60452399584045, 41.823580871670806], [-87.60451297774297, 41.82359728084015], [-87.60450234562784, 41.82361383111117], [-87.60449210196373, 41.8236305170976], [-87.60448224799534, 41.823647335206], [-87.60447278860879, 41.823664279165065], [-87.60446372506924, 41.823681343580795], [-87.60445506224238, 41.82369852398245], [-87.6044468013934, 41.823715814976026], [-87.6044389437976, 41.82373321026731], [-87.60443149431059, 41.82375070628574], [-87.60442445419751, 41.823768297637386], [-87.6044178259476, 41.823785977135316], [-87.6044116108056, 41.823803741186076], [-87.60440581126073, 41.82382158260278], [-87.60440042855778, 41.823839497791994], [-87.60439546517577, 41.82385748046702], [-87.60439092117632, 41.823875525226285], [-87.60438680023185, 41.823893626690996], [-87.60438310121057, 41.82391177855161], [-87.60437982657116, 41.82392997632201], [-87.60437697757878, 41.82394821460817], [-87.60437455311194, 41.82396648620023], [-87.60437255682261, 41.82398478752], [-87.60437098758929, 41.824003111357584], [-87.60436926671751, 41.82403533381279], [-87.60435230548126, 41.82416287487605]]]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DREXEL BLVD</t>
+          <t>COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DREXEL</t>
+          <t>COTTAGE GROVE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -17438,22 +17438,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>E HYDE PARK BLVD</t>
+          <t>E PERSHING RD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>E OAKWOOD BLVD</t>
+          <t>E 35TH ST</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Buffered Bike Lane</t>
+          <t>Bike Lane</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.44027790321</t>
+          <t>0.535169697043</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -17473,19 +17473,19 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[[[-87.6061357829986, 41.82285126887031], [-87.60609798571573, 41.82276399646166], [-87.60590091255791, 41.82238247366579], [-87.60556669332729, 41.8218485016191], [-87.60530502182334, 41.82143367779866], [-87.60503607482781, 41.82100731247258], [-87.6048651023532, 41.820736412610586], [-87.60468547053425, 41.82045272301633], [-87.60449083328942, 41.820146654278034], [-87.6044256482468, 41.820039488053965], [-87.60440298975179, 41.8199636312076], [-87.60436493891923, 41.819611683642336], [-87.60429991730739, 41.819055419679465], [-87.60429380433658, 41.81900362340333], [-87.60426189555417, 41.8187247681738], [-87.60423424833219, 41.81848098336986], [-87.60420878995686, 41.81825126419623], [-87.60417455131629, 41.817968413673675], [-87.60415552556421, 41.81781123864321], [-87.60413394449134, 41.81761153828346], [-87.60411028125793, 41.81739508449601], [-87.6040885112337, 41.8171992256062], [-87.6040700938691, 41.81703439693089], [-87.60405800489534, 41.81683774595473], [-87.60404268597567, 41.816588553468314], [-87.60403709666593, 41.81630849303128], [-87.60403120520014, 41.8160161354863], [-87.60402385839835, 41.81570661792346], [-87.6040170517352, 41.81545621443974], [-87.60400794890579, 41.81501570099713], [-87.60400263005133, 41.814758282399495], [-87.6039971166536, 41.8145069813334], [-87.60399159427311, 41.81425010973378], [-87.60398593909036, 41.81399836927459], [-87.60398044110272, 41.813765236437085], [-87.60397499985255, 41.81352699896516], [-87.60396816319397, 41.813199599950835], [-87.60396389986742, 41.8129954454885], [-87.60395896340789, 41.81276777679964], [-87.60395507075744, 41.812587068895915], [-87.60395103323813, 41.81239971908291], [-87.60394749744123, 41.81224261431615], [-87.60394634625938, 41.812192497109486], [-87.60394481883999, 41.812126322466376], [-87.60393970922209, 41.8119040592473], [-87.60393553325102, 41.81172255360749], [-87.60392887286369, 41.811376458031624], [-87.60392551762324, 41.81120206585357], [-87.6039220751111, 41.811026987049004], [-87.60391755623571, 41.81080453486339], [-87.60391271281719, 41.810565396211956], [-87.60390920747359, 41.810395859547214], [-87.60390545674095, 41.810224510714114], [-87.6039029260037, 41.810108878818895], [-87.60389805780825, 41.80989781291501], [-87.60389154426316, 41.80955704103505], [-87.60388737756344, 41.80933909368288], [-87.6038839679615, 41.80921055686321], [-87.60387961854272, 41.80904658706937], [-87.60387371153965, 41.80877837916568], [-87.60386741299754, 41.80847998089812], [-87.60386217213637, 41.80822741989517], [-87.60385829065206, 41.80802316594071], [-87.60385239269901, 41.80773868420216], [-87.60384783613233, 41.80751883906607], [-87.60384274399121, 41.807243419051346], [-87.60383646805631, 41.80693986273583], [-87.60383088501047, 41.80664640914328], [-87.6038268275711, 41.80644791716319], [-87.60381920996646, 41.8061785179137], [-87.60381478491121, 41.80591612025036], [-87.60381184231792, 41.80574166480126], [-87.60380626616268, 41.80551868439242], [-87.60380179621455, 41.80533089313059], [-87.60379613662855, 41.80512799991602], [-87.60379079943327, 41.80490019151557], [-87.6037865313686, 41.80469439808748], [-87.6037805331614, 41.80445368703591], [-87.60377677465617, 41.804267683853766], [-87.60377404877609, 41.80410075937107], [-87.60377006455334, 41.80385690535313], [-87.60376813499602, 41.80374251152941], [-87.60376478430065, 41.80361114875377], [-87.60375648729162, 41.803366141884204], [-87.60375141035728, 41.80319294589922], [-87.60374820447251, 41.803022835593254], [-87.60374626819105, 41.80289938597228], [-87.60374406398431, 41.80276709679405], [-87.603741005496, 41.802597042333126], [-87.60377786306702, 41.802278554577875]]]</t>
+          <t>[[[-87.61062764640718, 41.83117833227938], [-87.61056121164148, 41.8309831537708], [-87.61049735143008, 41.83088969918398], [-87.61035664310229, 41.830683783743886], [-87.61021807070779, 41.83042154772161], [-87.60976457816737, 41.82954607123712], [-87.60957313929535, 41.82921206775326], [-87.60953484063897, 41.829123898452686], [-87.60947872228488, 41.82899470323354], [-87.60920191148996, 41.828461613639654], [-87.60903435707688, 41.82813505890052], [-87.60893989467102, 41.82795095517259], [-87.60881964632634, 41.82771437489353], [-87.60875245248874, 41.82758217879819], [-87.60848246060718, 41.827057116463294], [-87.60835626491398, 41.82681471429994], [-87.6082719086208, 41.82665265487381], [-87.60807609502977, 41.82626881297509], [-87.60797191429859, 41.82606348435161], [-87.6079087205916, 41.82593893804116], [-87.60784009873232, 41.82580134557496], [-87.60760573951933, 41.82534195692333], [-87.60750781352307, 41.825147209548874], [-87.6073738248817, 41.824880744701375], [-87.60728073042753, 41.82469689396191], [-87.6071500174633, 41.824439506146774], [-87.60686734794898, 41.8239569091955]]]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MARTIN LUTHER KING JR DR</t>
+          <t>31ST DR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MARTIN LUTHER KING JR</t>
+          <t>31ST</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -17495,22 +17495,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>E GARFIELD BLVD</t>
+          <t>S MOE DR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>E 51ST ST</t>
+          <t>S FORT DEARBORN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.525487613949</t>
+          <t>0.112279352219</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -17530,19 +17530,19 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[[[-87.61610503358958, 41.80209463506868], [-87.6161372553474, 41.80190169269912], [-87.61614074146709, 41.80158907436339], [-87.61612777562215, 41.80089368105505], [-87.61611061011892, 41.80022228554601], [-87.6161072447521, 41.80009063210527], [-87.61609367670414, 41.799567542526496], [-87.61608066594823, 41.799007655365806], [-87.61607252526402, 41.798655650381], [-87.61607043851457, 41.798547458174994], [-87.6160678890834, 41.798457127876596], [-87.61605837110685, 41.79805028367454], [-87.61604192712679, 41.79739045646684], [-87.6160235286314, 41.79670545121182], [-87.61602194699849, 41.79663990734271], [-87.61601550198797, 41.7963728214937], [-87.61599616418324, 41.79563948379497], [-87.61599287316523, 41.795514680599055], [-87.61597940877292, 41.795011981545464], [-87.6159753641248, 41.794792923748744], [-87.6159725954511, 41.7946429706259], [-87.61596722873355, 41.79447924837816]]]</t>
+          <t>[[[-87.60986250664294, 41.83853270823932], [-87.6095086258396, 41.83853049214663], [-87.60918890021458, 41.83853812491465], [-87.60875811449299, 41.83854840731297], [-87.60865431875239, 41.83855088477592], [-87.60833750976242, 41.838558445341555], [-87.60824493561356, 41.83856065473611], [-87.60779764356145, 41.83857132811791], [-87.60768798164275, 41.83857394411922]]]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>31ST ST</t>
+          <t>OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>31ST</t>
+          <t>OAKWOOD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -17552,22 +17552,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>E PERSHING RD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S MOE DR</t>
+          <t>LAKESHORE DR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.374564177222</t>
+          <t>0.265190300727</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -17587,19 +17587,19 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>[[[-87.61711743673902, 41.83841544388878], [-87.61349382112748, 41.83846417399243], [-87.61336507987872, 41.8384654324603], [-87.61170778684063, 41.8384964974145], [-87.6113260948113, 41.838513422816135], [-87.61122239818451, 41.83851802083818], [-87.61106328407865, 41.83852507577069], [-87.61079286825503, 41.83852833767229], [-87.61023646107017, 41.83853504871899], [-87.61004517815752, 41.83853385151719], [-87.60986250664294, 41.83853270823932]]]</t>
+          <t>[[[-87.60435230548126, 41.82416287487605], [-87.60430631831143, 41.82416402356607], [-87.60428716161914, 41.824162095879494], [-87.60426796236939, 41.824160418216486], [-87.60424872656984, 41.824158991515496], [-87.6042294614419, 41.82415781582236], [-87.60421017058603, 41.824156892060216], [-87.60419086242726, 41.824156220282596], [-87.60417154057622, 41.82415580051237], [-87.60415221225436, 41.824155632795396], [-87.60413288226572, 41.82415571806249], [-87.60411355904553, 41.824156055466894], [-87.60409424500084, 41.824156645023855], [-87.60407494855669, 41.82415748678687], [-87.60405567333392, 41.82415857987863], [-87.60403642775758, 41.82415992435258], [-87.60401721664196, 41.82416152023936], [-87.60399804481145, 41.82416336666922], [-87.60397216606508, 41.82416626443172], [-87.60346372774372, 41.82428645007398], [-87.60283279718537, 41.82449961768677], [-87.60254227296632, 41.82459826474106], [-87.60246449645898, 41.82463065780316], [-87.60214041957721, 41.82476563187484], [-87.6020952755735, 41.8247849900892], [-87.6017964676506, 41.824913114836825], [-87.60160828555927, 41.824988222508935], [-87.60150680968545, 41.82502872373627], [-87.60091462496219, 41.825188150840695], [-87.60074975423764, 41.82519086558529], [-87.60046891563478, 41.82526537949098], [-87.60036960542857, 41.82529172834911], [-87.60027660609322, 41.82531640313449], [-87.59999145364394, 41.825392060591405], [-87.59984691458156, 41.8254304090753], [-87.5996240077739, 41.825489550046555], [-87.5995963400068, 41.82550927640572]]]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>33RD ST</t>
+          <t>31ST ST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>33RD</t>
+          <t>31ST</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -17609,22 +17609,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>S STATE ST</t>
+          <t>S MICHIGAN AVE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>S GILES AVE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marked Shared Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.47034639757</t>
+          <t>0.204433765585</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -17644,19 +17644,19 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[[[-87.62649453439884, 41.834657620039394], [-87.6261375484813, 41.834653255468275], [-87.62598820768505, 41.834655523097894], [-87.6258713558933, 41.83465729648271], [-87.62555479911322, 41.834663112644094], [-87.62521987635559, 41.834667222892755], [-87.62505539738287, 41.834670172980104], [-87.62490108129768, 41.834672941521305], [-87.62458217233613, 41.834675666707916], [-87.62423396810284, 41.83467955437231], [-87.62419467526055, 41.83468228203092], [-87.62332410153712, 41.834694699177206], [-87.6225766889668, 41.834705354550316], [-87.62204427228347, 41.83471294207457], [-87.62183407802331, 41.834710293288616], [-87.62162465056676, 41.834707653371126], [-87.62122627094816, 41.83471231672194], [-87.62080305524594, 41.834717269393636], [-87.62061503357474, 41.834712419521736], [-87.62049200866362, 41.83470924673693], [-87.6196388712932, 41.834730650392935], [-87.61940523053126, 41.834732824088015], [-87.61923746068237, 41.8347343849626], [-87.61879845501683, 41.83473992804518], [-87.61849043146212, 41.83474381686139], [-87.61818788325031, 41.83474705287812], [-87.61738398483341, 41.83475564899769]]]</t>
+          <t>[[[-87.62343694336933, 41.83833704540958], [-87.62323358361407, 41.83833847406264], [-87.6219191008301, 41.838356765893344], [-87.62177979242179, 41.83835870302541], [-87.62128211303167, 41.83836481491048], [-87.62100750971918, 41.8383681865488], [-87.62063024755903, 41.83837298145963], [-87.62047048387781, 41.83837500885838], [-87.62015738391769, 41.83837922174425], [-87.61999021695806, 41.83838147080919], [-87.61947655373596, 41.838387441384285]]]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OAKWOOD BLVD</t>
+          <t>35TH ST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OAKWOOD</t>
+          <t>35TH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -17666,12 +17666,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>S COTTAGE GROVE AVE</t>
+          <t>S INDIANA AVE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>E PERSHING RD</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.179532699715</t>
+          <t>0.247640012693</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -17701,19 +17701,19 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[[[-87.60684961994563, 41.822720681391324], [-87.60679180817826, 41.82272115395717], [-87.60677001340125, 41.82272103500519], [-87.60674821900858, 41.82272120146208], [-87.60672643224186, 41.822721651572905], [-87.60670465910856, 41.822722386276055], [-87.60668290562634, 41.822723405609615], [-87.60666118024034, 41.82272470782627], [-87.60663948895807, 41.82272629386447], [-87.60661783660379, 41.82272816285434], [-87.60659623160228, 41.822730314849224], [-87.60657467999161, 41.822732748086665], [-87.60655318900317, 41.82273546171211], [-87.60653176465463, 41.82273845576364], [-87.60651041297386, 41.822741729379096], [-87.6064891412025, 41.82274528080366], [-87.60646795535817, 41.82274911007541], [-87.60644686148913, 41.82275321453169], [-87.60642586802022, 41.8227575942258], [-87.60640497858236, 41.82276224738011], [-87.60638420162077, 41.82276717224742], [-87.6063635431735, 41.82277236706532], [-87.60634300805471, 41.82277783186432], [-87.60632260352641, 41.82278356308904], [-87.60630233682008, 41.822789559885024], [-87.60628221277028, 41.82279582048222], [-87.60626223741507, 41.82280234311821], [-87.6062424168028, 41.822809125130334], [-87.60622275817514, 41.8228161647638], [-87.60620326757022, 41.822823460256195], [-87.60618394862924, 41.82283100892967], [-87.6061357829986, 41.82285126887031], [-87.60489865036251, 41.82326907790459], [-87.60488618404133, 41.823273092730936], [-87.60487521949304, 41.823276932508655], [-87.60486278852834, 41.823281650728966], [-87.60484930661205, 41.82328723021869], [-87.60483704714119, 41.823292747232735], [-87.6048271855152, 41.82329751145608], [-87.6048184078212, 41.8233020088474], [-87.60481037940755, 41.823306348027266], [-87.60480191461397, 41.82331116882633], [-87.60479333766806, 41.82331632654415], [-87.6047855007208, 41.823321295379984], [-87.6047572327323, 41.823341526083084], [-87.60471652058943, 41.82336869605984], [-87.60470052458207, 41.823382623822745], [-87.60468485482315, 41.82339675893244], [-87.60466951859557, 41.82341109603318], [-87.60465451835765, 41.823425630638965], [-87.6046398601683, 41.82344035918691], [-87.60462554648588, 41.82345527719107], [-87.60461158337955, 41.82347038018828], [-87.60459797573527, 41.82348566190726], [-87.60458472599103, 41.823501119662524], [-87.60457183902265, 41.82351674808307], [-87.60455931849212, 41.82353254269051], [-87.6045471692855, 41.82354849721349], [-87.60453539263716, 41.823564608958954], [-87.60452399584045, 41.823580871670806], [-87.60451297774297, 41.82359728084015], [-87.60450234562784, 41.82361383111117], [-87.60449210196373, 41.8236305170976], [-87.60448224799534, 41.823647335206], [-87.60447278860879, 41.823664279165065], [-87.60446372506924, 41.823681343580795], [-87.60445506224238, 41.82369852398245], [-87.6044468013934, 41.823715814976026], [-87.6044389437976, 41.82373321026731], [-87.60443149431059, 41.82375070628574], [-87.60442445419751, 41.823768297637386], [-87.6044178259476, 41.823785977135316], [-87.6044116108056, 41.823803741186076], [-87.60440581126073, 41.82382158260278], [-87.60440042855778, 41.823839497791994], [-87.60439546517577, 41.82385748046702], [-87.60439092117632, 41.823875525226285], [-87.60438680023185, 41.823893626690996], [-87.60438310121057, 41.82391177855161], [-87.60437982657116, 41.82392997632201], [-87.60437697757878, 41.82394821460817], [-87.60437455311194, 41.82396648620023], [-87.60437255682261, 41.82398478752], [-87.60437098758929, 41.824003111357584], [-87.60436926671751, 41.82403533381279], [-87.60435230548126, 41.82416287487605]]]</t>
+          <t>[[[-87.62175790723948, 41.83105114677236], [-87.62147204346718, 41.83105439399251], [-87.62114680081156, 41.83105756560645], [-87.62071506301695, 41.83106177458682], [-87.62054500801808, 41.83106270827247], [-87.62038410991939, 41.83106359050268], [-87.61993842551381, 41.831068138560155], [-87.61959497831648, 41.83107164288365], [-87.61932790430228, 41.83107429835225], [-87.6192145415096, 41.83107542490796], [-87.61861331357758, 41.831080192721124], [-87.61840049624368, 41.8310834879503], [-87.61811354507196, 41.8310879292089], [-87.61794575632707, 41.83109052619566], [-87.61760482133919, 41.83109575717714], [-87.61730766754923, 41.83109415363711], [-87.61696083107093, 41.83109228088914]]]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COTTAGE GROVE AVE</t>
+          <t>35TH ST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COTTAGE GROVE</t>
+          <t>35TH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -17723,22 +17723,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>E PERSHING RD</t>
+          <t>S STATE ST</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>E 35TH ST</t>
+          <t>S INDIANA AVE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Marked Shared Lane</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.535169697043</t>
+          <t>0.251982034456</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -17758,19 +17758,19 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[[[-87.61062764640718, 41.83117833227938], [-87.61056121164148, 41.8309831537708], [-87.61049735143008, 41.83088969918398], [-87.61035664310229, 41.830683783743886], [-87.61021807070779, 41.83042154772161], [-87.60976457816737, 41.82954607123712], [-87.60957313929535, 41.82921206775326], [-87.60953484063897, 41.829123898452686], [-87.60947872228488, 41.82899470323354], [-87.60920191148996, 41.828461613639654], [-87.60903435707688, 41.82813505890052], [-87.60893989467102, 41.82795095517259], [-87.60881964632634, 41.82771437489353], [-87.60875245248874, 41.82758217879819], [-87.60848246060718, 41.827057116463294], [-87.60835626491398, 41.82681471429994], [-87.6082719086208, 41.82665265487381], [-87.60807609502977, 41.82626881297509], [-87.60797191429859, 41.82606348435161], [-87.6079087205916, 41.82593893804116], [-87.60784009873232, 41.82580134557496], [-87.60760573951933, 41.82534195692333], [-87.60750781352307, 41.825147209548874], [-87.6073738248817, 41.824880744701375], [-87.60728073042753, 41.82469689396191], [-87.6071500174633, 41.824439506146774], [-87.60686734794898, 41.8239569091955]]]</t>
+          <t>[[[-87.6266385987239, 41.83100580881331], [-87.6264732958851, 41.83101107967687], [-87.62623318245583, 41.83101873668085], [-87.62601026219642, 41.831016431371204], [-87.62591536563151, 41.83101335928809], [-87.62580089456586, 41.83100965335254], [-87.62578894519758, 41.8310097769209], [-87.62528748091881, 41.83101497359384], [-87.62497040535462, 41.83101825860181], [-87.62460523369673, 41.83102204008217], [-87.62425145860854, 41.831023753331884], [-87.62423505388152, 41.83102409322796], [-87.62325146933688, 41.831035886002816], [-87.623068985482, 41.831038072800894], [-87.62257009356864, 41.831042925980455], [-87.62249985576759, 41.831043609555515], [-87.62195505561091, 41.831048907025604], [-87.62175790723948, 41.83105114677236]]]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>31ST DR</t>
+          <t>PERSHING RD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>31ST</t>
+          <t>PERSHING</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -17780,22 +17780,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>S MOE DR</t>
+          <t>S MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S FORT DEARBORN</t>
+          <t>S COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Buffered Bike Lane</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.112279352219</t>
+          <t>0.52273584865</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -17815,19 +17815,19 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>[[[-87.60986250664294, 41.83853270823932], [-87.6095086258396, 41.83853049214663], [-87.60918890021458, 41.83853812491465], [-87.60875811449299, 41.83854840731297], [-87.60865431875239, 41.83855088477592], [-87.60833750976242, 41.838558445341555], [-87.60824493561356, 41.83856065473611], [-87.60779764356145, 41.83857132811791], [-87.60768798164275, 41.83857394411922]]]</t>
+          <t>[[[-87.61699111101917, 41.82382621643897], [-87.61672658426848, 41.823830247623874], [-87.61611742079225, 41.823839530348515], [-87.61610351380473, 41.8238397010112], [-87.6154691158385, 41.82384748030514], [-87.61514202830347, 41.82385149048068], [-87.61435832379438, 41.82386109676443], [-87.61307015328607, 41.82387688472249], [-87.61261856025574, 41.82388291330555], [-87.61213034165046, 41.82388942863265], [-87.61127647198559, 41.82389814834697], [-87.61055372981066, 41.82390552337138], [-87.60983565600785, 41.82391284582243], [-87.60958135685671, 41.82391543849396], [-87.6083907741053, 41.82392832878097], [-87.60833202655425, 41.82392896457945], [-87.60732163043673, 41.82394102449633], [-87.60702288161544, 41.823950057947265], [-87.60691033374472, 41.82395217241693], [-87.60686734794898, 41.8239569091955]]]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OAKWOOD BLVD</t>
+          <t>PERSHING RD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OAKWOOD</t>
+          <t>PERSHING</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -17837,12 +17837,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>E PERSHING RD</t>
+          <t>S COTTAGE GROVE AVE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LAKESHORE DR</t>
+          <t>E OAKWOOD BLVD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.265190300727</t>
+          <t>0.135533728291</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[[[-87.60435230548126, 41.82416287487605], [-87.60430631831143, 41.82416402356607], [-87.60428716161914, 41.824162095879494], [-87.60426796236939, 41.824160418216486], [-87.60424872656984, 41.824158991515496], [-87.6042294614419, 41.82415781582236], [-87.60421017058603, 41.824156892060216], [-87.60419086242726, 41.824156220282596], [-87.60417154057622, 41.82415580051237], [-87.60415221225436, 41.824155632795396], [-87.60413288226572, 41.82415571806249], [-87.60411355904553, 41.824156055466894], [-87.60409424500084, 41.824156645023855], [-87.60407494855669, 41.82415748678687], [-87.60405567333392, 41.82415857987863], [-87.60403642775758, 41.82415992435258], [-87.60401721664196, 41.82416152023936], [-87.60399804481145, 41.82416336666922], [-87.60397216606508, 41.82416626443172], [-87.60346372774372, 41.82428645007398], [-87.60283279718537, 41.82449961768677], [-87.60254227296632, 41.82459826474106], [-87.60246449645898, 41.82463065780316], [-87.60214041957721, 41.82476563187484], [-87.6020952755735, 41.8247849900892], [-87.6017964676506, 41.824913114836825], [-87.60160828555927, 41.824988222508935], [-87.60150680968545, 41.82502872373627], [-87.60091462496219, 41.825188150840695], [-87.60074975423764, 41.82519086558529], [-87.60046891563478, 41.82526537949098], [-87.60036960542857, 41.82529172834911], [-87.60027660609322, 41.82531640313449], [-87.59999145364394, 41.825392060591405], [-87.59984691458156, 41.8254304090753], [-87.5996240077739, 41.825489550046555], [-87.5995963400068, 41.82550927640572]]]</t>
+          <t>[[[-87.60686734794898, 41.8239569091955], [-87.60606651814183, 41.82417374136248], [-87.60576295911753, 41.82426465478336], [-87.60574292254485, 41.82427037292759], [-87.60572275653709, 41.824275828247], [-87.60570246591914, 41.82428101987172], [-87.60568205673985, 41.82428594513898], [-87.60566153743501, 41.824290603201796], [-87.60564091042225, 41.82429499317505], [-87.60562018535114, 41.824299113319164], [-87.60559936705677, 41.82430296186401], [-87.6055784615575, 41.824306538847644], [-87.60555747730946, 41.8243098416226], [-87.60553641792379, 41.8243128702117], [-87.60551529184642, 41.824315622867694], [-87.6054675496305, 41.82432080616751], [-87.60514959326278, 41.82431298815248], [-87.60506702606838, 41.82430186758017], [-87.60498473109828, 41.8242896709576], [-87.60490273359159, 41.824276402046785], [-87.60482105759388, 41.82426206370194], [-87.60473921548223, 41.8242465609951], [-87.6045999908213, 41.824210864913994], [-87.60435230548126, 41.82416287487605]]]</t>
         </is>
       </c>
     </row>
@@ -17894,12 +17894,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>S MICHIGAN AVE</t>
+          <t>S GILES AVE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S GILES AVE</t>
+          <t>S DR MARTIN LUTHER KING JR DR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.204433765585</t>
+          <t>0.121774289186</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -17929,19 +17929,19 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[[[-87.62343694336933, 41.83833704540958], [-87.62323358361407, 41.83833847406264], [-87.6219191008301, 41.838356765893344], [-87.62177979242179, 41.83835870302541], [-87.62128211303167, 41.83836481491048], [-87.62100750971918, 41.8383681865488], [-87.62063024755903, 41.83837298145963], [-87.62047048387781, 41.83837500885838], [-87.62015738391769, 41.83837922174425], [-87.61999021695806, 41.83838147080919], [-87.61947655373596, 41.838387441384285]]]</t>
+          <t>[[[-87.61947655373596, 41.838387441384285], [-87.61826297733084, 41.83840128373133], [-87.61746126495309, 41.838411426314124], [-87.61711743673902, 41.83841544388878]]]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>35TH ST</t>
+          <t>PAYNE DR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35TH</t>
+          <t>PAYNE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -17951,22 +17951,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>S INDIANA AVE</t>
+          <t>E RAINEY DR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>E 55TH ST</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bike Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.247640012693</t>
+          <t>0.0675160768248</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -17986,54 +17986,54 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[[[-87.62175790723948, 41.83105114677236], [-87.62147204346718, 41.83105439399251], [-87.62114680081156, 41.83105756560645], [-87.62071506301695, 41.83106177458682], [-87.62054500801808, 41.83106270827247], [-87.62038410991939, 41.83106359050268], [-87.61993842551381, 41.831068138560155], [-87.61959497831648, 41.83107164288365], [-87.61932790430228, 41.83107429835225], [-87.6192145415096, 41.83107542490796], [-87.61861331357758, 41.831080192721124], [-87.61840049624368, 41.8310834879503], [-87.61811354507196, 41.8310879292089], [-87.61794575632707, 41.83109052619566], [-87.61760482133919, 41.83109575717714], [-87.61730766754923, 41.83109415363711], [-87.61696083107093, 41.83109228088914]]]</t>
+          <t>[[[-87.60737728719235, 41.79496310174033], [-87.60739572258301, 41.79490141710621], [-87.60759032740498, 41.794597181214684], [-87.60781895881487, 41.79429315897816], [-87.60788597312641, 41.79420071616683], [-87.60793532745689, 41.79414594962413], [-87.60799024123432, 41.794105496864226]]]</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>35TH ST</t>
+          <t>55TH PL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>35TH</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>S STATE ST</t>
+          <t>E 55TH ST</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S INDIANA AVE</t>
+          <t>S DORCHESTER AVE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Marked Shared Lane</t>
+          <t>Protected Bike Lane</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.251982034456</t>
+          <t>0.0456951713071</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2W</t>
+          <t>1W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -18043,34 +18043,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[[[-87.6266385987239, 41.83100580881331], [-87.6264732958851, 41.83101107967687], [-87.62623318245583, 41.83101873668085], [-87.62601026219642, 41.831016431371204], [-87.62591536563151, 41.83101335928809], [-87.62580089456586, 41.83100965335254], [-87.62578894519758, 41.8310097769209], [-87.62528748091881, 41.83101497359384], [-87.62497040535462, 41.83101825860181], [-87.62460523369673, 41.83102204008217], [-87.62425145860854, 41.831023753331884], [-87.62423505388152, 41.83102409322796], [-87.62325146933688, 41.831035886002816], [-87.623068985482, 41.831038072800894], [-87.62257009356864, 41.831042925980455], [-87.62249985576759, 41.831043609555515], [-87.62195505561091, 41.831048907025604], [-87.62175790723948, 41.83105114677236]]]</t>
+          <t>[[[-87.59230182841584, 41.795115630665705], [-87.59228479651814, 41.79504607209104], [-87.59225548130618, 41.79497654411554], [-87.59219846154255, 41.79489528677071], [-87.59216267495331, 41.79487450803364], [-87.5920133591238, 41.794803290937494], [-87.59193680903836, 41.794782379617466], [-87.59185276036327, 41.794775717447465], [-87.59167067344248, 41.79477653357941]]]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PERSHING RD</t>
+          <t>55TH PL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PERSHING</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>S MARTIN LUTHER KING JR DR</t>
+          <t>S DORCHESTER AVE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S COTTAGE GROVE AVE</t>
+          <t>E 55TH ST</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -18080,17 +18080,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.52273584865</t>
+          <t>0.144696496175</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2W</t>
+          <t>1W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -18100,19 +18100,19 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[[[-87.61699111101917, 41.82382621643897], [-87.61672658426848, 41.823830247623874], [-87.61611742079225, 41.823839530348515], [-87.61610351380473, 41.8238397010112], [-87.6154691158385, 41.82384748030514], [-87.61514202830347, 41.82385149048068], [-87.61435832379438, 41.82386109676443], [-87.61307015328607, 41.82387688472249], [-87.61261856025574, 41.82388291330555], [-87.61213034165046, 41.82388942863265], [-87.61127647198559, 41.82389814834697], [-87.61055372981066, 41.82390552337138], [-87.60983565600785, 41.82391284582243], [-87.60958135685671, 41.82391543849396], [-87.6083907741053, 41.82392832878097], [-87.60833202655425, 41.82392896457945], [-87.60732163043673, 41.82394102449633], [-87.60702288161544, 41.823950057947265], [-87.60691033374472, 41.82395217241693], [-87.60686734794898, 41.8239569091955]]]</t>
+          <t>[[[-87.59167067344248, 41.79477653357941], [-87.59136866354801, 41.79477788763556], [-87.59102905319932, 41.7947802494273], [-87.5907804071988, 41.794781030192134], [-87.59057041516495, 41.79478167500291], [-87.59032230194119, 41.79478403653916], [-87.59011020296843, 41.79478605342406], [-87.58985624501801, 41.79478954209586], [-87.58964247007485, 41.794793948510694], [-87.58954419795131, 41.79480903782709], [-87.5894761210009, 41.79482602245259], [-87.5894100443973, 41.7948539709812], [-87.58930529537159, 41.794916096688844], [-87.58922782297005, 41.79504082853871], [-87.58920177375734, 41.79511475522187], [-87.58919925975736, 41.795164108872186], [-87.58920472557244, 41.79519313923364]]]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PERSHING RD</t>
+          <t>55TH ST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PERSHING</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -18122,12 +18122,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>S COTTAGE GROVE AVE</t>
+          <t>E 55TH PL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E OAKWOOD BLVD</t>
+          <t>S LAKE PARK AVE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.135533728291</t>
+          <t>0.0858058887654</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -18157,19 +18157,19 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[[[-87.60686734794898, 41.8239569091955], [-87.60606651814183, 41.82417374136248], [-87.60576295911753, 41.82426465478336], [-87.60574292254485, 41.82427037292759], [-87.60572275653709, 41.824275828247], [-87.60570246591914, 41.82428101987172], [-87.60568205673985, 41.82428594513898], [-87.60566153743501, 41.824290603201796], [-87.60564091042225, 41.82429499317505], [-87.60562018535114, 41.824299113319164], [-87.60559936705677, 41.82430296186401], [-87.6055784615575, 41.824306538847644], [-87.60555747730946, 41.8243098416226], [-87.60553641792379, 41.8243128702117], [-87.60551529184642, 41.824315622867694], [-87.6054675496305, 41.82432080616751], [-87.60514959326278, 41.82431298815248], [-87.60506702606838, 41.82430186758017], [-87.60498473109828, 41.8242896709576], [-87.60490273359159, 41.824276402046785], [-87.60482105759388, 41.82426206370194], [-87.60473921548223, 41.8242465609951], [-87.6045999908213, 41.824210864913994], [-87.60435230548126, 41.82416287487605]]]</t>
+          <t>[[[-87.58920472557244, 41.79519313923364], [-87.58843978013414, 41.795185708334266], [-87.58754346134559, 41.795176995453275]]]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31ST ST</t>
+          <t>55TH ST</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31ST</t>
+          <t>55TH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -18179,22 +18179,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>S GILES AVE</t>
+          <t>S LAKE PARK AVE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S DR MARTIN LUTHER KING JR DR</t>
+          <t>S HYDE PARK BLVD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Protected Bike Lane</t>
+          <t>Marked Shared Lane</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.121774289186</t>
+          <t>0.185855928634</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[[[-87.61947655373596, 41.838387441384285], [-87.61826297733084, 41.83840128373133], [-87.61746126495309, 41.838411426314124], [-87.61711743673902, 41.83841544388878]]]</t>
+          <t>[[[-87.58754346134559, 41.795176995453275], [-87.58738962534618, 41.795178680573635], [-87.58723653779546, 41.79518035774402], [-87.58718928018563, 41.79518087552708], [-87.587017867405, 41.79518275390326], [-87.58694172794344, 41.7951835872402], [-87.58690389104218, 41.795184002251354], [-87.58673557437942, 41.79518584540241], [-87.58671603381707, 41.795186059636485], [-87.58661850963912, 41.79518760010154], [-87.58616460134657, 41.79519476866744], [-87.58576988324349, 41.79519906136454], [-87.58540490313923, 41.795203699386356], [-87.58511445279412, 41.795207390147176], [-87.58484326462393, 41.795207078465104], [-87.58467848640464, 41.79520974297046], [-87.58451912941597, 41.795212320129835], [-87.58431745967604, 41.79521624722297], [-87.58394543361024, 41.795220065764205]]]</t>
         </is>
       </c>
     </row>

--- a/bronzeville_assets.xlsx
+++ b/bronzeville_assets.xlsx
@@ -16357,13 +16357,7270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No data available — check dataset ID in config.py</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>the_geom.type</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>the_geom.coordinates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[[-87.6151606, 41.8483925], [-87.6148959, 41.8477151], [-87.6145867, 41.8469169], [-87.614209, 41.846009], [-87.6138571, 41.8451778], [-87.6135723, 41.8445212], [-87.6131238, 41.8435573], [-87.6128979, 41.8430496], [-87.6123186, 41.841687], [-87.6116171, 41.8400363], [-87.6110429, 41.8386772], [-87.6104182, 41.8372166], [-87.6097378, 41.8356195], [-87.6093786, 41.8347725], [-87.6091962, 41.8343478], [-87.6090071, 41.8339276], [-87.6088656, 41.8336459], [-87.6087121, 41.8333665], [-87.6085719, 41.8331288], [-87.6084191, 41.8328922], [-87.6081777, 41.8325487], [-87.6079194, 41.8322107], [-87.6072785, 41.8313901], [-87.6066488, 41.8305665], [-87.6053336, 41.8288511], [-87.6027688, 41.8254802], [-87.60013, 41.8220317], [-87.5985838, 41.8200006], [-87.5976115, 41.818628], [-87.5952356, 41.8152299], [-87.5928738, 41.811869], [-87.5915844, 41.8100237]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>South Chicago Sub District</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[[-87.5926051, 41.7711321], [-87.592479, 41.7716769], [-87.5922952, 41.7724788], [-87.5922071, 41.7728641]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[[-87.6150721, 41.848412], [-87.6162743, 41.8512881], [-87.6165931, 41.8520821], [-87.6166152, 41.8521318], [-87.6172044, 41.8534124], [-87.6172453, 41.853551], [-87.6172853, 41.8537776], [-87.617292, 41.8540369], [-87.6172768, 41.854209], [-87.6172599, 41.8542787], [-87.6171767, 41.8546403], [-87.6170695, 41.8551077], [-87.6170338, 41.8554506]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[[-87.6170338, 41.8554506], [-87.6170516, 41.8557395], [-87.6170865, 41.8559206], [-87.6171454, 41.8561395], [-87.6171704, 41.8562032], [-87.6172241, 41.85634], [-87.6175181, 41.8570961], [-87.6176962, 41.8575366], [-87.6177691, 41.8577339], [-87.6179534, 41.8581967], [-87.6180636, 41.8585006], [-87.6181126, 41.8586944], [-87.6181635, 41.8589481], [-87.6182072, 41.8593366], [-87.6182681, 41.8599749], [-87.6183412, 41.8605352], [-87.6183888, 41.8607919], [-87.6184747, 41.8611175], [-87.6185927, 41.8614571], [-87.6188395, 41.8620664], [-87.6191479, 41.8627935], [-87.619341, 41.863255], [-87.6194671, 41.863609], [-87.6195502, 41.8639002], [-87.6196924, 41.864434], [-87.6197997, 41.8647671], [-87.6199069, 41.8650423], [-87.6199398, 41.8651286], [-87.6203844, 41.8661893], [-87.6211598, 41.8680018], [-87.6213077, 41.8683524], [-87.6214673, 41.8687309], [-87.6216496, 41.8691853], [-87.6216803, 41.8692606], [-87.6217686, 41.8694618], [-87.621832, 41.8696063], [-87.6219971, 41.8699837], [-87.622035, 41.87007], [-87.6221349, 41.8702875]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[[-87.6171172, 41.8554309], [-87.617154, 41.8552011], [-87.6171866, 41.8550637], [-87.6173135, 41.8546461], [-87.617371, 41.8544167], [-87.6173903, 41.8542455], [-87.6173913, 41.853963], [-87.6173577, 41.853677], [-87.617334, 41.8534938], [-87.6172412, 41.85324], [-87.616707, 41.8521094], [-87.6163999, 41.8513333], [-87.6163735, 41.8512683], [-87.6151606, 41.8483925]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[[-87.6286302, 41.8018056], [-87.6286048, 41.801294], [-87.628584, 41.8005335], [-87.6285441, 41.7995482], [-87.6285059, 41.7983367], [-87.6284696, 41.7971659], [-87.6284621, 41.7968919], [-87.628442, 41.796156], [-87.6284008, 41.7947138]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[[-87.6284585, 41.7983356], [-87.6284884, 41.799553], [-87.6285245, 41.8005227], [-87.628578, 41.8018062]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[[-87.628779, 41.8001847], [-87.6286948, 41.7995246]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[[-87.6288098, 41.8018042], [-87.6288005, 41.8016063], [-87.6287898, 41.8012644], [-87.6287951, 41.8009885], [-87.6287951, 41.8007625], [-87.628779, 41.8001847], [-87.6287522, 41.7993089], [-87.6287469, 41.799101], [-87.6287429, 41.7989394], [-87.6287396, 41.7988097], [-87.6287334, 41.798565]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[[-87.6288005, 41.8016063], [-87.6288166, 41.8013844], [-87.6288514, 41.8010964], [-87.6288541, 41.8009265], [-87.62883, 41.7998427], [-87.6288005, 41.7987979]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[[-87.6290714, 41.8075984], [-87.6291139, 41.8073286], [-87.6291104, 41.8071347], [-87.6290756, 41.8068567], [-87.6290367, 41.8066735], [-87.6289753, 41.8063944], [-87.6289537, 41.8062332], [-87.628895, 41.8046834], [-87.6288815, 41.8037167], [-87.6288609, 41.8034033], [-87.6288313, 41.802671]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[[-87.6288313, 41.802671], [-87.6288161, 41.802]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[[-87.6286364, 41.802013], [-87.6286302, 41.8018056]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[[-87.6289373, 41.8083242], [-87.6289534, 41.8080803], [-87.6289748, 41.8079563], [-87.6290124, 41.8078184], [-87.6290499, 41.8076724], [-87.6290714, 41.8075984], [-87.6291787, 41.8072346], [-87.6292216, 41.8070706], [-87.6292545, 41.8068507], [-87.629336, 41.8064743], [-87.6293591, 41.8063369], [-87.6293815, 41.8060873], [-87.6293822, 41.8060487], [-87.6293937, 41.8058914], [-87.6294108, 41.8057678], [-87.6294307, 41.8056828], [-87.629502, 41.8054865], [-87.629561, 41.8053585], [-87.6296201, 41.8052211], [-87.6296568, 41.8050833], [-87.6296817, 41.8049167], [-87.6296817, 41.8048305], [-87.629696, 41.8046438], [-87.6297256, 41.8045036], [-87.6298441, 41.8042191], [-87.62989, 41.8040852], [-87.6299383, 41.8038797], [-87.6299687, 41.8036326], [-87.62995, 41.8028267]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[[-87.6290275, 41.808263], [-87.6290159, 41.8080183], [-87.6290177, 41.8079063], [-87.6290258, 41.8078304], [-87.6290499, 41.8076724]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[[-87.6290275, 41.808263], [-87.6290418, 41.808041], [-87.6290775, 41.8078543], [-87.6291304, 41.8076504], [-87.6292913, 41.8071326], [-87.6293182, 41.8070166], [-87.6293447, 41.8067669], [-87.6293454, 41.8067383]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[[-87.6290575, 41.8090684], [-87.6290297, 41.808336]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[[-87.6287848, 41.8092962], [-87.6287888, 41.8094696], [-87.6288006, 41.8099181], [-87.6288058, 41.8101415], [-87.6288129, 41.810364], [-87.6288681, 41.8122889], [-87.6289797, 41.8163575]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[[-87.6287786, 41.8090899], [-87.6287848, 41.8092962]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[[-87.628578, 41.8018062], [-87.6285842, 41.802013]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[[-87.6285842, 41.802013], [-87.6286197, 41.803409], [-87.6286641, 41.8050809], [-87.628701, 41.8062934], [-87.6287239, 41.8076032], [-87.6287443, 41.808128], [-87.6287596, 41.8085197], [-87.6287701, 41.8088629], [-87.6287786, 41.8090899]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[[-87.6288361, 41.8092959], [-87.6288308, 41.8090899]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[[-87.6290653, 41.8092863], [-87.6290591, 41.8090868]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[[-87.6289863, 41.8118123], [-87.6289729, 41.8109677], [-87.6289782, 41.8107778], [-87.628997, 41.810372], [-87.6289812, 41.8097704], [-87.6289706, 41.8092875]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[[-87.6290325, 41.8163575], [-87.6289478, 41.8131105], [-87.6288979, 41.8115056], [-87.6288827, 41.8109938], [-87.6288755, 41.8107613], [-87.6288658, 41.8102657], [-87.6288361, 41.8092959]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[[-87.6288308, 41.8090899], [-87.6287534, 41.8062387], [-87.628714, 41.8050768], [-87.6286727, 41.8034033], [-87.6286364, 41.802013]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[[-87.6291943, 41.8193526], [-87.6292434, 41.8197169], [-87.6292651, 41.8200492], [-87.6292645, 41.8202407]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[[-87.6291863, 41.8190672], [-87.6291931, 41.8192632]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[[-87.6291229, 41.8165532], [-87.6291525, 41.8178617], [-87.6291863, 41.8190672]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[[-87.6291179, 41.8163605], [-87.6291229, 41.8165532]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[[-87.6290476, 41.819066], [-87.629053, 41.8192658]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[[-87.6289858, 41.8165593], [-87.6290158, 41.8178723], [-87.6290476, 41.819066]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[[-87.6289797, 41.8163575], [-87.6289858, 41.8165593]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[[-87.6292795, 41.8274353], [-87.6293754, 41.8308836]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[[-87.6292755, 41.8272245], [-87.6292795, 41.8274353]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[[-87.6291817, 41.8237816], [-87.6292755, 41.8272245]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[[-87.6291779, 41.8235867], [-87.6291817, 41.8237816]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[[-87.629053, 41.8192658], [-87.6290702, 41.8198422], [-87.6290958, 41.8207811], [-87.6291245, 41.821807], [-87.6291588, 41.8230896], [-87.6291779, 41.8235867]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[[-87.6294263, 41.8308828], [-87.6293332, 41.8274323]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[[-87.6294345, 41.8310734], [-87.6294263, 41.8308828]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[[-87.6293801, 41.8310741], [-87.6294329, 41.8329119], [-87.6294348, 41.8330123], [-87.6294787, 41.8345278]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[[-87.6293754, 41.8308836], [-87.6293801, 41.8310741]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[[-87.6291046, 41.8192649], [-87.6290984, 41.8190664]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[[-87.6292286, 41.8235861], [-87.6291808, 41.8220473], [-87.6291737, 41.8218141], [-87.6291548, 41.821012], [-87.6291257, 41.8200832], [-87.6291046, 41.8192649]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[[-87.6292329, 41.8237812], [-87.6292286, 41.8235861]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[[-87.6293265, 41.8272225], [-87.6292804, 41.8255287], [-87.6292329, 41.8237812]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[[-87.6293332, 41.8274323], [-87.6293265, 41.8272225]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[[-87.6290376, 41.8165595], [-87.6290325, 41.8163575]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[[-87.6290984, 41.8190664], [-87.6290672, 41.8178708], [-87.6290376, 41.8165595]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[[-87.6295774, 41.8381655], [-87.6295854, 41.8383673]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[[-87.6294857, 41.8347393], [-87.6295774, 41.8381655]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[[-87.6294787, 41.8345278], [-87.6294857, 41.8347393]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[[-87.6297399, 41.8443376], [-87.6297767, 41.8454585]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[[-87.6296717, 41.841931], [-87.6296974, 41.8429131], [-87.6297399, 41.8443376]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[[-87.6295854, 41.8383673], [-87.6296717, 41.841931]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[[-87.6298807, 41.8481145], [-87.6299095, 41.8492771]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[[-87.6298337, 41.8464791], [-87.6298807, 41.8481145]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[[-87.6297821, 41.845658], [-87.6298337, 41.8464791]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[[-87.6297767, 41.8454585], [-87.6297821, 41.845658]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[[-87.6298376, 41.8456568], [-87.6298284, 41.845458]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>[[-87.6299347, 41.8511339], [-87.6299514, 41.8513809], [-87.6299823, 41.8516289], [-87.6300151, 41.8518538], [-87.6300478, 41.8520436], [-87.6300914, 41.852253], [-87.6301206, 41.8523824], [-87.6301479, 41.8524962], [-87.6302073, 41.8527013]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[[-87.6299266, 41.8509453], [-87.6299347, 41.8511339]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[[-87.6299095, 41.8492771], [-87.6299059, 41.8500907], [-87.6299266, 41.8509453]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[[-87.6297412, 41.8422003], [-87.6296364, 41.838366]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>[[-87.6298021, 41.8443232], [-87.6297412, 41.8422003]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>[[-87.6298284, 41.845458], [-87.6298021, 41.8443232]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>[[-87.6295305, 41.8345271], [-87.6294856, 41.8330073], [-87.6294355, 41.8311171], [-87.6294345, 41.8310734]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>[[-87.6295367, 41.8347387], [-87.6295305, 41.8345271]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>[[-87.6296297, 41.8381655], [-87.6295367, 41.8347387]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>[[-87.6296364, 41.838366], [-87.6296297, 41.8381655]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>[[-87.6299361, 41.8481272], [-87.6298871, 41.8464731]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>[[-87.6299637, 41.8492771], [-87.6299361, 41.8481272]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>[[-87.6299783, 41.8509448], [-87.6299569, 41.8501097], [-87.6299637, 41.8492771]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>[[-87.6299856, 41.8511332], [-87.6299783, 41.8509448]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>[[-87.6389908, 41.751586], [-87.6389292, 41.7517631], [-87.6388568, 41.7519963], [-87.6386436, 41.7526446], [-87.6384666, 41.7531408], [-87.63826, 41.7536941], [-87.6380615, 41.7542213], [-87.6378791, 41.7546626], [-87.6376646, 41.7551798], [-87.6373387, 41.7560222], [-87.6370597, 41.7567475], [-87.6368063, 41.7574358], [-87.636593, 41.758024], [-87.6365193, 41.7582501], [-87.6364348, 41.7585102], [-87.6363396, 41.7588224], [-87.6362068, 41.7592305], [-87.6360874, 41.7595957], [-87.6359077, 41.7600849], [-87.635673, 41.7606901], [-87.635386, 41.7614294], [-87.6350897, 41.7621916], [-87.6346189, 41.7634061]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>[[-87.6302073, 41.8527013], [-87.6302449, 41.852834], [-87.6303083, 41.8530495]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>[[-87.6303083, 41.8530495], [-87.6304401, 41.8534531], [-87.6305201, 41.8537213], [-87.6305712, 41.8539442], [-87.6306034, 41.8541354], [-87.6306269, 41.8543666], [-87.6306419, 41.8547613]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>[[-87.6306419, 41.8547613], [-87.6306479, 41.8550238]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>[[-87.6298871, 41.8464731], [-87.6298376, 41.8456568]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>[[-87.630264, 41.8527013], [-87.6301861, 41.8524366], [-87.6301406, 41.8522428], [-87.630097, 41.8520192], [-87.6300678, 41.8518457], [-87.6300296, 41.8516004], [-87.6300023, 41.8513646], [-87.6299856, 41.8511332]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>[[-87.6303661, 41.8530482], [-87.6303023, 41.8528324], [-87.630264, 41.8527013]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>[[-87.6306936, 41.8547362], [-87.630683, 41.8544271], [-87.6306593, 41.8541853], [-87.6306205, 41.8539296], [-87.6305669, 41.8536889], [-87.6304843, 41.8534137], [-87.6303661, 41.8530482]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>[[-87.6307009, 41.8549989], [-87.6306936, 41.8547362]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>[[-87.6314242, 41.8672013], [-87.6313754, 41.8670775], [-87.6312628, 41.8668119], [-87.630898, 41.8660009], [-87.6307156, 41.8655874], [-87.6306029, 41.8652559], [-87.6305439, 41.8649602], [-87.6305225, 41.8645847], [-87.6304956, 41.8634281], [-87.6304822, 41.8628648], [-87.6304876, 41.8626711], [-87.6305117, 41.8623255], [-87.6305386, 41.8621057], [-87.6305707, 41.8619319], [-87.6306217, 41.8615644]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>[[-87.63065, 41.8618827], [-87.6306539, 41.8614246], [-87.6306593, 41.861089]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>[[-87.6315263, 41.8672], [-87.6314773, 41.8670675], [-87.6313164, 41.866702], [-87.6308282, 41.8656154], [-87.6306995, 41.8652479], [-87.6306512, 41.8650122], [-87.6306298, 41.8646966], [-87.6305922, 41.8634261], [-87.6305815, 41.8629807], [-87.6305868, 41.862713], [-87.6306083, 41.8623994], [-87.6306476, 41.8619126], [-87.63065, 41.8618827]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[[-87.6308615, 41.8582602], [-87.6308431, 41.8586642], [-87.6308311, 41.8590292]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>[[-87.6305332, 41.862693], [-87.6305815, 41.8623454], [-87.6306476, 41.8619126]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>[[-87.6305332, 41.862693], [-87.6305654, 41.8622915], [-87.6306217, 41.8615644]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[[-87.6308495, 41.8576732], [-87.630832, 41.8571136], [-87.6308156, 41.8567394], [-87.6307914, 41.8564637], [-87.63075, 41.8560288], [-87.6307275, 41.855726], [-87.6307141, 41.8554309], [-87.6307009, 41.8549989]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[[-87.6308524, 41.8578668], [-87.6308495, 41.8576732]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[[-87.6306479, 41.8550238], [-87.6306685, 41.8555839], [-87.6306899, 41.8559689], [-87.630737, 41.8564415], [-87.63076, 41.8567214], [-87.6307849, 41.8571669], [-87.6307961, 41.8576748]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[[-87.6307961, 41.8576748], [-87.6308042, 41.8578679]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[[-87.6314738, 41.8672007], [-87.6314425, 41.8671215], [-87.6313566, 41.8669058], [-87.6312628, 41.866704], [-87.6308282, 41.8657233], [-87.6307209, 41.8654676], [-87.6306458, 41.8652199], [-87.6305976, 41.8649722], [-87.6305707, 41.8646246], [-87.6305439, 41.8634301], [-87.6305278, 41.8629307], [-87.6305332, 41.862693]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>[[-87.6284008, 41.7947138], [-87.6283847, 41.7941498]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>[[-87.6282775, 41.7898488], [-87.6282289, 41.788394], [-87.6282144, 41.7874305]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[[-87.6282829, 41.7900368], [-87.6282775, 41.7898488]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[[-87.6283016, 41.7908687], [-87.6282829, 41.7900368]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>[[-87.6283097, 41.7910527], [-87.6283016, 41.7908687]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>[[-87.6283847, 41.7941498], [-87.6283797, 41.793826], [-87.6283416, 41.7924092], [-87.6283097, 41.7910527]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>[[-87.6282236, 41.7856157], [-87.6282296, 41.7855039], [-87.6282362, 41.7853965]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>[[-87.6282064, 41.7872175], [-87.6281951, 41.7867995], [-87.6281973, 41.7862284], [-87.6282236, 41.7856157]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>[[-87.6282144, 41.7874305], [-87.6282064, 41.7872175]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>[[-87.6282362, 41.7853965], [-87.6282498, 41.7851331], [-87.6282704, 41.7846999], [-87.628281, 41.7844426], [-87.6282891, 41.7842273], [-87.6283, 41.7838243], [-87.6283012, 41.7832784]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>[[-87.6281533, 41.7872215], [-87.6281581, 41.7874305]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>[[-87.6281674, 41.7856138], [-87.6281481, 41.7860653], [-87.6281365, 41.7865083], [-87.6281431, 41.786798], [-87.6281431, 41.7869426], [-87.6281533, 41.7872215]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>[[-87.6281849, 41.7853959], [-87.6281757, 41.7855005], [-87.6281674, 41.7856138]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>[[-87.6298403, 41.7764579], [-87.6293034, 41.7775483], [-87.6289491, 41.7782981], [-87.6287573, 41.7787482], [-87.6286323, 41.7790925], [-87.628516, 41.779461], [-87.6283762, 41.780039], [-87.6283157, 41.780359], [-87.6282507, 41.7808417], [-87.6282062, 41.7813969], [-87.6282096, 41.7818307]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>[[-87.6282506, 41.7910607], [-87.6282894, 41.7924421], [-87.6283253, 41.7938327], [-87.6283337, 41.7941498]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>[[-87.6282453, 41.7908647], [-87.6282506, 41.7910607]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>[[-87.6282185, 41.7900388], [-87.6282453, 41.7908647]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>[[-87.6282104, 41.7898468], [-87.6282185, 41.7900388]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>[[-87.6281581, 41.7874305], [-87.6281818, 41.7883598], [-87.6282104, 41.7898468]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>[[-87.6283471, 41.7947118], [-87.6283879, 41.7960931], [-87.62839, 41.7961657], [-87.6284585, 41.7983356]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>[[-87.6283337, 41.7941498], [-87.6283471, 41.7947118]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>[[-87.6301758, 41.7758729], [-87.6304225, 41.7753025], [-87.6306136, 41.774785], [-87.6307296, 41.7744387]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>[[-87.6282608, 41.7817347], [-87.6282611, 41.7814383], [-87.6283058, 41.7808247], [-87.6283619, 41.7803987], [-87.6284278, 41.7800507], [-87.6285746, 41.7794722], [-87.6286527, 41.7791993], [-87.6287935, 41.7787926], [-87.6289896, 41.7783227], [-87.6293486, 41.777568], [-87.6298791, 41.776491]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>[[-87.6369199, 41.848133], [-87.6369063, 41.8477642], [-87.6368875, 41.8470279], [-87.6368687, 41.8461748], [-87.6368459, 41.8453046], [-87.6368271, 41.8444194], [-87.6368043, 41.8435352], [-87.6367802, 41.8426361], [-87.6367601, 41.8417399], [-87.6367386, 41.8408556], [-87.6367158, 41.8399424], [-87.6366944, 41.8390802], [-87.6366702, 41.8379881], [-87.6366461, 41.8370329], [-87.6366246, 41.8360986], [-87.6366032, 41.8352483], [-87.6365817, 41.8344619], [-87.6365616, 41.8335316], [-87.6365361, 41.8325214], [-87.636512, 41.8315401], [-87.6364905, 41.8306878], [-87.6364744, 41.8299453], [-87.6364516, 41.8289929], [-87.6364262, 41.8280636], [-87.6363993, 41.8269453], [-87.6363832, 41.8262968], [-87.6363698, 41.8256472]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>[[-87.6368402, 41.8089421], [-87.6368955, 41.8087497], [-87.6371544, 41.8078641], [-87.6372348, 41.8076172], [-87.6373099, 41.8074222], [-87.6374052, 41.8072053], [-87.6375044, 41.8070204], [-87.6376211, 41.8068364], [-87.6377337, 41.8066835], [-87.6378665, 41.8065205], [-87.6379684, 41.8064096], [-87.63812, 41.8062606], [-87.6383761, 41.8060327], [-87.6388442, 41.8056478], [-87.6392411, 41.8053159], [-87.6394785, 41.805106], [-87.6396475, 41.8049381], [-87.6397776, 41.8047921], [-87.6398782, 41.8046681], [-87.6399989, 41.8044962], [-87.6400753, 41.8043712], [-87.6401705, 41.8041933], [-87.6402537, 41.8040074], [-87.6403207, 41.8038164], [-87.640373, 41.8036095], [-87.6404052, 41.8034345], [-87.640424, 41.8032336], [-87.6404307, 41.8030646], [-87.6404186, 41.8024128], [-87.6404016, 41.8017733]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>[[-87.6396394, 41.7779039], [-87.6396461, 41.7780829]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>[[-87.636105, 41.8169581], [-87.6361351, 41.8165573]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>[[-87.6363705, 41.8216919], [-87.6363643, 41.8214647], [-87.6363633, 41.8214271], [-87.6363497, 41.8211719], [-87.6363269, 41.821006], [-87.636284, 41.8207641], [-87.6362116, 41.8203763]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>[[-87.6363738, 41.8218619], [-87.6363705, 41.8216919]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>[[-87.6402195, 41.7944913], [-87.640206, 41.7939456]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>[[-87.6401706, 41.7944921], [-87.6401839, 41.7952484], [-87.6402134, 41.7963392], [-87.6402322, 41.7970341], [-87.6402564, 41.7980859], [-87.6402805, 41.7990656], [-87.6403019, 41.7998945], [-87.6403167, 41.8004753], [-87.6403395, 41.8012271], [-87.6403485, 41.8015961]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>[[-87.6401565, 41.7939462], [-87.6401706, 41.7944921]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MOW Storage Track</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>[[-87.6404186, 41.8024128], [-87.6404387, 41.8026318], [-87.6404642, 41.8027837], [-87.6404776, 41.8029067], [-87.6404897, 41.8031796], [-87.6405004, 41.8035385], [-87.6404991, 41.8036545], [-87.6404857, 41.8037814], [-87.6404615, 41.8039314], [-87.6404267, 41.8040613], [-87.6403757, 41.8042063], [-87.6403207, 41.8043293], [-87.6402443, 41.8044642], [-87.640141, 41.8046202], [-87.6400069, 41.8048031], [-87.6398768, 41.8049571], [-87.6397695, 41.805068], [-87.6396327, 41.805202], [-87.6394611, 41.8053559], [-87.6393109, 41.8054669], [-87.6391808, 41.8055509], [-87.6390172, 41.8056508], [-87.6387945, 41.8057998]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MOW Storage Track</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>[[-87.6381709, 41.8062806], [-87.6384432, 41.8060707], [-87.6387945, 41.8057998], [-87.6392411, 41.8054379], [-87.6394866, 41.805226], [-87.6396515, 41.805072], [-87.6397896, 41.8049311], [-87.6399224, 41.8047741], [-87.6400565, 41.8045922], [-87.6401477, 41.8044462], [-87.6402295, 41.8043003], [-87.6402939, 41.8041593], [-87.6403583, 41.8040014], [-87.6404119, 41.8038304], [-87.6404468, 41.8036745], [-87.6404709, 41.8034665], [-87.6404897, 41.8031796]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>[[-87.640206, 41.7939456], [-87.6401839, 41.7933207], [-87.6401571, 41.7922628], [-87.640133, 41.7913719], [-87.6401196, 41.790838]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>[[-87.6397253, 41.7808541], [-87.6397454, 41.7815822]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>[[-87.6397199, 41.7806591], [-87.6397253, 41.7808541]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>[[-87.6396944, 41.7799211], [-87.6397199, 41.7806591]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>[[-87.6396904, 41.7797051], [-87.6396944, 41.7799211]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>[[-87.6396461, 41.7780829], [-87.6396689, 41.778932], [-87.6396904, 41.7797051]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>[[-87.6397896, 41.7833632], [-87.639795, 41.7835603]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>[[-87.6397736, 41.7826702], [-87.6397896, 41.7833632]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>[[-87.6397682, 41.7824722], [-87.6397736, 41.7826702]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>[[-87.6397494, 41.7817792], [-87.6397682, 41.7824722]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>[[-87.6397454, 41.7815822], [-87.6397494, 41.7817792]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>[[-87.6399747, 41.7870112], [-87.6399761, 41.7872112]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>[[-87.6398274, 41.7847783], [-87.6398339, 41.7849573], [-87.6398567, 41.7852563], [-87.6398892, 41.7856543], [-87.6399398, 41.7861402], [-87.6399506, 41.7863142], [-87.6399626, 41.7865402], [-87.6399747, 41.7870112]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>[[-87.6398205, 41.7845653], [-87.6398274, 41.7847783]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>[[-87.639795, 41.7835603], [-87.6398205, 41.7845653]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>[[-87.6400713, 41.790839], [-87.6400914, 41.7916929], [-87.6401129, 41.7924528], [-87.6401343, 41.7933237], [-87.6401565, 41.7939462]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>[[-87.6400686, 41.790657], [-87.6400713, 41.790839]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>[[-87.6399761, 41.7872112], [-87.6399975, 41.7878912], [-87.640023, 41.7888681], [-87.640027, 41.7890241], [-87.6400471, 41.7898461], [-87.6400686, 41.790657]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>[[-87.639909, 41.7845643], [-87.6398822, 41.7835583]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>[[-87.6399144, 41.784777], [-87.639909, 41.7845643]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>[[-87.6400217, 41.7870112], [-87.6400056, 41.7863742], [-87.6399962, 41.7861452], [-87.639972, 41.7857983], [-87.6399412, 41.7852913], [-87.6399264, 41.7850353], [-87.6399144, 41.784777]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>[[-87.6400257, 41.7872122], [-87.6400217, 41.7870112]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>[[-87.6401155, 41.790656], [-87.6401008, 41.790088], [-87.6400726, 41.7890221], [-87.6400686, 41.7888701], [-87.6400257, 41.7872122]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>[[-87.6398379, 41.7817772], [-87.6398326, 41.7815832]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>[[-87.6398554, 41.7824752], [-87.6398379, 41.7817772]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>[[-87.6398607, 41.7826672], [-87.6398554, 41.7824752]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>[[-87.6398768, 41.7833612], [-87.6398607, 41.7826672]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>[[-87.6398822, 41.7835583], [-87.6398768, 41.7833612]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>[[-87.6397843, 41.7797291], [-87.6397601, 41.778832], [-87.6397414, 41.7780829]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>[[-87.6397896, 41.7799171], [-87.6397843, 41.7797291]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>[[-87.6398071, 41.7806571], [-87.6397896, 41.7799171]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>[[-87.6398111, 41.7808571], [-87.6398071, 41.7806571]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>[[-87.6398326, 41.7815832], [-87.6398111, 41.7808571]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>[[-87.6401196, 41.790838], [-87.6401155, 41.790656]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>[[-87.6397414, 41.7780829], [-87.6397373, 41.7779039]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>South Chicago Sub District</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>[[-87.5477609, 41.7285805], [-87.5477719, 41.7289565], [-87.5477819, 41.7291216], [-87.5477974, 41.7293123], [-87.5478269, 41.7295966], [-87.5478417, 41.7297712], [-87.5478517, 41.7299343], [-87.5478533, 41.7300305], [-87.5478542, 41.730116], [-87.5478569, 41.7302152], [-87.5478631, 41.7304483], [-87.5478826, 41.7311864], [-87.5479062, 41.7318622], [-87.5479094, 41.7319487], [-87.5479119, 41.7320361], [-87.5479295, 41.7326796], [-87.5479496, 41.7334282], [-87.5479657, 41.7342279], [-87.5479791, 41.7346492], [-87.5479986, 41.7354723], [-87.5480173, 41.7362389], [-87.5480328, 41.7368088], [-87.5480402, 41.7370075], [-87.5480516, 41.7371911], [-87.5480643, 41.7373057], [-87.5480691, 41.7373307], [-87.5480852, 41.7374296], [-87.548101, 41.7375249], [-87.5481239, 41.7376755], [-87.5481762, 41.7379867], [-87.5482286, 41.7382564], [-87.5482682, 41.7384355], [-87.5483338, 41.7386802], [-87.5483922, 41.7388743], [-87.5484447, 41.7390266], [-87.5484813, 41.739134], [-87.5485605, 41.7393417], [-87.5486591, 41.7395653], [-87.5487624, 41.7397805], [-87.5488837, 41.7400131], [-87.5489984, 41.7402173], [-87.5491579, 41.7404715], [-87.5492894, 41.7406686], [-87.5494141, 41.7408377], [-87.5495388, 41.7409988], [-87.5496756, 41.7411679], [-87.549862, 41.7413831], [-87.5500538, 41.7415902], [-87.5502214, 41.7417553], [-87.550391, 41.7419199], [-87.5504903, 41.7420095], [-87.5507934, 41.7422817], [-87.5509993, 41.7424558], [-87.5510985, 41.7425519], [-87.5511924, 41.7426564], [-87.5512715, 41.742764], [-87.5513466, 41.7428881], [-87.5513976, 41.7429987], [-87.5514365, 41.7431067], [-87.5514647, 41.7432248], [-87.5514794, 41.7433219], [-87.5514819, 41.7434045], [-87.551484, 41.7434716], [-87.5514851, 41.7435445], [-87.5514895, 41.7440598], [-87.5514941, 41.7445762], [-87.5514954, 41.7446655], [-87.5514983, 41.7447373], [-87.551511, 41.7452461], [-87.5515326, 41.7462507], [-87.5515356, 41.7464017], [-87.551537, 41.7464719], [-87.5515403, 41.7465579], [-87.5515393, 41.7466073], [-87.5515478, 41.746756], [-87.5515689, 41.7472501], [-87.5515944, 41.7482134], [-87.5515952, 41.7482987], [-87.5515967, 41.7483755], [-87.5516108, 41.7488897], [-87.5516164, 41.7491666], [-87.5516175, 41.7492211], [-87.5516184, 41.7492651], [-87.5516276, 41.7497777], [-87.5516313, 41.7500353], [-87.5516324, 41.7501058], [-87.551635, 41.750191], [-87.5516417, 41.7506235], [-87.5516501, 41.7507353], [-87.5516641, 41.7508598], [-87.5516903, 41.750975], [-87.5517262, 41.7510927], [-87.5517654, 41.7511865], [-87.551814, 41.7512795], [-87.5518818, 41.7513876], [-87.5519669, 41.7515001], [-87.5520413, 41.7515862], [-87.5521392, 41.7516922], [-87.5522733, 41.7518223], [-87.5523009, 41.7518442], [-87.5523809, 41.7519228], [-87.5524629, 41.7519972], [-87.5537522, 41.7531961], [-87.5539028, 41.753337], [-87.5542211, 41.7536296], [-87.554303, 41.7537071], [-87.554378, 41.7537791], [-87.5546887, 41.7540679], [-87.5553639, 41.7546847], [-87.5561498, 41.7554132], [-87.5562409, 41.7554969], [-87.5563254, 41.7555753], [-87.5569491, 41.7561559], [-87.5576686, 41.7568327], [-87.5580771, 41.7572163], [-87.5581487, 41.7572836], [-87.5582317, 41.7573607], [-87.5588555, 41.7579351], [-87.5596082, 41.7586254], [-87.5598814, 41.7588745], [-87.5600594, 41.7590426], [-87.5601363, 41.7591158], [-87.5602272, 41.7592039], [-87.5603983, 41.7593751], [-87.5606134, 41.7596102], [-87.5610737, 41.7601185], [-87.5615135, 41.7606102], [-87.5617146, 41.7608326], [-87.5617762, 41.7609002], [-87.5618479, 41.7609803], [-87.5621331, 41.7612964], [-87.5624979, 41.7616996], [-87.5633141, 41.7626083], [-87.5633776, 41.7626795], [-87.5634533, 41.7627644], [-87.5638424, 41.7631986], [-87.5643118, 41.7637333], [-87.5649164, 41.7644175], [-87.5649722, 41.7644803], [-87.5650502, 41.7645668], [-87.5659948, 41.7656143], [-87.5660492, 41.7656761], [-87.5661853, 41.7658149], [-87.5662956, 41.7659097], [-87.5663677, 41.765962], [-87.5663878, 41.7659748], [-87.5664491, 41.7660142], [-87.5665085, 41.7660467], [-87.5666064, 41.7660972], [-87.566648, 41.7661123], [-87.5667197, 41.766145], [-87.5668123, 41.7661762], [-87.5669504, 41.766214], [-87.5670899, 41.76624], [-87.5672481, 41.7662591], [-87.5673903, 41.7662651], [-87.5675586, 41.7662676], [-87.5680459, 41.7662612], [-87.5681531, 41.7662599], [-87.5682591, 41.7662591], [-87.5696872, 41.766244], [-87.5697772, 41.7662438], [-87.5698863, 41.7662421], [-87.5713034, 41.7662276], [-87.5714013, 41.7662262], [-87.5715037, 41.7662259], [-87.5725187, 41.7662138], [-87.5726189, 41.7662131], [-87.5727239, 41.7662125], [-87.5737742, 41.7662038], [-87.5738811, 41.766203], [-87.5739889, 41.7662019], [-87.5749842, 41.7661919], [-87.5750843, 41.766191], [-87.5751841, 41.7661905], [-87.5755341, 41.766188], [-87.5758506, 41.7661895], [-87.5760558, 41.766191], [-87.5761855, 41.766191], [-87.576308, 41.7661913], [-87.5764296, 41.7661905], [-87.5781131, 41.7661745], [-87.5782507, 41.7661735], [-87.5790156, 41.7661537], [-87.5792705, 41.7661503], [-87.579373, 41.7661491], [-87.5794807, 41.766148], [-87.5811267, 41.7661312], [-87.5812324, 41.766131], [-87.5813356, 41.7661303], [-87.5823514, 41.7661207], [-87.582444, 41.7661198], [-87.5825514, 41.7661186], [-87.5835787, 41.7661083], [-87.5836809, 41.7661066], [-87.5837849, 41.7661063], [-87.5846759, 41.7660978], [-87.5847786, 41.766097], [-87.5848831, 41.7660955], [-87.5853195, 41.76609], [-87.5857044, 41.766091], [-87.5857782, 41.7660913], [-87.5859325, 41.7660929], [-87.586326, 41.7660975], [-87.5864834, 41.7660977], [-87.5869422, 41.766092], [-87.5885126, 41.7660816], [-87.5887085, 41.7660775], [-87.5891282, 41.7660675], [-87.5893109, 41.7660659], [-87.5893247, 41.7660658], [-87.5893428, 41.7660655], [-87.5894435, 41.7660643], [-87.5895474, 41.7660678], [-87.5895909, 41.766069], [-87.589725, 41.76608], [-87.5898612, 41.7660994], [-87.5900348, 41.766135], [-87.5900663, 41.7661441], [-87.590187, 41.766179], [-87.5903426, 41.7662325], [-87.590468, 41.7662821], [-87.5906088, 41.7663501], [-87.5907429, 41.7664261], [-87.5908726, 41.7665095], [-87.5908891, 41.7665201], [-87.5909965, 41.7666023], [-87.5911412, 41.7666911], [-87.5912753, 41.7667852], [-87.591443, 41.7669012], [-87.5916482, 41.7670513], [-87.5918145, 41.7671843], [-87.5919311, 41.7672923], [-87.5920492, 41.7674274], [-87.5921471, 41.7675614], [-87.5922034, 41.7676484], [-87.5922627, 41.7677463], [-87.5922973, 41.7678289], [-87.5923269, 41.7679068], [-87.5923442, 41.7679525], [-87.5923817, 41.7680705], [-87.5924099, 41.7681916], [-87.59243, 41.7683336], [-87.5924408, 41.7685047], [-87.5924501, 41.7687987], [-87.5924547, 41.7690996], [-87.5924653, 41.7692974], [-87.5924796, 41.7694438], [-87.5924991, 41.7695581], [-87.5925367, 41.7697498]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>South Chicago Sub District</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>[[-87.5925367, 41.7697498], [-87.5926504, 41.7703938], [-87.5926758, 41.770543], [-87.5926864, 41.7707135], [-87.5926599, 41.7708637], [-87.5926051, 41.7711321]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>South Chicago Sub District</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>[[-87.5925745, 41.7695861], [-87.5925588, 41.7695157], [-87.5925377, 41.7693988], [-87.5925254, 41.7692782], [-87.5925176, 41.7690963], [-87.5925118, 41.7687897], [-87.5925078, 41.7685597], [-87.5924998, 41.7684186], [-87.5924877, 41.7682846], [-87.5924756, 41.7682066], [-87.5924582, 41.7681156], [-87.5924354, 41.7680255], [-87.5924086, 41.7679365], [-87.5923975, 41.7679062], [-87.5923885, 41.7678815], [-87.5923656, 41.7678284], [-87.5923349, 41.7677465], [-87.5922946, 41.7676674], [-87.5922356, 41.7675704], [-87.5921685, 41.7674724], [-87.5920854, 41.7673664], [-87.5920036, 41.7672773], [-87.5919043, 41.7671803], [-87.5917729, 41.7670713], [-87.5916616, 41.7669883], [-87.591439, 41.7668292], [-87.5912177, 41.7666742], [-87.5911398, 41.7666189], [-87.5909946, 41.7665304], [-87.5908708, 41.7664397], [-87.5908623, 41.7664341], [-87.5907416, 41.7663581], [-87.5906316, 41.7662981], [-87.5905203, 41.766243], [-87.5904023, 41.766192], [-87.5902762, 41.766145], [-87.590209, 41.7661245], [-87.590181, 41.766116], [-87.5900408, 41.7660811], [-87.5899269, 41.7660563], [-87.5898041, 41.7660373], [-87.5896586, 41.76602], [-87.5895515, 41.7660134], [-87.5895303, 41.7660124], [-87.5894421, 41.766008], [-87.5893409, 41.7660068], [-87.5892972, 41.766006], [-87.5891798, 41.7660071], [-87.5886163, 41.7660112], [-87.587209, 41.7660229], [-87.5864829, 41.7660289], [-87.5863236, 41.7660312], [-87.5859301, 41.7660353], [-87.5857762, 41.7660382], [-87.5855555, 41.766042], [-87.5850942, 41.766049], [-87.5848817, 41.7660515], [-87.5847783, 41.766053], [-87.5846746, 41.7660539], [-87.583784, 41.7660638], [-87.5836788, 41.7660643], [-87.5835763, 41.766066], [-87.5825511, 41.7660759], [-87.5824433, 41.766077], [-87.5823508, 41.7660778], [-87.5813264, 41.7660865], [-87.5812307, 41.7660866], [-87.581134, 41.7660867], [-87.5803145, 41.766097], [-87.5794812, 41.7661048], [-87.5793724, 41.7661055], [-87.5792683, 41.7661077], [-87.5790116, 41.7661103], [-87.5787984, 41.7661103], [-87.5785563, 41.7661075], [-87.5782502, 41.766105], [-87.5781143, 41.766106], [-87.5771214, 41.7661163], [-87.5764294, 41.7661219], [-87.5763069, 41.7661231], [-87.5761848, 41.7661245], [-87.5761256, 41.7661265], [-87.5758144, 41.766133], [-87.5755831, 41.7661395], [-87.575182, 41.7661459], [-87.5750832, 41.7661474], [-87.5749821, 41.7661484], [-87.5739938, 41.7661594], [-87.5738827, 41.76616], [-87.5737747, 41.7661612], [-87.5727163, 41.7661697], [-87.572613, 41.7661712], [-87.5725161, 41.7661713], [-87.5714999, 41.7661837], [-87.5713972, 41.7661848], [-87.5713004, 41.7661856], [-87.5698855, 41.7661997], [-87.569776, 41.7662006], [-87.5696861, 41.7662017], [-87.5682559, 41.7662163], [-87.5681521, 41.7662169], [-87.5680454, 41.766218], [-87.5676612, 41.766222], [-87.5674506, 41.766218], [-87.5672924, 41.766208], [-87.5671583, 41.766189], [-87.5670308, 41.7661605], [-87.5669034, 41.766127], [-87.56677, 41.7660787], [-87.5666664, 41.766034], [-87.5666481, 41.7660194], [-87.5665783, 41.7659882], [-87.5665068, 41.7659487], [-87.566433, 41.7659005], [-87.5663909, 41.7658717], [-87.5663519, 41.7658416], [-87.5662951, 41.7657953], [-87.5662255, 41.7657366], [-87.566175, 41.7656893], [-87.5660787, 41.7655819], [-87.5658664, 41.7653465], [-87.5653419, 41.7647665], [-87.5651402, 41.7645441], [-87.5650623, 41.7644575], [-87.5650032, 41.7643884], [-87.5645458, 41.7638908], [-87.5642515, 41.7635732], [-87.5638155, 41.7630976], [-87.5634944, 41.7627458], [-87.5634208, 41.7626639], [-87.5633537, 41.7625895], [-87.5628251, 41.7620057], [-87.5621479, 41.7612484], [-87.5618909, 41.7609654], [-87.5618206, 41.760886], [-87.5617575, 41.7608167], [-87.5614431, 41.7604651], [-87.5607478, 41.7596938], [-87.5602971, 41.759191], [-87.5602108, 41.7590963], [-87.5601313, 41.7590122], [-87.5600497, 41.7589285], [-87.5599042, 41.7587915], [-87.5588658, 41.7578336], [-87.5587294, 41.757705], [-87.5583482, 41.7573569], [-87.5582641, 41.7572795], [-87.5581933, 41.7572148], [-87.5580039, 41.7570437], [-87.5575928, 41.7566761], [-87.5571181, 41.7562434], [-87.5566681, 41.7558242], [-87.5563992, 41.7555736], [-87.5563128, 41.755495], [-87.5562045, 41.755392], [-87.5558071, 41.7550223], [-87.5552875, 41.7545341], [-87.5547175, 41.7539979], [-87.5544793, 41.7537736], [-87.5544071, 41.7537056], [-87.5542923, 41.7535979], [-87.5538706, 41.753209], [-87.5530152, 41.7524103], [-87.5525669, 41.7519935], [-87.5524911, 41.7519212], [-87.5524065, 41.751842], [-87.5523243, 41.7517683], [-87.5521714, 41.7516212], [-87.5520702, 41.7515106], [-87.5519736, 41.7513901], [-87.5518911, 41.7512595], [-87.5518214, 41.7511214], [-87.5517663, 41.750984], [-87.5517313, 41.7508277], [-87.5517107, 41.7506809], [-87.5517043, 41.7505286], [-87.5516971, 41.75019], [-87.5516945, 41.7501049], [-87.5516943, 41.7500344], [-87.5516821, 41.7492645], [-87.5516808, 41.7492208], [-87.5516799, 41.7491778], [-87.551662, 41.748374], [-87.5516603, 41.7482979], [-87.5516591, 41.7482128], [-87.5516491, 41.7474889], [-87.5516325, 41.7466104], [-87.5516331, 41.7465569], [-87.551631, 41.7464717], [-87.5516296, 41.7464005], [-87.5516067, 41.7452436], [-87.5515936, 41.7447359], [-87.5515931, 41.7446644], [-87.5515911, 41.7445756], [-87.5515827, 41.7439698], [-87.5515739, 41.7436171], [-87.5515713, 41.7435466], [-87.5515676, 41.7434711], [-87.5515575, 41.7434046], [-87.5515485, 41.7433459], [-87.5515283, 41.7432488], [-87.5514895, 41.7431107], [-87.5514459, 41.7429902], [-87.5513956, 41.7428781], [-87.5513312, 41.7427585], [-87.5512669, 41.7426544], [-87.5511991, 41.7425629], [-87.5511206, 41.7424803], [-87.5510039, 41.7423727], [-87.5507062, 41.7421211], [-87.550544, 41.741977], [-87.550381, 41.7418284], [-87.5502509, 41.7416983], [-87.5500981, 41.7415442], [-87.5499023, 41.7413311], [-87.5497641, 41.7411719], [-87.5495804, 41.7409488], [-87.5494503, 41.7407807], [-87.549335, 41.7406196], [-87.5492196, 41.7404484], [-87.5491204, 41.7402903], [-87.548999, 41.7400702], [-87.5489152, 41.7399151], [-87.5488274, 41.7397355], [-87.5487409, 41.7395398], [-87.5486215, 41.7392466], [-87.5485223, 41.7389739], [-87.5484511, 41.7387513], [-87.5483865, 41.738519], [-87.5483137, 41.7382079], [-87.548289, 41.7380902], [-87.54826, 41.7379342], [-87.5481966, 41.7375239], [-87.5481804, 41.7374278], [-87.5481643, 41.7373295], [-87.5481475, 41.7372281], [-87.5481257, 41.7370959], [-87.5481059, 41.7369584], [-87.5480917, 41.7368399], [-87.5480824, 41.7367203], [-87.5480763, 41.7365887], [-87.5480723, 41.736424], [-87.5480523, 41.735704], [-87.5480328, 41.7350205], [-87.5480207, 41.734398], [-87.5480046, 41.7338376], [-87.5479858, 41.733084], [-87.54796, 41.7320362], [-87.5479563, 41.7319482], [-87.5479543, 41.7318617], [-87.5479429, 41.7313485], [-87.5479155, 41.7302148], [-87.5479105, 41.7301154], [-87.5479074, 41.7300256], [-87.5479012, 41.7295902], [-87.5478805, 41.7294027], [-87.5477824, 41.7287928], [-87.5477609, 41.7285805]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>South Chicago Sub District</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>[[-87.5926494, 41.7711389], [-87.5927128, 41.7708727], [-87.5927356, 41.7707131], [-87.5927352, 41.7706282], [-87.5927303, 41.7705467], [-87.5925745, 41.7695861]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>[[-87.5621479, 41.7612484], [-87.5622967, 41.7614345], [-87.5623933, 41.7615715], [-87.5624979, 41.7616996]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>[[-87.5614431, 41.7604651], [-87.5613553, 41.7603761], [-87.5612051, 41.760245], [-87.5610737, 41.7601185]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>[[-87.6394537, 41.7669997], [-87.6394376, 41.7665466], [-87.6394068, 41.7653622]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>[[-87.6394604, 41.7671857], [-87.6394537, 41.7669997]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>[[-87.6394068, 41.7653622], [-87.6394028, 41.7652062]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>[[-87.6393706, 41.7638487], [-87.6393545, 41.7632635], [-87.6393438, 41.7628254], [-87.6393438, 41.7626513], [-87.6393464, 41.7625333], [-87.6393505, 41.7624133], [-87.6393639, 41.7622192], [-87.639392, 41.761825], [-87.6394282, 41.7612999], [-87.6394537, 41.7609407], [-87.6394738, 41.7606376], [-87.6394926, 41.7604435], [-87.6395208, 41.7602665], [-87.639553, 41.7601324], [-87.6395811, 41.7600354], [-87.639616, 41.7599404]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>[[-87.6395476, 41.772457], [-87.6395382, 41.7721119], [-87.6395342, 41.7719179], [-87.6395355, 41.7717678], [-87.6395409, 41.7716448], [-87.6395463, 41.7714958], [-87.6395516, 41.7713197], [-87.6395543, 41.7711747], [-87.6395543, 41.7710607], [-87.6395476, 41.7708266]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>[[-87.6395422, 41.7706456], [-87.6395329, 41.7700815], [-87.6395168, 41.7694043], [-87.6395074, 41.7690122]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>[[-87.6395476, 41.7708266], [-87.6395422, 41.7706456]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>[[-87.639502, 41.7688292], [-87.6394913, 41.7684161], [-87.6394752, 41.7677099], [-87.6394604, 41.7671857]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>[[-87.6395074, 41.7690122], [-87.639502, 41.7688292]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>[[-87.6396415, 41.7760845], [-87.6396281, 41.7756335], [-87.639612, 41.7750214], [-87.6395966, 41.7744452]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>[[-87.6396481, 41.7762573], [-87.6396415, 41.7760845]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>[[-87.6395926, 41.7742673], [-87.6395784, 41.7737512], [-87.639552, 41.7726484]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>[[-87.6395966, 41.7744452], [-87.6395926, 41.7742673]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>[[-87.639552, 41.7726484], [-87.6395476, 41.772457]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>[[-87.6395509, 41.7744448], [-87.6395664, 41.7750734], [-87.6395932, 41.7760865]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>[[-87.6395463, 41.7742693], [-87.6395509, 41.7744448]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>[[-87.6395978, 41.7762568], [-87.6396066, 41.7765646], [-87.6396133, 41.7768116], [-87.6396214, 41.7771937], [-87.6396394, 41.7779039]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>[[-87.6395932, 41.7760865], [-87.6395978, 41.7762568]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>[[-87.6397373, 41.7779039], [-87.639726, 41.7776057], [-87.6397139, 41.7773767], [-87.6396978, 41.7771527], [-87.6396777, 41.7769337], [-87.6396656, 41.7767426], [-87.6396562, 41.7765666], [-87.6396509, 41.7764176], [-87.6396481, 41.7762573]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>[[-87.6394296, 41.7688312], [-87.6394269, 41.7690142]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>[[-87.6394577, 41.7708186], [-87.6394671, 41.7712207], [-87.6394792, 41.7717338], [-87.6394993, 41.77246]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>[[-87.6394537, 41.7706316], [-87.6394577, 41.7708186]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>[[-87.6395051, 41.7726464], [-87.6395181, 41.7732121], [-87.6395355, 41.7738612], [-87.6395463, 41.7742693]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>[[-87.6394993, 41.77246], [-87.6395051, 41.7726464]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>[[-87.6393598, 41.7653642], [-87.6393706, 41.7658133], [-87.6393853, 41.7664375], [-87.6394095, 41.7670027]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>[[-87.6393558, 41.7652092], [-87.6393598, 41.7653642]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>[[-87.6394135, 41.7671847], [-87.6394336, 41.7679839], [-87.6394376, 41.7684071], [-87.6394336, 41.7686441], [-87.6394296, 41.7688312]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>[[-87.6394095, 41.7670027], [-87.6394135, 41.7671847]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>[[-87.6394269, 41.7690142], [-87.6394215, 41.7693293], [-87.6394229, 41.7694813], [-87.6394269, 41.7696554], [-87.6394349, 41.7699264], [-87.6394537, 41.7706316]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>[[-87.6393706, 41.7638487], [-87.6393558, 41.7636657], [-87.6393129, 41.7632515], [-87.6393035, 41.7630975]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>[[-87.6393478, 41.7648551], [-87.6393505, 41.764641], [-87.6393719, 41.7642899], [-87.6393746, 41.7640938]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>[[-87.6395583, 41.7599373], [-87.6395194, 41.7600604], [-87.6394779, 41.7602255], [-87.6394484, 41.7603955], [-87.6394229, 41.7605906], [-87.6394041, 41.7608117], [-87.639384, 41.7611798], [-87.6393438, 41.761761], [-87.6393156, 41.7622122]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>[[-87.6325335, 41.7691407], [-87.6326126, 41.7689286]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>[[-87.6313447, 41.7725859], [-87.6315341, 41.7721023], [-87.6319075, 41.7709835], [-87.6325335, 41.7691407]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>[[-87.6312664, 41.7728089], [-87.6313447, 41.7725859]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>[[-87.6307296, 41.7744387], [-87.6307795, 41.7743026], [-87.63083, 41.7741325], [-87.6309535, 41.7737405], [-87.6310921, 41.7733109], [-87.6312664, 41.7728089]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>[[-87.6339725, 41.7652696], [-87.6343132, 41.7643374], [-87.6345653, 41.7636751]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>[[-87.6338947, 41.7654847], [-87.6339725, 41.7652696]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>[[-87.6332939, 41.7670962], [-87.6338947, 41.7654847]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>[[-87.6332188, 41.7673042], [-87.6332939, 41.7670962]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>[[-87.6326126, 41.7689286], [-87.6332188, 41.7673042]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>[[-87.6339175, 41.7652696], [-87.6338397, 41.7654817]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>[[-87.6345183, 41.7636651], [-87.634222, 41.7644414], [-87.6339175, 41.7652696]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>[[-87.6346189, 41.7634061], [-87.6345183, 41.7636651]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>[[-87.6346659, 41.7634191], [-87.6350052, 41.7625508], [-87.6354209, 41.7614844], [-87.6358621, 41.76035], [-87.636007, 41.7599708], [-87.6361049, 41.7596977], [-87.6361961, 41.7594426], [-87.6363288, 41.7590375], [-87.6364951, 41.7585032], [-87.6366762, 41.757952], [-87.636872, 41.7574148], [-87.6369659, 41.7571607], [-87.6371174, 41.7567515], [-87.6373964, 41.7560172], [-87.6377182, 41.7551808], [-87.6379328, 41.7546616], [-87.6381863, 41.7540102], [-87.6383539, 41.753584], [-87.638594, 41.7529467], [-87.6387723, 41.7524355], [-87.6388702, 41.7521253], [-87.6389654, 41.7518142], [-87.6390072, 41.7516959]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>[[-87.6345653, 41.7636751], [-87.6346659, 41.7634191]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>[[-87.6324812, 41.7691437], [-87.6323003, 41.7696577], [-87.6318564, 41.770976], [-87.6315101, 41.7719538], [-87.6312708, 41.7725852]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>[[-87.6325603, 41.7689286], [-87.6324812, 41.7691437]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>[[-87.6331638, 41.7673052], [-87.6325603, 41.7689286]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>[[-87.633243, 41.7670912], [-87.6331638, 41.7673052]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>[[-87.6338397, 41.7654817], [-87.633243, 41.7670912]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>[[-87.6306904, 41.7743959], [-87.6305891, 41.7747015], [-87.6303778, 41.7752623], [-87.6301722, 41.7757693]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>[[-87.6311917, 41.772806], [-87.6310409, 41.7732332], [-87.6308868, 41.7737279], [-87.6308408, 41.7738669], [-87.6308039, 41.7739773], [-87.6307699, 41.774125], [-87.6306904, 41.7743959]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>[[-87.6312708, 41.7725852], [-87.6311917, 41.772806]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>[[-87.6363698, 41.8256472], [-87.6363739, 41.8254653], [-87.6363926, 41.8248956], [-87.636406, 41.8245868], [-87.6364154, 41.824283], [-87.6364195, 41.8240522], [-87.6364154, 41.8237574], [-87.6363953, 41.8228049], [-87.6363738, 41.8218619]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>[[-87.6367362, 41.8091291], [-87.636693, 41.8092805], [-87.6364583, 41.8101302], [-87.6363095, 41.810654], [-87.636229, 41.8110069], [-87.63617, 41.8113507], [-87.6361298, 41.8116456], [-87.6361123, 41.8119175], [-87.6361029, 41.8121644], [-87.6361097, 41.8125482], [-87.6361338, 41.8133708], [-87.6361606, 41.8143894], [-87.6361873, 41.8151544], [-87.6361982, 41.8156068], [-87.6361973, 41.8158247], [-87.6361829, 41.8160153], [-87.6361566, 41.8162855], [-87.6361351, 41.8165573]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>[[-87.6184076, 41.8592478], [-87.6185391, 41.8604903], [-87.618592, 41.8608808], [-87.6186409, 41.8611335], [-87.6187033, 41.8613938], [-87.6187501, 41.861559]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>[[-87.6193874, 41.8624405], [-87.6194912, 41.8628569], [-87.6195281, 41.8630732]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>[[-87.6152176, 41.8483828], [-87.6149433, 41.8477051], [-87.6146426, 41.8469046], [-87.6142532, 41.845998], [-87.6138993, 41.8451718], [-87.6136172, 41.8445125], [-87.6133431, 41.8439192], [-87.6131377, 41.8434796], [-87.6129422, 41.8430343], [-87.6123741, 41.8416738], [-87.6116808, 41.8400283], [-87.6110985, 41.838664], [-87.6104785, 41.8372029], [-87.6098008, 41.8356049], [-87.609439, 41.8347615], [-87.6092579, 41.8343378], [-87.6090735, 41.8339162], [-87.6089307, 41.8336279], [-87.6087763, 41.8333423], [-87.6086323, 41.8331073], [-87.6084769, 41.8328723], [-87.6082246, 41.8325292], [-87.6079585, 41.832191], [-87.6073234, 41.8313746], [-87.6066945, 41.8305542], [-87.6053789, 41.8288336], [-87.6028008, 41.8254508], [-87.6001714, 41.8220143], [-87.5986298, 41.819983], [-87.5980376, 41.8191451], [-87.5976552, 41.818604], [-87.59649, 41.816945], [-87.5952885, 41.8152297], [-87.5929226, 41.8118616], [-87.5916267, 41.8100071]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>[[-87.6192048, 41.8624652], [-87.6193075, 41.8628614], [-87.6193443, 41.862986]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>[[-87.6193281, 41.8624498], [-87.6195382, 41.8633158], [-87.6195711, 41.8634722]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>[[-87.6182199, 41.8585525], [-87.6184398, 41.8590979], [-87.6187617, 41.859879], [-87.618869, 41.8601367], [-87.6189575, 41.8604503], [-87.6191774, 41.8612694], [-87.6194108, 41.8620874]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>[[-87.6188287, 41.8605982], [-87.6188079, 41.8609637]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>[[-87.6192649, 41.8624588], [-87.6189541, 41.8611571]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>[[-87.6171809, 41.8554179], [-87.6172069, 41.8552219], [-87.6172423, 41.8550634], [-87.6173657, 41.8546339], [-87.6174157, 41.8544296], [-87.6174361, 41.8542585], [-87.6174338, 41.8539703], [-87.6174225, 41.8537431], [-87.6173848, 41.8534912], [-87.6172784, 41.853209], [-87.6167662, 41.8520949], [-87.6164278, 41.8512537], [-87.6152176, 41.8483828]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>[[-87.6192048, 41.8624652], [-87.6188926, 41.8611647]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>[[-87.6192649, 41.8624588], [-87.6194456, 41.863188], [-87.6194925, 41.8633341]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>[[-87.6182728, 41.8590185], [-87.6183996, 41.8600988], [-87.618462, 41.8606212]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>[[-87.6179784, 41.8578655], [-87.6180495, 41.8580171], [-87.6181064, 41.8581822], [-87.6182601, 41.8585605], [-87.6186758, 41.8595494], [-87.6189414, 41.8602106], [-87.6190674, 41.8606881], [-87.6193464, 41.8617188], [-87.6194108, 41.8620874], [-87.6194689, 41.8625229], [-87.6194725, 41.8625498], [-87.6195106, 41.8628979], [-87.6195281, 41.8630732], [-87.6195711, 41.8634722], [-87.6195992, 41.863678]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>[[-87.6191245, 41.8624632], [-87.6193443, 41.862986], [-87.6194925, 41.8633341], [-87.6195992, 41.863678]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>[[-87.6208734, 41.867236], [-87.6206133, 41.8666152], [-87.6203013, 41.8658637], [-87.6199116, 41.8649289], [-87.6197749, 41.8645374], [-87.6196334, 41.864032], [-87.6195154, 41.8636045], [-87.6193866, 41.863247], [-87.6192585, 41.8629323], [-87.6192176, 41.8628054], [-87.6191801, 41.8626366], [-87.6191245, 41.8624632]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>[[-87.6183251, 41.8590565], [-87.6184827, 41.8604084], [-87.618533, 41.8608837], [-87.6185501, 41.8609992]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>[[-87.6186249, 41.8597996], [-87.6186329, 41.8599809], [-87.6186141, 41.8601197], [-87.6186122, 41.8602013]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>[[-87.6169736, 41.8554644], [-87.616998, 41.8557463], [-87.6170364, 41.8559263], [-87.6170974, 41.8561456], [-87.6171234, 41.8562133], [-87.6171745, 41.8563465], [-87.6174746, 41.8571076], [-87.6176276, 41.8574973], [-87.6177205, 41.8577393], [-87.6179066, 41.8582075], [-87.6180149, 41.8585088], [-87.6180653, 41.8587005], [-87.6181158, 41.8589521], [-87.6181606, 41.8593399], [-87.6182203, 41.8599778], [-87.6182962, 41.8605386], [-87.6183416, 41.8607981], [-87.6184279, 41.8611255], [-87.6185465, 41.8614668], [-87.6187936, 41.862077], [-87.6190867, 41.8627679], [-87.6191021, 41.8628042], [-87.6192882, 41.8632653], [-87.6194076, 41.8636208], [-87.6194898, 41.8639074], [-87.6196355, 41.8644432], [-87.6197407, 41.8647806], [-87.6198808, 41.8651473], [-87.6203258, 41.8662021], [-87.6210617, 41.8680037], [-87.6212046, 41.8683519], [-87.6213623, 41.8687285], [-87.6215448, 41.8691878], [-87.6215823, 41.8692753], [-87.6216611, 41.869459], [-87.6216704, 41.8694814], [-87.6216804, 41.8695039]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>[[-87.6185578, 41.8596413], [-87.6186122, 41.8602013], [-87.6186598, 41.8606881], [-87.6187241, 41.8612434], [-87.6187999, 41.861552], [-87.6188294, 41.8616682], [-87.6188643, 41.8617997], [-87.6189092, 41.8619341]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>[[-87.6180455, 41.8582326], [-87.6181743, 41.8585845], [-87.618362, 41.85903], [-87.6186383, 41.8596932], [-87.6186606, 41.8597499], [-87.6187513, 41.8599703], [-87.6188327, 41.8601687], [-87.6188985, 41.8604028], [-87.6189494, 41.8606381], [-87.6190776, 41.86114]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>[[-87.6186606, 41.8597499], [-87.6186919, 41.8598665], [-87.618708, 41.8599528], [-87.6187288, 41.8600692], [-87.618749, 41.8601837], [-87.6187784, 41.8606012], [-87.6187925, 41.8607759], [-87.6188079, 41.8609637], [-87.6187925, 41.8612643], [-87.6187949, 41.8613899]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>[[-87.6193281, 41.8624498], [-87.6190172, 41.861147]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>[[-87.6150275, 41.8484239], [-87.6162172, 41.8513018], [-87.6165643, 41.8521443], [-87.6171603, 41.8534662], [-87.6172058, 41.8536282], [-87.6172343, 41.853796], [-87.6172429, 41.8540234], [-87.6172314, 41.8541535], [-87.6171923, 41.8543606], [-87.6170064, 41.8551019], [-87.6169736, 41.8554644]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>[[-87.6184908, 41.8594955], [-87.6186222, 41.8607919], [-87.6186598, 41.8611076], [-87.6187033, 41.8613938]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>[[-87.6186732, 41.8602286], [-87.6187704, 41.861166], [-87.6187949, 41.8613899], [-87.6188126, 41.8615609], [-87.6188294, 41.8616682]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>[[-87.59141, 41.8100926], [-87.592725, 41.8118901], [-87.5950738, 41.8152366], [-87.5974787, 41.8186565], [-87.5982603, 41.8197363], [-87.5999886, 41.8220646], [-87.6026029, 41.8254809], [-87.6051892, 41.8288669], [-87.6064957, 41.8305808], [-87.607137, 41.8314185], [-87.6077845, 41.8322479], [-87.6080442, 41.8325857], [-87.6082928, 41.8329252], [-87.6084506, 41.8331662], [-87.6085961, 41.8334108], [-87.6087336, 41.8336629], [-87.6088593, 41.8339139], [-87.6090494, 41.8343523], [-87.6092398, 41.8347915], [-87.6096087, 41.8356684], [-87.6103048, 41.8373039], [-87.6110039, 41.8389472], [-87.6112916, 41.8396125], [-87.6116198, 41.8403867], [-87.6121845, 41.8417147], [-87.6126498, 41.8428179], [-87.612973, 41.8435715], [-87.6131049, 41.8438747], [-87.6132434, 41.8441653], [-87.6136377, 41.8449556], [-87.6138183, 41.8453394], [-87.6139858, 41.8457291], [-87.6142815, 41.846424], [-87.6145035, 41.8469736], [-87.6146398, 41.8473489], [-87.6147697, 41.8477283], [-87.6150275, 41.8484239]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>[[-87.6003685, 41.7368202], [-87.6001721, 41.7376851], [-87.5985553, 41.7447709], [-87.5971766, 41.7508364], [-87.5961062, 41.7555244], [-87.5952444, 41.7593521], [-87.5938027, 41.765782], [-87.5934905, 41.7671706], [-87.5932163, 41.768358], [-87.5930579, 41.7690452], [-87.5927391, 41.7703142], [-87.5926813, 41.7705677], [-87.5923885, 41.7718434], [-87.5922705, 41.7723755], [-87.5922544, 41.7724925], [-87.592239, 41.7726546], [-87.5922071, 41.7728641]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>[[-87.629395, 41.8083274], [-87.6293709, 41.8075695], [-87.6293597, 41.8071496], [-87.629352, 41.8069523], [-87.6293447, 41.8067669]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>[[-87.6296388, 41.8031045], [-87.6296434, 41.8035997], [-87.629671, 41.8045], [-87.6296817, 41.8048305]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>[[-87.6293822, 41.8060487], [-87.6293687, 41.8057522], [-87.6293383, 41.805492], [-87.6292169, 41.8047874], [-87.6291837, 41.804442], [-87.6291677, 41.8040494], [-87.6291417, 41.8033825], [-87.6291072, 41.8021625]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>[[-87.6291439, 41.8067729], [-87.6291335, 41.8063594], [-87.6290774, 41.8047834], [-87.6290498, 41.8038429]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>[[-87.6293151, 41.8083306], [-87.6293015, 41.8079875], [-87.6292918, 41.8075309]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>[[-87.6296641, 41.807313], [-87.6296756, 41.8075045], [-87.6297265, 41.8076504], [-87.6298189, 41.8077632], [-87.6299721, 41.8079002]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>[[-87.6291677, 41.8040494], [-87.6291427, 41.8045635]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>[[-87.6304588, 41.8081442], [-87.6301879, 41.8080163], [-87.6299721, 41.8079002], [-87.629813, 41.8077852], [-87.6297212, 41.8076844], [-87.629577, 41.8074531]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>[[-87.6288313, 41.802671], [-87.6288548, 41.8028595], [-87.6289128, 41.8031381], [-87.628984, 41.8034853], [-87.6290498, 41.8038429], [-87.6291427, 41.8045635], [-87.6291525, 41.8047214], [-87.6292428, 41.8055358], [-87.6293096, 41.8061294], [-87.629336, 41.8064743], [-87.6293454, 41.8067383]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>[[-87.6290367, 41.8066735], [-87.6290132, 41.806458], [-87.6289594, 41.8047814], [-87.6289385, 41.8034898], [-87.6289128, 41.8031381]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>[[-87.6298865, 41.802608], [-87.6299124, 41.8036354], [-87.6299052, 41.8037985], [-87.6298606, 41.8040196], [-87.6298131, 41.8041929]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>[[-87.6296371, 41.8083221], [-87.6296343, 41.8082906], [-87.6296231, 41.8079755], [-87.6296082, 41.8078952], [-87.6295457, 41.8077088], [-87.629437, 41.8074868], [-87.6293865, 41.8073515], [-87.6293597, 41.8071496]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>[[-87.6291139, 41.8073286], [-87.6291389, 41.8070806], [-87.6291439, 41.8067729], [-87.6291109, 41.8065377], [-87.6290776, 41.8063292], [-87.6290211, 41.8047854], [-87.6289986, 41.8037391], [-87.628984, 41.8034853]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>[[-87.6295387, 41.8030574], [-87.6295522, 41.8036097], [-87.6295887, 41.8048053], [-87.6295888, 41.8051454], [-87.6295689, 41.805294], [-87.629502, 41.8054865]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>[[-87.6298208, 41.8030539], [-87.6298311, 41.8036077], [-87.6298417, 41.8039731], [-87.6298131, 41.8041929], [-87.6297256, 41.8045036]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>[[-87.6295538, 41.8083244], [-87.6295519, 41.8082516], [-87.6295364, 41.8081367], [-87.6294742, 41.8079683], [-87.6294008, 41.8077706]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>[[-87.6293096, 41.8061294], [-87.629303, 41.8063849], [-87.629291, 41.8064881], [-87.6292545, 41.8068507]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>[[-87.6295285, 41.8073628], [-87.6294856, 41.8072679], [-87.6294308, 41.8071142], [-87.629402, 41.8069467], [-87.6293875, 41.8065628], [-87.6293898, 41.8063764], [-87.6293888, 41.806317], [-87.6293815, 41.8060873]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>[[-87.6297694, 41.8083189], [-87.6297647, 41.808215], [-87.6297454, 41.8081372], [-87.6296725, 41.8079639], [-87.6295457, 41.8077088]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>[[-87.6292337, 41.8083304], [-87.6292318, 41.8081016], [-87.629233, 41.8079843], [-87.6292732, 41.8077454]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>[[-87.629927, 41.8082892], [-87.6299136, 41.8081962], [-87.6298902, 41.8080966], [-87.6298652, 41.8080276], [-87.629736, 41.807785]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>[[-87.6293687, 41.8057522], [-87.629401, 41.8052972], [-87.6294099, 41.8049801], [-87.6293296, 41.8020842]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>[[-87.6294748, 41.8083232], [-87.6294598, 41.8080712], [-87.62945, 41.8079689], [-87.6294008, 41.8077706], [-87.6293709, 41.8075695]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>[[-87.6291572, 41.8083326], [-87.6291555, 41.8082572], [-87.6291748, 41.8081109], [-87.6292008, 41.8079843], [-87.6292732, 41.8077454], [-87.6292918, 41.8075309], [-87.629292, 41.8074225], [-87.6293174, 41.8072535], [-87.6293415, 41.8071125], [-87.629352, 41.8069523]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>[[-87.6294261, 41.8020702], [-87.629461, 41.8036117], [-87.6294976, 41.8047954], [-87.6295061, 41.8052537], [-87.6294924, 41.8054015], [-87.6294307, 41.8056828]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>[[-87.6291737, 41.8218141], [-87.6290958, 41.8207811]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>[[-87.6288681, 41.8122889], [-87.6288979, 41.8115056]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>[[-87.6289706, 41.8092875], [-87.6289653, 41.8090874]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>[[-87.6289653, 41.8090874], [-87.6289373, 41.8083242]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>[[-87.6289863, 41.8118123], [-87.6288827, 41.8109938]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>[[-87.6289812, 41.8097704], [-87.6289677, 41.8100616], [-87.6289194, 41.8103814], [-87.6288926, 41.8104854], [-87.6288755, 41.8107613]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>[[-87.6298769, 41.8082879], [-87.629876, 41.8082182], [-87.62986, 41.8081203], [-87.6298296, 41.808014], [-87.629736, 41.807785], [-87.6296622, 41.8076504], [-87.629577, 41.8074531], [-87.6295285, 41.8073628]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>[[-87.6220961, 41.8698967], [-87.6220641, 41.869809], [-87.622029, 41.8696838], [-87.6219861, 41.869541], [-87.6219373, 41.8694183], [-87.6218928, 41.8693063], [-87.6216577, 41.8687235], [-87.6214993, 41.8683504], [-87.6213555, 41.8680021], [-87.6213012, 41.8678749], [-87.6208944, 41.8669665], [-87.6207957, 41.8667461], [-87.6206044, 41.8663051], [-87.620206, 41.8653394], [-87.6199338, 41.8646352], [-87.6198131, 41.8642597], [-87.6197125, 41.8638422], [-87.6196173, 41.8632949], [-87.6195543, 41.8627271], [-87.6195333, 41.8625256], [-87.6195053, 41.8622567], [-87.6194785, 41.8620434], [-87.6194449, 41.8618392], [-87.6193652, 41.8615001], [-87.619354, 41.861461], [-87.6191855, 41.8608718], [-87.6189568, 41.8600218], [-87.6187839, 41.8594245], [-87.6186859, 41.8591653], [-87.6185578, 41.8588942], [-87.6181455, 41.8581589], [-87.6179784, 41.8578655], [-87.617897, 41.8577107], [-87.6178031, 41.8575159], [-87.617683, 41.8572583], [-87.6176077, 41.8570724], [-87.6173166, 41.856325], [-87.6172615, 41.8561817], [-87.617248, 41.8561467], [-87.6171775, 41.8559115], [-87.6171409, 41.8557462], [-87.6171228, 41.8555878], [-87.6171172, 41.8554309]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>[[-87.622392, 41.8705792], [-87.622325, 41.8704052], [-87.6222888, 41.8702729], [-87.6222552, 41.8701421], [-87.622197, 41.8698889], [-87.6221647, 41.869773], [-87.6221295, 41.8696558], [-87.6220886, 41.8695358], [-87.622034, 41.8693961], [-87.6219499, 41.8691812], [-87.6216027, 41.8683499], [-87.6214006, 41.8678668], [-87.6209962, 41.866942], [-87.6208216, 41.8665428], [-87.6204655, 41.8656884], [-87.620135, 41.8648949], [-87.6200465, 41.8646632], [-87.6199284, 41.8642677], [-87.6198399, 41.8639561], [-87.6197836, 41.8636884], [-87.6196951, 41.863185], [-87.6196012, 41.8625404], [-87.6195993, 41.8625284], [-87.6194886, 41.8618107], [-87.6194114, 41.8614901], [-87.6193997, 41.86145], [-87.6192311, 41.8608718], [-87.6189414, 41.8597951], [-87.6188669, 41.8595328], [-87.6187831, 41.8592817], [-87.6187348, 41.8591598], [-87.6186088, 41.8588882], [-87.6181913, 41.8581496], [-87.6179459, 41.8577051], [-87.6178343, 41.8574939], [-87.6177304, 41.8572478], [-87.6176546, 41.8570601], [-87.6173642, 41.8563165], [-87.61731, 41.8561672], [-87.6172834, 41.856094], [-87.6172263, 41.8558915], [-87.6171905, 41.8556584], [-87.6171818, 41.8555389], [-87.6171809, 41.8554179]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>[[-87.5922201, 41.7730203], [-87.5922742, 41.7728195], [-87.5923828, 41.7724949], [-87.5924253, 41.7723401], [-87.5925343, 41.7718656], [-87.592835, 41.7705609], [-87.5930488, 41.7695795], [-87.5931621, 41.7690562], [-87.5933174, 41.7683333], [-87.5935706, 41.7672376], [-87.5939056, 41.7657679], [-87.595427, 41.7590043], [-87.5962144, 41.7555345], [-87.5973714, 41.7504746], [-87.5987424, 41.7444411], [-87.6003726, 41.7373101], [-87.6004864, 41.7368223]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>[[-87.592835, 41.7705609], [-87.5928093, 41.7707251], [-87.5927945, 41.7709001], [-87.5927661, 41.7710887]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>[[-87.5932071, 41.7691215], [-87.5931533, 41.7692952], [-87.5930488, 41.7695795], [-87.5926813, 41.7705677], [-87.5925846, 41.7708426], [-87.5925287, 41.7710269]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>South Chicago Sub District</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>[[-87.5922201, 41.7730203], [-87.5923494, 41.7724365], [-87.5925923, 41.7714003], [-87.5926494, 41.7711389]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>[[-87.5914995, 41.8100573], [-87.5927713, 41.8118762], [-87.5951167, 41.8152207], [-87.5975169, 41.8186416], [-87.5982969, 41.81972], [-87.6000304, 41.8220439], [-87.6026297, 41.8254512], [-87.6052213, 41.8288449], [-87.6065403, 41.8305691], [-87.6071812, 41.831405], [-87.607826, 41.8322309], [-87.6080858, 41.8325682], [-87.6083311, 41.8329104], [-87.6084942, 41.8331522], [-87.6086424, 41.833406], [-87.6087825, 41.8336564], [-87.6089066, 41.8339101], [-87.6091003, 41.8343463], [-87.6092854, 41.834783], [-87.6096572, 41.8356587], [-87.6103493, 41.8372902], [-87.6110449, 41.8389372], [-87.6113327, 41.8396028], [-87.611661, 41.8403773], [-87.6122256, 41.841705], [-87.6126909, 41.8428082], [-87.6130139, 41.8435544], [-87.6132182, 41.8439921], [-87.6134304, 41.8444267], [-87.613691, 41.844942], [-87.6138666, 41.8453289], [-87.6140355, 41.8457167], [-87.6143274, 41.8464136], [-87.6145525, 41.846962], [-87.6146921, 41.8473424], [-87.6148238, 41.8477203], [-87.6150721, 41.848412]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>[[-87.6282096, 41.7818307], [-87.628208, 41.7819496], [-87.6282258, 41.7825315], [-87.6282434, 41.783064]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>[[-87.6308311, 41.8590292], [-87.6308316, 41.8590824], [-87.6308408, 41.8594851], [-87.630847, 41.8597545], [-87.6308414, 41.8598367], [-87.6307649, 41.8603463], [-87.630748, 41.8604572], [-87.630684, 41.8609157], [-87.6306593, 41.861089], [-87.6306217, 41.8615644]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>[[-87.6393156, 41.7622122], [-87.6392982, 41.7624763], [-87.6392941, 41.7626563], [-87.6392955, 41.7628014], [-87.6393035, 41.7630975]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>[[-87.6291038, 41.8160132], [-87.629139, 41.8155834], [-87.6291321, 41.8151014], [-87.629044, 41.8122053], [-87.6290299, 41.8114057], [-87.6290649, 41.8105678], [-87.629045, 41.8099376], [-87.6290516, 41.8097474], [-87.6290611, 41.80955], [-87.6290644, 41.8094403], [-87.6290653, 41.8092863]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>[[-87.6282507, 41.7832823], [-87.6282518, 41.7838026], [-87.6282417, 41.7842282], [-87.6282175, 41.7846497], [-87.6281989, 41.7851121], [-87.6281849, 41.7853959]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>[[-87.6282944, 41.783062], [-87.6282796, 41.7825989], [-87.6282623, 41.7818458], [-87.6282608, 41.7817347]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>[[-87.6282434, 41.783064], [-87.6282507, 41.7832823]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>[[-87.6283012, 41.7832784], [-87.6282944, 41.783062]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>[[-87.5873975, 41.8027117], [-87.5874703, 41.802915], [-87.587636, 41.8032759], [-87.587722, 41.8034943]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>[[-87.5876989, 41.8028816], [-87.5877319, 41.803035], [-87.5877661, 41.8032134], [-87.587836, 41.8034916], [-87.5879, 41.8037186]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>[[-87.6288161, 41.802], [-87.6288098, 41.8018042]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>[[-87.6291179, 41.8163605], [-87.6291038, 41.8160132], [-87.6289863, 41.8118123]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>[[-87.6291931, 41.8192632], [-87.6291943, 41.8193526]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>[[-87.6362116, 41.8203763], [-87.6361781, 41.8201894], [-87.6361459, 41.8199805], [-87.6361271, 41.8197787], [-87.636111, 41.8195788]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>[[-87.6393035, 41.7630975], [-87.6393236, 41.7639778], [-87.6393478, 41.7648551]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>[[-87.6393478, 41.7648551], [-87.6393558, 41.7652092]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>[[-87.6393746, 41.7640938], [-87.6393706, 41.7638487]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>[[-87.6394028, 41.7652062], [-87.6393934, 41.764753], [-87.6393746, 41.7640938]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>[[-87.5913367, 41.7769246], [-87.5917178, 41.7752144], [-87.5920897, 41.7735985], [-87.5922201, 41.7730203]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>[[-87.591254, 41.7772911], [-87.5913367, 41.7769246]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>[[-87.5912832, 41.7769168], [-87.5911986, 41.777285]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>[[-87.5922071, 41.7728641], [-87.5916768, 41.7751611], [-87.5915547, 41.7757349], [-87.5913289, 41.7767172], [-87.5912832, 41.7769168]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>[[-87.5916013, 41.7761595], [-87.5918149, 41.7752288], [-87.5921786, 41.773615], [-87.5923215, 41.7730191], [-87.5924709, 41.7723593], [-87.5927661, 41.7710887], [-87.5928562, 41.7706708], [-87.5932071, 41.7691215], [-87.5932231, 41.769063], [-87.5933438, 41.7684974], [-87.593637, 41.7672389], [-87.5939646, 41.7657767], [-87.5962612, 41.7555375], [-87.6005366, 41.7368223]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>[[-87.5911669, 41.7780795], [-87.5914773, 41.7766863], [-87.5916013, 41.7761595]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>[[-87.591369, 41.7761243], [-87.590928, 41.778061]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>[[-87.6003228, 41.7368178], [-87.5960572, 41.7555187], [-87.5937432, 41.7657792], [-87.5934235, 41.767161], [-87.5931855, 41.7682212], [-87.5929864, 41.7690375], [-87.5927217, 41.7701834], [-87.5925287, 41.7710269], [-87.592346, 41.7718381], [-87.5922277, 41.7723712], [-87.5921158, 41.7728264], [-87.5919075, 41.7737524], [-87.5915916, 41.7751447], [-87.591369, 41.7761243]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>[[-87.6299957, 41.7762499], [-87.6301758, 41.7758729]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>[[-87.6301722, 41.7757693], [-87.6299902, 41.776148]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>[[-87.6298791, 41.776491], [-87.6299957, 41.7762499]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>[[-87.6299902, 41.776148], [-87.6298403, 41.7764579]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>[[-87.6290591, 41.8090868], [-87.6290575, 41.8090684]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Wash Lead</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>[[-87.6290297, 41.808336], [-87.6290275, 41.808263]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>[[-87.6295365, 41.8029667], [-87.6295387, 41.8030574]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>[[-87.6295146, 41.8020662], [-87.6295365, 41.8029667]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>[[-87.6298191, 41.8029621], [-87.6298208, 41.8030539]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>[[-87.6298016, 41.8020242], [-87.6298191, 41.8029621]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>[[-87.6403976, 41.8015956], [-87.6403797, 41.8009352], [-87.6403556, 41.8000264], [-87.64031, 41.7982178], [-87.6402872, 41.797341], [-87.6402577, 41.7961462], [-87.6402195, 41.7944913]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>[[-87.6403521, 41.8017745], [-87.6403596, 41.8020439], [-87.6403851, 41.8030066], [-87.6403757, 41.8032466], [-87.640361, 41.8034095], [-87.6403341, 41.8035675], [-87.6402859, 41.8037534], [-87.6402349, 41.8039164], [-87.6401625, 41.8040923], [-87.640086, 41.8042473], [-87.6399814, 41.8044322], [-87.6398151, 41.8046691], [-87.6396542, 41.8048591], [-87.639441, 41.805076], [-87.6391915, 41.8052989], [-87.6388254, 41.8056058], [-87.6383949, 41.8059597], [-87.6381361, 41.8061807], [-87.6379698, 41.8063326], [-87.6378035, 41.8065095], [-87.6376667, 41.8066775], [-87.6375567, 41.8068294], [-87.6374575, 41.8069834], [-87.6373421, 41.8071913], [-87.6372697, 41.8073583], [-87.6371799, 41.8075972]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>[[-87.6403485, 41.8015961], [-87.6403521, 41.8017745]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>[[-87.6404016, 41.8017733], [-87.6403976, 41.8015956]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>[[-87.6361351, 41.8165573], [-87.6362285, 41.8159741], [-87.6362453, 41.8158435], [-87.6362505, 41.8156748], [-87.6362357, 41.815136], [-87.6362102, 41.8142904], [-87.6361874, 41.8133918], [-87.6361606, 41.8125762], [-87.6361553, 41.8122373], [-87.6361593, 41.8120224], [-87.6361687, 41.8118195], [-87.6361861, 41.8116226], [-87.6362049, 41.8114737], [-87.6362371, 41.8112538], [-87.636276, 41.8110508], [-87.6363108, 41.8108979], [-87.6363698, 41.810659], [-87.6365106, 41.8101472], [-87.6366863, 41.8095015], [-87.6367892, 41.8091282]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>[[-87.6367892, 41.8091282], [-87.6368402, 41.8089421]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>[[-87.6371799, 41.8075972], [-87.6371021, 41.8078521], [-87.6369116, 41.8085068], [-87.6367902, 41.8089433]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>[[-87.6367902, 41.8089433], [-87.6367362, 41.8091291]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>[[-87.6195992, 41.863678], [-87.6197112, 41.8641179], [-87.6198252, 41.8645173], [-87.6199036, 41.8647546], [-87.6200733, 41.8651965], [-87.6204032, 41.8659816], [-87.6204764, 41.8661548]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>[[-87.6191245, 41.8624632], [-87.6189092, 41.8619341], [-87.6187501, 41.861559], [-87.6186792, 41.8613892], [-87.618584, 41.8611425], [-87.6185501, 41.8609992], [-87.618462, 41.8606212], [-87.6184217, 41.8604662], [-87.6183828, 41.860305], [-87.6182977, 41.8596273], [-87.6182065, 41.8588343]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>[[-87.6190776, 41.86114], [-87.6193874, 41.8624405]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>[[-87.6190172, 41.861147], [-87.6188912, 41.8606343], [-87.6188636, 41.8605342], [-87.6188153, 41.8603205], [-87.6187871, 41.8601197], [-87.6187513, 41.8599703]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>[[-87.6189541, 41.8611571], [-87.6189287, 41.8610346], [-87.6189206, 41.8609422], [-87.6189179, 41.8607964], [-87.6188912, 41.8606343]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Metra Line</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>[[-87.6188926, 41.8611647], [-87.6188582, 41.8609438], [-87.6188287, 41.8605982], [-87.618826, 41.8604443], [-87.6188153, 41.8603205]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>[[-87.6368781, 41.8500805], [-87.636888, 41.8499501]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>[[-87.636888, 41.8499501], [-87.6368993, 41.8498428], [-87.6369293, 41.8495507], [-87.6369385, 41.8494885], [-87.6369492, 41.8493107], [-87.6369475, 41.8492476], [-87.6369318, 41.8486653], [-87.6369229, 41.8482456]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Southwest Sub District</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>[[-87.6369229, 41.8482456], [-87.6369199, 41.848133]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>[[-87.5893698, 41.785935], [-87.5894048, 41.7857761], [-87.5896174, 41.7847697], [-87.5899763, 41.7831486], [-87.590381, 41.7814914], [-87.5905649, 41.7807043]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>[[-87.589272, 41.7863982], [-87.5893698, 41.785935]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>[[-87.5892731, 41.7859375], [-87.5895431, 41.7847582], [-87.5902714, 41.7815563], [-87.5904643, 41.7807045]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>[[-87.5891701, 41.7863983], [-87.5892731, 41.7859375]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>[[-87.5904214, 41.7807047], [-87.5902366, 41.7815031], [-87.5894983, 41.7847458], [-87.5892247, 41.7859387]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>[[-87.5892247, 41.7859387], [-87.5891258, 41.7863983]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>[[-87.5903235, 41.7807049], [-87.5901413, 41.781496], [-87.5894017, 41.7847384], [-87.5891301, 41.7859412]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>[[-87.5891301, 41.7859412], [-87.5890256, 41.7863983]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>[[-87.5889887, 41.7876121], [-87.5891353, 41.7869692], [-87.589272, 41.7863982]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>[[-87.5888855, 41.7880558], [-87.5889887, 41.7876121]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>[[-87.5888916, 41.7876122], [-87.5890413, 41.7869597], [-87.5891701, 41.7863983]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>[[-87.588788, 41.7880564], [-87.5888916, 41.7876122]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>[[-87.5891258, 41.7863983], [-87.5888449, 41.7876123]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>[[-87.5888449, 41.7876123], [-87.5887973, 41.7878198], [-87.5887432, 41.7880566]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>[[-87.5890256, 41.7863983], [-87.5887453, 41.7876125]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>[[-87.5887453, 41.7876125], [-87.5887041, 41.7878034], [-87.5886447, 41.7880572]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>[[-87.58812, 41.7914236], [-87.5882251, 41.7909724], [-87.5888855, 41.7880558]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>[[-87.5876616, 41.7934728], [-87.5877236, 41.7931979]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>[[-87.5880225, 41.7914237], [-87.5881299, 41.7909666], [-87.588788, 41.7880564]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>[[-87.5875615, 41.7934735], [-87.5876241, 41.7931992]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>[[-87.5887432, 41.7880566], [-87.5880835, 41.7909555], [-87.5879715, 41.7914237]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>[[-87.5875759, 41.7931999], [-87.5875162, 41.7934738]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>[[-87.5886447, 41.7880572], [-87.5879888, 41.7909419], [-87.5878817, 41.7914237]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>[[-87.5874787, 41.7932012], [-87.5874161, 41.7934745]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>[[-87.6308042, 41.8578679], [-87.6308121, 41.8584501], [-87.6308217, 41.8587439], [-87.6308311, 41.8590292]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Joliet Sub District</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>[[-87.63065, 41.8618827], [-87.6306647, 41.861694], [-87.6306861, 41.8614206], [-87.6307102, 41.8611089], [-87.6307343, 41.8609194], [-87.6307963, 41.8604652], [-87.6308108, 41.8603405], [-87.630829, 41.8602257], [-87.6308864, 41.8598632], [-87.630898, 41.8597645], [-87.6308765, 41.8589075], [-87.6308615, 41.8582602], [-87.6308524, 41.8578668]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>[[-87.5877236, 41.7931979], [-87.5880093, 41.7919237], [-87.5880581, 41.7917103]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>[[-87.5880581, 41.7917103], [-87.58812, 41.7914236]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>[[-87.5876241, 41.7931992], [-87.5879172, 41.7919141], [-87.5879592, 41.7917104]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>[[-87.5879592, 41.7917104], [-87.5880225, 41.7914237]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>[[-87.5879084, 41.7917105], [-87.5877621, 41.7923636], [-87.5875759, 41.7931999]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>[[-87.5879715, 41.7914237], [-87.5879084, 41.7917105]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>[[-87.5878187, 41.7917106], [-87.5876692, 41.7923519], [-87.5874787, 41.7932012]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>[[-87.5878817, 41.7914237], [-87.5878187, 41.7917106]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>[[-87.5907286, 41.7789239], [-87.5904359, 41.7802015], [-87.5903785, 41.7804637]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>[[-87.5903785, 41.7804637], [-87.5903235, 41.7807049]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>[[-87.5908251, 41.7789243], [-87.5905289, 41.7802152], [-87.5904777, 41.7804633]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>[[-87.5904777, 41.7804633], [-87.5904214, 41.7807047]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>[[-87.5905246, 41.7804631], [-87.590578, 41.7802055], [-87.5908366, 41.7790971], [-87.5908774, 41.7789245]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>[[-87.5904643, 41.7807045], [-87.5905246, 41.7804631]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>[[-87.5906199, 41.7804627], [-87.5906743, 41.7802123], [-87.5909336, 41.7791093], [-87.5909727, 41.7789248]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>[[-87.5905649, 41.7807043], [-87.5906199, 41.7804627]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>[[-87.5910398, 41.7786283], [-87.5911029, 41.7783309], [-87.5911669, 41.7780795]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>[[-87.5909727, 41.7789248], [-87.5910398, 41.7786283]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>[[-87.5909445, 41.7786274], [-87.591013, 41.7783186], [-87.591254, 41.7772911]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>[[-87.5908774, 41.7789245], [-87.5909445, 41.7786274]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>[[-87.5911986, 41.777285], [-87.5909716, 41.778292], [-87.5908949, 41.778627]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>[[-87.5908949, 41.778627], [-87.5908251, 41.7789243]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>[[-87.590928, 41.778061], [-87.5908762, 41.7782841], [-87.590797, 41.7786261]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>[[-87.590797, 41.7786261], [-87.5907286, 41.7789239]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>[[-87.5874161, 41.7934745], [-87.5874069, 41.7935151], [-87.5872592, 41.7941138], [-87.5871803, 41.7945157], [-87.587061, 41.7950749]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>[[-87.587061, 41.7950749], [-87.5870118, 41.7953183]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>[[-87.5875162, 41.7934738], [-87.5875038, 41.7935266], [-87.5873608, 41.7941243], [-87.58727, 41.7945381], [-87.5871496, 41.7950738]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>[[-87.5871496, 41.7950738], [-87.587093, 41.795317]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>[[-87.5872018, 41.7950729], [-87.5873141, 41.7945537], [-87.5874148, 41.7940966], [-87.5875615, 41.7934735]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>[[-87.5871519, 41.795316], [-87.5872018, 41.7950729]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>[[-87.587302, 41.7950721], [-87.5874126, 41.7945693], [-87.5875131, 41.794097], [-87.5876616, 41.7934728]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>[[-87.5872536, 41.7953144], [-87.587302, 41.7950721]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>[[-87.5870316, 41.7994561], [-87.5870145, 41.7992982], [-87.5869901, 41.7988137], [-87.5869749, 41.7984536], [-87.5869819, 41.7979274], [-87.5869922, 41.7975643], [-87.5870106, 41.7971989], [-87.5870439, 41.7967689], [-87.5870877, 41.7963437], [-87.5871365, 41.7959813], [-87.5872091, 41.7955292], [-87.5872536, 41.7953144]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>[[-87.5870629, 41.7998041], [-87.5870316, 41.7994561]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>[[-87.5869411, 41.7994566], [-87.586926, 41.7992469], [-87.5869134, 41.7988153], [-87.5869149, 41.7979232], [-87.5869245, 41.7975588], [-87.5869431, 41.7971907], [-87.5869714, 41.7967624], [-87.5870081, 41.7963332], [-87.5870445, 41.7959711], [-87.587084, 41.795683], [-87.5871519, 41.795316]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>[[-87.5869682, 41.7998063], [-87.5869411, 41.7994566]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>[[-87.587093, 41.795317], [-87.5869951, 41.7958173], [-87.586925, 41.7962717], [-87.5868709, 41.7967446], [-87.5868385, 41.7971415], [-87.5868169, 41.7975148], [-87.5868058, 41.7979301], [-87.5868066, 41.7983116], [-87.5868217, 41.7988228], [-87.586842, 41.79912], [-87.5868781, 41.799457]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>[[-87.5868781, 41.799457], [-87.5869189, 41.7998075]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>[[-87.5870118, 41.7953183], [-87.5869083, 41.7959075], [-87.586858, 41.7962824], [-87.5868064, 41.7967563], [-87.5867735, 41.7971639], [-87.5867503, 41.7975943], [-87.5867409, 41.7979296], [-87.5867387, 41.798377], [-87.5867517, 41.7988477], [-87.586794, 41.7994574]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>[[-87.586794, 41.7994574], [-87.5868242, 41.7998099]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>[[-87.5875202, 41.8022805], [-87.5874757, 41.8021257], [-87.5873252, 41.8014884], [-87.5872444, 41.801076], [-87.587183, 41.8006992], [-87.5871676, 41.8006061], [-87.5870629, 41.7998041]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>[[-87.5876192, 41.8026262], [-87.5875202, 41.8022805]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>[[-87.587425, 41.8022834], [-87.5872314, 41.8014973], [-87.5870855, 41.8007093], [-87.5870702, 41.8006086], [-87.5869889, 41.8000595], [-87.5869682, 41.7998063]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>[[-87.5875231, 41.8026274], [-87.587425, 41.8022834]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>[[-87.5869189, 41.7998075], [-87.587022, 41.8006099], [-87.5871826, 41.8014998], [-87.5873231, 41.8020804], [-87.587373, 41.8022844]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>[[-87.587373, 41.8022844], [-87.5874707, 41.802628]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>[[-87.5868242, 41.7998099], [-87.5868723, 41.8002526], [-87.5869292, 41.8006207], [-87.5869936, 41.8010549], [-87.5870883, 41.8015068], [-87.5871794, 41.8019276], [-87.5872274, 41.8020896], [-87.5872766, 41.8022866]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>[[-87.5872766, 41.8022866], [-87.5873736, 41.8026291]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>[[-87.5873736, 41.8026291], [-87.5873975, 41.8027117], [-87.5876398, 41.8035613], [-87.5878057, 41.8040948], [-87.5879611, 41.8045005], [-87.5880687, 41.8047604], [-87.5882051, 41.8050595], [-87.5883845, 41.8054228], [-87.5885552, 41.805759], [-87.588758, 41.8061405], [-87.5891163, 41.8067594], [-87.5893003, 41.8070657], [-87.5894988, 41.807369], [-87.5897074, 41.8076807], [-87.5903716, 41.8086263], [-87.59062, 41.8089904], [-87.5912249, 41.8098362]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>[[-87.5912249, 41.8098362], [-87.59141, 41.8100926]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>[[-87.5874707, 41.802628], [-87.587722, 41.8034943], [-87.5878597, 41.8039516], [-87.588026, 41.8044652], [-87.5881171, 41.8046955], [-87.5882606, 41.8050321], [-87.5884554, 41.8054173], [-87.5886306, 41.8057466], [-87.5888303, 41.8061102], [-87.589014, 41.8064239], [-87.5891978, 41.806726], [-87.5893868, 41.8070347], [-87.5895901, 41.8073402], [-87.5904714, 41.808596], [-87.591198, 41.8096321], [-87.5912384, 41.809689], [-87.5913182, 41.809801]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>[[-87.5913182, 41.809801], [-87.5914995, 41.8100573]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>[[-87.5914038, 41.8097685], [-87.5913256, 41.8096558], [-87.5911421, 41.8093915], [-87.5905674, 41.8085731], [-87.5895906, 41.807169], [-87.5893072, 41.8067221], [-87.5891074, 41.8063863], [-87.5889352, 41.8060787], [-87.5887523, 41.8057324], [-87.5885953, 41.8054154], [-87.5884342, 41.8050736], [-87.5882455, 41.804616], [-87.5880647, 41.804155], [-87.5879, 41.8037186], [-87.5876545, 41.8030628], [-87.5875231, 41.8026274]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>[[-87.5915844, 41.8100237], [-87.5914038, 41.8097685]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>[[-87.5914472, 41.8097519], [-87.5906198, 41.8085719], [-87.5896338, 41.8071572], [-87.5893606, 41.8067066], [-87.5891541, 41.8063603], [-87.5889869, 41.8060598], [-87.588825, 41.8057569], [-87.5886521, 41.8054043], [-87.5884845, 41.8050606], [-87.5882918, 41.804602], [-87.5881164, 41.8041369], [-87.5878998, 41.8035231], [-87.5876989, 41.8028816], [-87.5876192, 41.8026262]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>University Park Sub District</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>[[-87.5916267, 41.8100071], [-87.5914472, 41.8097519]]</t>
         </is>
       </c>
     </row>
